--- a/results/05_transient_transcription_output/905/905_197311_SF.JPG_stage_digit_manipulation.xlsx
+++ b/results/05_transient_transcription_output/905/905_197311_SF.JPG_stage_digit_manipulation.xlsx
@@ -748,9 +748,9 @@
 </t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">221
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">241
 </t>
         </is>
       </c>
@@ -762,7 +762,7 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
@@ -780,7 +780,7 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
@@ -791,15 +791,24 @@
         </is>
       </c>
       <c r="M4" s="3" t="n"/>
-      <c r="N4" s="3" t="n"/>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="P4" s="3" t="n"/>
-      <c r="Q4" s="3" t="n"/>
+      <c r="Q4" s="3" t="inlineStr">
+        <is>
+          <t>431</t>
+        </is>
+      </c>
       <c r="R4" s="3" t="n"/>
       <c r="S4" s="3" t="inlineStr">
         <is>
@@ -807,16 +816,21 @@
 </t>
         </is>
       </c>
-      <c r="T4" s="3" t="n"/>
+      <c r="T4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">851
+</t>
+        </is>
+      </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">43
 </t>
         </is>
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">803
 </t>
         </is>
       </c>
@@ -828,13 +842,13 @@
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
+          <t xml:space="preserve">861
 </t>
         </is>
       </c>
@@ -872,18 +886,27 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">265
 </t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
-</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="n"/>
-      <c r="I5" s="3" t="n"/>
+          <t xml:space="preserve">13
+</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>4380</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">35
@@ -892,19 +915,15 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17 5
-</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">183
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">99
+211
+</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="n"/>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -916,13 +935,13 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
-      <c r="P5" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">416
+          <t xml:space="preserve">900
+</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -934,7 +953,8 @@
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">213
+</t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr">
@@ -945,7 +965,7 @@
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">743
+          <t xml:space="preserve">943
 </t>
         </is>
       </c>
@@ -1007,7 +1027,7 @@
       <c r="D6" s="3" t="n"/>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
@@ -1017,9 +1037,9 @@
 </t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">119
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
@@ -1037,43 +1057,40 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="L6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">725
+          <t xml:space="preserve">52
+</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="n"/>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16495171
+178
+2 2 4221
 </t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
-</t>
-        </is>
-      </c>
-      <c r="P6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">416
+          <t xml:space="preserve">251
+</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -1091,7 +1108,7 @@
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t>083</t>
+          <t>783</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
@@ -1101,31 +1118,31 @@
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
+          <t xml:space="preserve">910
 </t>
         </is>
       </c>
@@ -1150,24 +1167,20 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2744
-</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+          <t xml:space="preserve">344
+</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="n"/>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -1179,7 +1192,7 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -1197,7 +1210,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -1207,27 +1220,27 @@
 </t>
         </is>
       </c>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">179
+      <c r="M7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">729
 </t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8821
+          <t xml:space="preserve">940
 </t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -1237,9 +1250,9 @@
 </t>
         </is>
       </c>
-      <c r="R7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">227
+      <c r="R7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
@@ -1275,7 +1288,7 @@
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
@@ -1287,7 +1300,7 @@
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
@@ -1306,25 +1319,25 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2602
+          <t xml:space="preserve">16024
 </t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -1348,49 +1361,39 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">093
-</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">133
+</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="n"/>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>4580</t>
-        </is>
-      </c>
-      <c r="N8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18628
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">818
+</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="n"/>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8821
+          <t xml:space="preserve">898
 </t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
-        </is>
-      </c>
-      <c r="Q8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">465
-</t>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t>4451</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
@@ -1407,13 +1410,13 @@
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">871
+          <t xml:space="preserve">821
 </t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">59
 </t>
         </is>
       </c>
@@ -1435,8 +1438,18 @@
 </t>
         </is>
       </c>
-      <c r="Y8" s="3" t="n"/>
-      <c r="Z8" s="3" t="n"/>
+      <c r="Y8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">860
+</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">38
+</t>
+        </is>
+      </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
           <t>5</t>
@@ -1452,34 +1465,21 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22404
-</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">829
-</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>778</t>
-        </is>
-      </c>
+          <t xml:space="preserve">16024
+</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n"/>
+      <c r="E9" s="3" t="n"/>
+      <c r="F9" s="3" t="n"/>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>52</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">617
+          <t xml:space="preserve">627
 </t>
         </is>
       </c>
@@ -1497,54 +1497,53 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">894
-</t>
+          <t>371</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8145
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">982
+          <t xml:space="preserve">75
 </t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">882
 </t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>37</t>
+          <t xml:space="preserve">1271
+</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>710</t>
         </is>
       </c>
       <c r="S9" s="3" t="n"/>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1842
+          <t xml:space="preserve">3892
 </t>
         </is>
       </c>
@@ -1556,7 +1555,7 @@
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">989
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
@@ -1568,21 +1567,16 @@
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
-        </is>
-      </c>
-      <c r="Z9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">127
+</t>
+        </is>
+      </c>
+      <c r="Z9" s="3" t="n"/>
       <c r="AA9" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -1598,74 +1592,69 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22404
+          <t xml:space="preserve">1464
 </t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
-</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">661
+          <t xml:space="preserve">4465227
+8179171
+</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2282891
+181
 </t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">295
-</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">135
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">82828
+199812
+</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">821
-</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">146
-</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="n"/>
+          <t xml:space="preserve">34
+</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="n"/>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">792871272
+1
+</t>
+        </is>
+      </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">845
 </t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">784
 </t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">94
+2
 </t>
         </is>
       </c>
@@ -1677,63 +1666,40 @@
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">929
-</t>
-        </is>
-      </c>
-      <c r="S10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">390
-</t>
-        </is>
-      </c>
-      <c r="T10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">768
-</t>
-        </is>
-      </c>
-      <c r="U10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">106
-</t>
-        </is>
-      </c>
-      <c r="V10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">981
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="S10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7424
+1111
+</t>
+        </is>
+      </c>
+      <c r="T10" s="3" t="n"/>
+      <c r="U10" s="3" t="n"/>
+      <c r="V10" s="3" t="n"/>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">77
 </t>
         </is>
       </c>
       <c r="X10" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">066
-</t>
-        </is>
-      </c>
-      <c r="Y10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">845
-</t>
-        </is>
-      </c>
-      <c r="Z10" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t xml:space="preserve">451
+</t>
+        </is>
+      </c>
+      <c r="Y10" s="3" t="n"/>
+      <c r="Z10" s="3" t="n"/>
       <c r="AA10" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -1749,31 +1715,15 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1289
-</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">284
-</t>
-        </is>
-      </c>
-      <c r="E11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">661
-</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">295
-</t>
-        </is>
-      </c>
+          <t>4985</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n"/>
+      <c r="E11" s="3" t="n"/>
+      <c r="F11" s="3" t="n"/>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
@@ -1785,73 +1735,49 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">821
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">104
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">46
+</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="n"/>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
-        </is>
-      </c>
-      <c r="M11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">77718
+6222
+</t>
+        </is>
+      </c>
+      <c r="M11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">691
 </t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1906
-</t>
-        </is>
-      </c>
-      <c r="P11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="Q11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">268
-</t>
-        </is>
-      </c>
-      <c r="R11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">929
-</t>
-        </is>
-      </c>
-      <c r="S11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">231
+24721195
+</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="n"/>
+      <c r="Q11" s="3" t="n"/>
+      <c r="R11" s="3" t="n"/>
+      <c r="S11" s="3" t="n"/>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">768
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
@@ -1861,33 +1787,33 @@
 </t>
         </is>
       </c>
-      <c r="V11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">981
-</t>
-        </is>
-      </c>
-      <c r="W11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">185
-</t>
-        </is>
-      </c>
-      <c r="X11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">066
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="W11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">865
+</t>
+        </is>
+      </c>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
+          <t xml:space="preserve">8960
 </t>
         </is>
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">45
 </t>
         </is>
       </c>
@@ -1906,7 +1832,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2996
+          <t xml:space="preserve">996
 </t>
         </is>
       </c>
@@ -1929,78 +1855,69 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
-</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">140
-</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">977
+</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="n"/>
+      <c r="I12" s="3" t="n"/>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
+          <t xml:space="preserve">59
 </t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
-        </is>
-      </c>
-      <c r="M12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="M12" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">911
 </t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t xml:space="preserve">12
+</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">1661
 </t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
-        </is>
-      </c>
-      <c r="Q12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">268
-</t>
-        </is>
-      </c>
-      <c r="R12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">265
-</t>
-        </is>
-      </c>
-      <c r="S12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">390
+          <t xml:space="preserve">64
+</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">260
+</t>
+        </is>
+      </c>
+      <c r="R12" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">415
+</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
@@ -2018,11 +1935,11 @@
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="W12" s="8" t="inlineStr">
+          <t xml:space="preserve">217
+</t>
+        </is>
+      </c>
+      <c r="W12" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">198
 </t>
@@ -2030,7 +1947,7 @@
       </c>
       <c r="X12" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
@@ -2042,7 +1959,8 @@
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">40
+</t>
         </is>
       </c>
       <c r="AA12" s="3" t="inlineStr">
@@ -2090,7 +2008,8 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">159
+1109
 </t>
         </is>
       </c>
@@ -2100,34 +2019,34 @@
 </t>
         </is>
       </c>
-      <c r="J13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">394
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
       <c r="K13" s="3" t="n"/>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
@@ -2151,7 +2070,7 @@
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -2163,7 +2082,7 @@
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -2175,13 +2094,13 @@
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
-        </is>
-      </c>
-      <c r="X13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
+      <c r="X13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
@@ -2212,13 +2131,14 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2238
+          <t xml:space="preserve">3238
 </t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>7285</t>
+          <t xml:space="preserve">275
+</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -2227,67 +2147,49 @@
 </t>
         </is>
       </c>
-      <c r="F14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9225
-</t>
-        </is>
-      </c>
+      <c r="F14" s="3" t="n"/>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>051</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">05
+</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="n"/>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40
-</t>
-        </is>
-      </c>
-      <c r="L14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="n"/>
+      <c r="L14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">771
 </t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="N14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="n"/>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">926
+          <t xml:space="preserve">921
 </t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -2297,20 +2199,21 @@
 </t>
         </is>
       </c>
-      <c r="R14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">114
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t>4271</t>
+          <t xml:space="preserve">237
+</t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">275
 </t>
         </is>
       </c>
@@ -2334,16 +2237,11 @@
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="Y14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">958
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="Y14" s="3" t="n"/>
       <c r="Z14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">09
@@ -2365,7 +2263,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2600
+          <t xml:space="preserve">2666
 </t>
         </is>
       </c>
@@ -2381,75 +2279,55 @@
 </t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
+      <c r="F15" s="3" t="n"/>
       <c r="G15" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">714
-</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
+          <t xml:space="preserve">324
+</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="n"/>
+      <c r="I15" s="3" t="n"/>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222
+</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">183
+</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="n"/>
+      <c r="O15" s="3" t="n"/>
+      <c r="P15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">26
 </t>
         </is>
       </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">215
-</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="n"/>
-      <c r="L15" s="3" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
-      <c r="M15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">172
-</t>
-        </is>
-      </c>
-      <c r="N15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">896
-</t>
-        </is>
-      </c>
-      <c r="P15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">212
-</t>
-        </is>
-      </c>
-      <c r="Q15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">210
+      <c r="Q15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">410
 </t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">65
 </t>
         </is>
       </c>
@@ -2462,7 +2340,7 @@
       <c r="T15" s="3" t="n"/>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -2480,12 +2358,13 @@
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t>097</t>
+          <t xml:space="preserve">958
+</t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
@@ -2510,7 +2389,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89348
+          <t xml:space="preserve">348
 </t>
         </is>
       </c>
@@ -2528,13 +2407,13 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29225
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
@@ -2556,20 +2435,16 @@
 </t>
         </is>
       </c>
-      <c r="K16" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="K16" s="3" t="n"/>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">828
 </t>
         </is>
       </c>
@@ -2581,42 +2456,38 @@
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>1584</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
-        </is>
-      </c>
-      <c r="S16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2291
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">414
+</t>
+        </is>
+      </c>
+      <c r="S16" s="3" t="n"/>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t xml:space="preserve">21214
+7922
+</t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">157
 </t>
         </is>
       </c>
@@ -2634,7 +2505,7 @@
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">803
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -2646,8 +2517,7 @@
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AA16" s="3" t="inlineStr">
@@ -2663,39 +2533,30 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>156468</t>
-        </is>
-      </c>
+      <c r="C17" s="3" t="n"/>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>1372</t>
+          <t>33</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>561</t>
-        </is>
-      </c>
-      <c r="F17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">099
-</t>
-        </is>
-      </c>
+          <t>666</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="n"/>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>060</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">790
-</t>
-        </is>
-      </c>
-      <c r="I17" s="8" t="inlineStr">
+          <t xml:space="preserve">30
+</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">108
 </t>
@@ -2703,42 +2564,37 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">853
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t>865594</t>
-        </is>
-      </c>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="n"/>
       <c r="P17" s="3" t="inlineStr">
         <is>
           <t>614</t>
         </is>
       </c>
-      <c r="Q17" s="8" t="inlineStr">
+      <c r="Q17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">193
 </t>
@@ -2746,26 +2602,20 @@
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">744
+981
 </t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="T17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">665
-</t>
-        </is>
-      </c>
-      <c r="U17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">591
-</t>
+          <t>7556</t>
+        </is>
+      </c>
+      <c r="T17" s="3" t="n"/>
+      <c r="U17" s="3" t="inlineStr">
+        <is>
+          <t>35</t>
         </is>
       </c>
       <c r="V17" s="8" t="inlineStr">
@@ -2774,20 +2624,20 @@
 </t>
         </is>
       </c>
-      <c r="W17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">989
-</t>
-        </is>
-      </c>
-      <c r="X17" s="3" t="inlineStr">
-        <is>
-          <t>097</t>
+      <c r="W17" s="8" t="inlineStr">
+        <is>
+          <t>6121</t>
+        </is>
+      </c>
+      <c r="X17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">203
+</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -2811,15 +2661,15 @@
 </t>
         </is>
       </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">681
-</t>
-        </is>
-      </c>
-      <c r="E18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">711
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">268
+</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
@@ -2829,7 +2679,7 @@
 </t>
         </is>
       </c>
-      <c r="G18" s="8" t="inlineStr">
+      <c r="G18" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">971
 </t>
@@ -2837,27 +2687,23 @@
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>446</t>
+          <t xml:space="preserve">1
+</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">30
 </t>
         </is>
       </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30
-</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23
-</t>
-        </is>
-      </c>
+      <c r="K18" s="3" t="n"/>
       <c r="L18" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">178
@@ -2866,19 +2712,18 @@
       </c>
       <c r="M18" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>5341</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 99
+          <t xml:space="preserve">9
 </t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">932
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
@@ -2890,16 +2735,11 @@
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">202
-</t>
-        </is>
-      </c>
-      <c r="S18" s="8" t="inlineStr">
+          <t>03</t>
+        </is>
+      </c>
+      <c r="R18" s="3" t="n"/>
+      <c r="S18" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">291
 </t>
@@ -2907,7 +2747,7 @@
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1881
+          <t xml:space="preserve">1851
 </t>
         </is>
       </c>
@@ -2919,25 +2759,25 @@
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
-      <c r="W18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
-      <c r="X18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">574
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="W18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">097
+</t>
+        </is>
+      </c>
+      <c r="X18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -2960,12 +2800,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12534
-</t>
-        </is>
-      </c>
+      <c r="C19" s="3" t="n"/>
       <c r="D19" s="3" t="inlineStr">
         <is>
           <t>33</t>
@@ -2979,36 +2814,31 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">77718
+273
 </t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>0164</t>
-        </is>
-      </c>
+          <t xml:space="preserve">77
+</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="n"/>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>303</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
-</t>
+          <t>55</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
@@ -3020,18 +2850,14 @@
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="N19" s="3" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="n"/>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
+          <t xml:space="preserve">871
 </t>
         </is>
       </c>
@@ -3055,7 +2881,7 @@
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
@@ -3067,40 +2893,35 @@
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
-        </is>
-      </c>
-      <c r="V19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="V19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">691
 </t>
         </is>
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">49
 </t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">835
-</t>
-        </is>
-      </c>
-      <c r="Z19" s="3" t="inlineStr">
-        <is>
           <t xml:space="preserve">15
 </t>
         </is>
       </c>
+      <c r="Z19" s="3" t="n"/>
       <c r="AA19" s="3" t="inlineStr">
         <is>
           <t>12</t>
@@ -3114,40 +2935,35 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">221
-</t>
-        </is>
-      </c>
+      <c r="C20" s="3" t="n"/>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
-</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">162
-</t>
-        </is>
-      </c>
-      <c r="F20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">209
-</t>
-        </is>
-      </c>
-      <c r="G20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">067
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">621
+</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="H20" s="3" t="n"/>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">122
+      <c r="I20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">454824
 </t>
         </is>
       </c>
@@ -3171,25 +2987,25 @@
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">874
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -3199,51 +3015,46 @@
 </t>
         </is>
       </c>
-      <c r="R20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">202
-</t>
-        </is>
-      </c>
-      <c r="S20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">206
-</t>
-        </is>
-      </c>
+      <c r="R20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">685
+</t>
+        </is>
+      </c>
+      <c r="S20" s="3" t="n"/>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
-        </is>
-      </c>
-      <c r="U20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="V20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">234
+          <t xml:space="preserve">31
+</t>
+        </is>
+      </c>
+      <c r="U20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">729
+</t>
+        </is>
+      </c>
+      <c r="V20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">341
 </t>
         </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">835
 </t>
         </is>
       </c>
@@ -3268,72 +3079,66 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12534
+          <t xml:space="preserve">2534
 </t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">883
 </t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>0164</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">119
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">828127
+160
+745414119
+</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="n"/>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">591
-</t>
-        </is>
-      </c>
-      <c r="K21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">31
+</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="n"/>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t xml:space="preserve">283
+</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
@@ -3344,7 +3149,7 @@
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
+          <t xml:space="preserve">67
 </t>
         </is>
       </c>
@@ -3360,15 +3165,16 @@
 </t>
         </is>
       </c>
-      <c r="S21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">898
+      <c r="S21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">47
 </t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">26
+1 1
 </t>
         </is>
       </c>
@@ -3378,27 +3184,27 @@
 </t>
         </is>
       </c>
-      <c r="V21" s="3" t="inlineStr">
+      <c r="V21" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">209
 </t>
         </is>
       </c>
-      <c r="W21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">202
+      <c r="W21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">991
 </t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">736
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
@@ -3423,7 +3229,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">53349
+          <t xml:space="preserve">2661
 </t>
         </is>
       </c>
@@ -3435,42 +3241,33 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="F22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2925
-</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">90
-</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">749
-</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
+          <t>130</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">255
+</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
+      <c r="I22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4282
 </t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">23
+77
 </t>
         </is>
       </c>
@@ -3482,13 +3279,13 @@
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
@@ -3500,7 +3297,8 @@
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">12
+2
 </t>
         </is>
       </c>
@@ -3516,39 +3314,31 @@
 </t>
         </is>
       </c>
-      <c r="S22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
-</t>
-        </is>
-      </c>
-      <c r="T22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">140
-</t>
-        </is>
-      </c>
-      <c r="U22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">112
+      <c r="S22" s="3" t="n"/>
+      <c r="T22" s="3" t="n"/>
+      <c r="U22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
-        </is>
-      </c>
-      <c r="W22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">890
-</t>
-        </is>
-      </c>
-      <c r="X22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">231
+</t>
+        </is>
+      </c>
+      <c r="W22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">449
+190
+</t>
+        </is>
+      </c>
+      <c r="X22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">124
+1856
 </t>
         </is>
       </c>
@@ -3579,7 +3369,7 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15486
+          <t xml:space="preserve">392
 </t>
         </is>
       </c>
@@ -3597,38 +3387,28 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">3106
 </t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">749
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">66
+</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="n"/>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="K23" s="3" t="inlineStr">
-        <is>
-          <t>6163</t>
-        </is>
-      </c>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="n"/>
       <c r="L23" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">180
@@ -3637,49 +3417,49 @@
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1171
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">2512
 </t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3931
+          <t xml:space="preserve">400
 </t>
         </is>
       </c>
@@ -3697,7 +3477,8 @@
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">998
+          <t xml:space="preserve">449
+190
 </t>
         </is>
       </c>
@@ -3734,139 +3515,116 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>309</t>
+          <t xml:space="preserve">586
+</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>7376</t>
+          <t>37</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
-</t>
-        </is>
-      </c>
-      <c r="F24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1159
+          <t>8510</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>572</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">193
-</t>
-        </is>
-      </c>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="n"/>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">904
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">879
+          <t xml:space="preserve">177
 </t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>8692</t>
+          <t xml:space="preserve">491
+</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>633</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
-        </is>
-      </c>
-      <c r="S24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">381
-</t>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="S24" s="3" t="inlineStr">
+        <is>
+          <t>752</t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">787
+          <t xml:space="preserve">937
 </t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">103
-</t>
-        </is>
-      </c>
-      <c r="W24" s="3" t="inlineStr">
-        <is>
-          <t>199</t>
-        </is>
-      </c>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="V24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">163
+</t>
+        </is>
+      </c>
+      <c r="W24" s="3" t="n"/>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t>1705</t>
-        </is>
-      </c>
-      <c r="Y24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">008
-</t>
-        </is>
-      </c>
-      <c r="Z24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">63
-</t>
-        </is>
-      </c>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y24" s="3" t="n"/>
+      <c r="Z24" s="3" t="n"/>
       <c r="AA24" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -3882,7 +3640,7 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2798
+          <t xml:space="preserve">397
 </t>
         </is>
       </c>
@@ -3894,65 +3652,65 @@
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">701
+          <t xml:space="preserve">791
 </t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
-</t>
+          <t>1448</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>105</t>
+          <t xml:space="preserve">15
+</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
-</t>
+          <t>984</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">39
 </t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="M25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">741
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">878
 </t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">6
 </t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9380
+          <t xml:space="preserve">381
 </t>
         </is>
       </c>
@@ -3970,18 +3728,19 @@
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t>644</t>
+          <t xml:space="preserve">38
+</t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">825
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
@@ -3993,31 +3752,26 @@
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="Y25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">750
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">211
+</t>
+        </is>
+      </c>
+      <c r="Y25" s="3" t="n"/>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -4036,137 +3790,112 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3414
+          <t xml:space="preserve">2798
 </t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
+          <t>948</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="n"/>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="n"/>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="n"/>
+      <c r="K26" s="3" t="n"/>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">174
 </t>
         </is>
       </c>
-      <c r="F26" s="3" t="inlineStr">
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="O26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">940
+</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="Q26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222
+</t>
+        </is>
+      </c>
+      <c r="R26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">200
+</t>
+        </is>
+      </c>
+      <c r="S26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
+      <c r="T26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">865
+</t>
+        </is>
+      </c>
+      <c r="U26" s="3" t="n"/>
+      <c r="V26" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">211
 </t>
         </is>
       </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">101
-</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">120
-</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">119
-</t>
-        </is>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">38
-</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="L26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="M26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
-      <c r="N26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="O26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">940
-</t>
-        </is>
-      </c>
-      <c r="P26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">121
-</t>
-        </is>
-      </c>
-      <c r="Q26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="R26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">816
-</t>
-        </is>
-      </c>
-      <c r="S26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">146
-</t>
-        </is>
-      </c>
-      <c r="T26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">839
-</t>
-        </is>
-      </c>
-      <c r="U26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">99
-</t>
-        </is>
-      </c>
-      <c r="V26" s="3" t="inlineStr">
-        <is>
-          <t>016</t>
-        </is>
-      </c>
-      <c r="W26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">197
+      <c r="W26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8020
 </t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
@@ -4191,7 +3920,7 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3436
+          <t xml:space="preserve">3414
 </t>
         </is>
       </c>
@@ -4203,60 +3932,62 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">792
+67
 </t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>1499</t>
+          <t xml:space="preserve">12
+1119
+</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">37
 </t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -4268,61 +3999,60 @@
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
+          <t>411</t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="S27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46
+</t>
+        </is>
+      </c>
+      <c r="T27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">839
+</t>
+        </is>
+      </c>
+      <c r="U27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">47
+</t>
+        </is>
+      </c>
+      <c r="V27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="W27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">197
+</t>
+        </is>
+      </c>
+      <c r="X27" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">188
 </t>
         </is>
       </c>
-      <c r="S27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">227
-</t>
-        </is>
-      </c>
-      <c r="T27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">696
-</t>
-        </is>
-      </c>
-      <c r="U27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">147
-</t>
-        </is>
-      </c>
-      <c r="V27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">209
-</t>
-        </is>
-      </c>
-      <c r="W27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="X27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">824
-</t>
-        </is>
-      </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">836
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
@@ -4347,7 +4077,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">51
+          <t xml:space="preserve">3700
 </t>
         </is>
       </c>
@@ -4359,60 +4089,47 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">792
+67
+</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="n"/>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">101
+</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="n"/>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">35
+</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="n"/>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">167
 </t>
         </is>
       </c>
-      <c r="F28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">817
-</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">101
-</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">707
-</t>
-        </is>
-      </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">35
-</t>
-        </is>
-      </c>
-      <c r="K28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">79
-</t>
-        </is>
-      </c>
-      <c r="L28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="M28" s="3" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -4424,66 +4141,67 @@
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t>855</t>
-        </is>
-      </c>
-      <c r="R28" s="3" t="inlineStr">
+          <t xml:space="preserve">255
+</t>
+        </is>
+      </c>
+      <c r="R28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="S28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">897
+</t>
+        </is>
+      </c>
+      <c r="T28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">696
+</t>
+        </is>
+      </c>
+      <c r="U28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">99
+</t>
+        </is>
+      </c>
+      <c r="V28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">209
+</t>
+        </is>
+      </c>
+      <c r="W28" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">188
 </t>
         </is>
       </c>
-      <c r="S28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="T28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7467
-</t>
-        </is>
-      </c>
-      <c r="U28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">99
-</t>
-        </is>
-      </c>
-      <c r="V28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="W28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">864
-</t>
-        </is>
-      </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">785
+          <t xml:space="preserve">83836
 </t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
@@ -4502,25 +4220,21 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3436
+          <t xml:space="preserve">4536
 </t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">65
-</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">4007
+263
+</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="n"/>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">414
 </t>
         </is>
       </c>
@@ -4532,12 +4246,12 @@
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>1499</t>
+          <t>141</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">331
+          <t xml:space="preserve">335
 </t>
         </is>
       </c>
@@ -4549,7 +4263,7 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
@@ -4561,20 +4275,20 @@
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">6041
+151
 </t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">71
 </t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
-</t>
+          <t>05840</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
@@ -4589,51 +4303,51 @@
 </t>
         </is>
       </c>
-      <c r="R29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">127
+      <c r="R29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7272
 </t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">866
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">815
-</t>
-        </is>
-      </c>
-      <c r="U29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">612
+          <t xml:space="preserve">747
+</t>
+        </is>
+      </c>
+      <c r="U29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
+          <t xml:space="preserve">752
 </t>
         </is>
       </c>
@@ -4658,37 +4372,36 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>1788</t>
+          <t xml:space="preserve">3436
+</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1211
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">814
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">064
 </t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">707
-</t>
+          <t>70</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
@@ -4705,7 +4418,7 @@
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -4717,48 +4430,48 @@
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>551</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>865</t>
+          <t xml:space="preserve">865
+</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">2280
 </t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1094
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t xml:space="preserve">815
+</t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
@@ -4769,25 +4482,25 @@
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1618
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">918
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>881</t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
@@ -4811,13 +4524,13 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23577
+          <t xml:space="preserve">17884
 </t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
@@ -4829,25 +4542,25 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
-        </is>
-      </c>
-      <c r="G31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">51111
-</t>
-        </is>
-      </c>
-      <c r="H31" s="8" t="inlineStr">
+          <t xml:space="preserve">213
+</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">501
+</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">141
 </t>
         </is>
       </c>
-      <c r="I31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">830
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
@@ -4857,9 +4570,9 @@
 </t>
         </is>
       </c>
-      <c r="K31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">297
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 3
 </t>
         </is>
       </c>
@@ -4871,49 +4584,42 @@
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">812
-</t>
-        </is>
-      </c>
-      <c r="N31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">018
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="n"/>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>85431</t>
+          <t xml:space="preserve">45845
+</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">011
-</t>
+          <t>61</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">1 48
 </t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="S31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
+          <t>018</t>
+        </is>
+      </c>
+      <c r="S31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">024
 </t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">784
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
@@ -4924,31 +4630,29 @@
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">918
 </t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">999
+          <t xml:space="preserve">7
 </t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">832
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>002</t>
         </is>
       </c>
       <c r="AA31" s="3" t="inlineStr">
@@ -4966,13 +4670,13 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2666
+          <t xml:space="preserve">357
 </t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
+          <t xml:space="preserve">264
 </t>
         </is>
       </c>
@@ -4984,89 +4688,88 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
+          <t xml:space="preserve">24
+77
 </t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">134
+</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">39
+</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="n"/>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2
+</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+777
+</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">909
+</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="Q32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
+      <c r="R32" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">100
 </t>
         </is>
       </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">134
-</t>
-        </is>
-      </c>
-      <c r="I32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26
-</t>
-        </is>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">39
-</t>
-        </is>
-      </c>
-      <c r="K32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="L32" s="3" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="M32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6811
-</t>
-        </is>
-      </c>
-      <c r="N32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="O32" s="3" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="P32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="Q32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">183
-</t>
-        </is>
-      </c>
-      <c r="R32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">491
 </t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9780
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
@@ -5078,31 +4781,26 @@
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
-        </is>
-      </c>
-      <c r="X32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">206
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">7
+</t>
+        </is>
+      </c>
+      <c r="X32" s="3" t="n"/>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
+          <t xml:space="preserve">834
 </t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
@@ -5121,23 +4819,23 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14008
+          <t xml:space="preserve">2666
 </t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
+          <t xml:space="preserve">73
 </t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
-        </is>
-      </c>
-      <c r="F33" s="8" t="inlineStr">
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">217
 </t>
@@ -5161,18 +4859,8 @@
 </t>
         </is>
       </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">97
-</t>
-        </is>
-      </c>
-      <c r="K33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">297
-</t>
-        </is>
-      </c>
+      <c r="J33" s="3" t="n"/>
+      <c r="K33" s="3" t="n"/>
       <c r="L33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">190
@@ -5181,7 +4869,8 @@
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>45</t>
+          <t xml:space="preserve">157
+</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
@@ -5192,73 +4881,73 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
-      </c>
-      <c r="P33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">011
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
+      <c r="P33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">616
 </t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">183
+</t>
+        </is>
+      </c>
+      <c r="R33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="S33" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">204
 </t>
         </is>
       </c>
-      <c r="R33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="S33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">774
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="W33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">175
+</t>
+        </is>
+      </c>
+      <c r="W33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">868
+          <t xml:space="preserve">9461
 </t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">302
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -5277,13 +4966,13 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12502
+          <t xml:space="preserve">4068
 </t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
@@ -5295,43 +4984,39 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">417
 </t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
-        </is>
-      </c>
-      <c r="H34" s="8" t="inlineStr">
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">156
 </t>
         </is>
       </c>
-      <c r="I34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">120
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7777
+262
 </t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
-        </is>
-      </c>
-      <c r="K34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">39
+</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="n"/>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
@@ -5343,7 +5028,7 @@
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
@@ -5355,61 +5040,61 @@
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">43
 </t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">748
+          <t xml:space="preserve">74
 </t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
-</t>
-        </is>
-      </c>
-      <c r="V34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">57
+</t>
+        </is>
+      </c>
+      <c r="V34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
+          <t xml:space="preserve">860
 </t>
         </is>
       </c>
@@ -5434,7 +5119,7 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2688
+          <t xml:space="preserve">356
 </t>
         </is>
       </c>
@@ -5452,13 +5137,13 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>
@@ -5468,85 +5153,80 @@
 </t>
         </is>
       </c>
-      <c r="I35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">120
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
+          <t xml:space="preserve">37
 </t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>001</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>450</t>
-        </is>
-      </c>
-      <c r="N35" s="3" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="O35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8200
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="N35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">837
+</t>
+        </is>
+      </c>
+      <c r="O35" s="3" t="n"/>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">200
+</t>
+        </is>
+      </c>
+      <c r="S35" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">198
 </t>
         </is>
       </c>
-      <c r="S35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">211
-</t>
-        </is>
-      </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">760
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
@@ -5558,7 +5238,7 @@
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">011
+          <t xml:space="preserve">606
 </t>
         </is>
       </c>
@@ -5570,7 +5250,7 @@
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -5589,7 +5269,7 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3568
+          <t xml:space="preserve">4688
 </t>
         </is>
       </c>
@@ -5601,35 +5281,37 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>484</t>
+          <t xml:space="preserve">207
+</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>84</t>
+          <t xml:space="preserve">82
+</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
@@ -5641,88 +5323,76 @@
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
-        </is>
-      </c>
-      <c r="M36" s="3" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
-      <c r="N36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">154
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="n"/>
+      <c r="N36" s="3" t="n"/>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8980
+          <t xml:space="preserve">8006
 </t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t>9641</t>
+          <t xml:space="preserve">228
+</t>
         </is>
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
+      <c r="S36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">211
+</t>
+        </is>
+      </c>
+      <c r="T36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">760
+</t>
+        </is>
+      </c>
+      <c r="U36" s="3" t="n"/>
+      <c r="V36" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">208
 </t>
         </is>
       </c>
-      <c r="S36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">211
-</t>
-        </is>
-      </c>
-      <c r="T36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">602
-</t>
-        </is>
-      </c>
-      <c r="U36" s="3" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="V36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">808
-</t>
-        </is>
-      </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t>06</t>
+          <t xml:space="preserve">116
+</t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">952
+          <t xml:space="preserve">956
 </t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA36" s="3" t="inlineStr">
@@ -5740,30 +5410,27 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>1643</t>
+          <t xml:space="preserve">358
+</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>1377</t>
+          <t>174</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>892</t>
+          <t>89</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1071
-</t>
-        </is>
-      </c>
-      <c r="G37" s="3" t="inlineStr">
-        <is>
-          <t>083</t>
-        </is>
-      </c>
+          <t xml:space="preserve">221
+</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="n"/>
       <c r="H37" s="3" t="inlineStr">
         <is>
           <t>806</t>
@@ -5771,96 +5438,91 @@
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
-</t>
+          <t>313</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>7361</t>
+          <t xml:space="preserve">16
+</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>285</t>
-        </is>
-      </c>
-      <c r="M37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">154
-</t>
-        </is>
-      </c>
-      <c r="N37" s="3" t="n"/>
+          <t>883</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="n"/>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t>284</t>
+        </is>
+      </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8980
+          <t xml:space="preserve">70
 </t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">45
+</t>
+        </is>
+      </c>
+      <c r="Q37" s="3" t="inlineStr">
+        <is>
+          <t>9611</t>
+        </is>
+      </c>
+      <c r="R37" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">208
 </t>
         </is>
       </c>
-      <c r="Q37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1123
-</t>
-        </is>
-      </c>
-      <c r="R37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">991
-</t>
-        </is>
-      </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">038
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2894
-</t>
-        </is>
-      </c>
-      <c r="U37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">68
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">62
+</t>
+        </is>
+      </c>
+      <c r="U37" s="3" t="n"/>
       <c r="V37" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">981
+2248
 </t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">985
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1114
+          <t xml:space="preserve">77
+181 1
 </t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
@@ -5885,107 +5547,103 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">329
-</t>
-        </is>
-      </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">863
+          <t xml:space="preserve">6432
+</t>
+        </is>
+      </c>
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">637
 </t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
-      <c r="F38" s="8" t="inlineStr">
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">171
+</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>085</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">141
 </t>
         </is>
       </c>
-      <c r="G38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">970
-</t>
-        </is>
-      </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">141
-</t>
-        </is>
-      </c>
-      <c r="I38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">011
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>375</t>
+          <t xml:space="preserve">11
+</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">5247
+2272
+1
+</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">177
+</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">14
 </t>
         </is>
       </c>
-      <c r="L38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">177
-</t>
-        </is>
-      </c>
-      <c r="M38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">154
-</t>
-        </is>
-      </c>
-      <c r="N38" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="N38" s="3" t="n"/>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>796</t>
-        </is>
-      </c>
-      <c r="P38" s="3" t="n"/>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="P38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
-        </is>
-      </c>
-      <c r="R38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
-      <c r="S38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">081
+          <t>77</t>
+        </is>
+      </c>
+      <c r="R38" s="3" t="n"/>
+      <c r="S38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">638
 </t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">771
-</t>
+          <t>558</t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
@@ -5995,25 +5653,21 @@
 </t>
         </is>
       </c>
-      <c r="W38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0921
+      <c r="W38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14441
+346
 </t>
         </is>
       </c>
       <c r="X38" s="3" t="n"/>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1229
-</t>
-        </is>
-      </c>
-      <c r="Z38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">44
+</t>
+        </is>
+      </c>
+      <c r="Z38" s="3" t="n"/>
       <c r="AA38" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -6029,52 +5683,48 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">1
+1 23
 </t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">414
 </t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">971
 </t>
         </is>
       </c>
       <c r="H39" s="3" t="n"/>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>375</t>
-        </is>
-      </c>
-      <c r="K39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">37
+</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="n"/>
       <c r="L39" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">188
@@ -6083,53 +5733,49 @@
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>76</t>
+          <t xml:space="preserve">171
+</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t xml:space="preserve">182
+</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
-</t>
-        </is>
-      </c>
-      <c r="R39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
-      <c r="S39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">125
+</t>
+        </is>
+      </c>
+      <c r="R39" s="3" t="n"/>
+      <c r="S39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">808
+          <t xml:space="preserve">71
 </t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">350
 </t>
         </is>
       </c>
@@ -6139,9 +5785,9 @@
 </t>
         </is>
       </c>
-      <c r="W39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">809
+      <c r="W39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">851
 </t>
         </is>
       </c>
@@ -6157,12 +5803,7 @@
 </t>
         </is>
       </c>
-      <c r="Z39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
+      <c r="Z39" s="3" t="n"/>
       <c r="AA39" s="3" t="inlineStr">
         <is>
           <t>26</t>
@@ -6190,100 +5831,82 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">160
+</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">207
+</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">38
+</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="n"/>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">158
 </t>
         </is>
       </c>
-      <c r="F40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">207
-</t>
-        </is>
-      </c>
-      <c r="G40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">98
-</t>
-        </is>
-      </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="I40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">38
-</t>
-        </is>
-      </c>
-      <c r="K40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="L40" s="3" t="inlineStr">
-        <is>
-          <t>438</t>
-        </is>
-      </c>
-      <c r="M40" s="3" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="N40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
+      <c r="N40" s="3" t="n"/>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
+          <t xml:space="preserve">2852
 </t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
       <c r="R40" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">1626
 </t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t>60</t>
+          <t xml:space="preserve">231 1
+</t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="U40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">012
+          <t xml:space="preserve">721
+</t>
+        </is>
+      </c>
+      <c r="U40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
@@ -6313,7 +5936,7 @@
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
@@ -6332,7 +5955,7 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3590
+          <t xml:space="preserve">2864
 </t>
         </is>
       </c>
@@ -6344,65 +5967,57 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>015</t>
+          <t xml:space="preserve">297
+</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">196
+111
+</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">58
+</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">090
+</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="n"/>
+      <c r="M41" s="3" t="n"/>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">18
 </t>
         </is>
       </c>
-      <c r="I41" s="3" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">58
-</t>
-        </is>
-      </c>
-      <c r="K41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">177
-</t>
-        </is>
-      </c>
-      <c r="M41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">153
-</t>
-        </is>
-      </c>
-      <c r="N41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">762
+          <t xml:space="preserve">766
 </t>
         </is>
       </c>
@@ -6414,31 +6029,29 @@
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
-        </is>
-      </c>
-      <c r="R41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">202
-</t>
-        </is>
-      </c>
-      <c r="S41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">204
-</t>
+          <t xml:space="preserve">268
+</t>
+        </is>
+      </c>
+      <c r="R41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">951
+</t>
+        </is>
+      </c>
+      <c r="S41" s="3" t="inlineStr">
+        <is>
+          <t>42</t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">614
-</t>
-        </is>
-      </c>
-      <c r="U41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
+          <t>7444</t>
+        </is>
+      </c>
+      <c r="U41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
@@ -6456,13 +6069,13 @@
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">805
+          <t xml:space="preserve">705
 </t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
@@ -6487,80 +6100,82 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">3590
 </t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
-        </is>
-      </c>
-      <c r="F42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">227
-</t>
-        </is>
-      </c>
-      <c r="G42" s="3" t="n"/>
+          <t xml:space="preserve">156
+</t>
+        </is>
+      </c>
+      <c r="F42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">135
+</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
       <c r="H42" s="3" t="n"/>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>71</t>
+          <t xml:space="preserve">39
+</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">63
+          <t xml:space="preserve">163
 </t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
-        </is>
-      </c>
-      <c r="L42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">177
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">29
+2
+</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="n"/>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
+          <t xml:space="preserve">9271249
+157
 </t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
-</t>
-        </is>
-      </c>
-      <c r="P42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">316
+          <t xml:space="preserve">66
+</t>
+        </is>
+      </c>
+      <c r="P42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
@@ -6572,22 +6187,17 @@
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">855
-</t>
-        </is>
-      </c>
-      <c r="U42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">141
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">579
+</t>
+        </is>
+      </c>
+      <c r="U42" s="3" t="n"/>
       <c r="V42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">222
@@ -6596,23 +6206,28 @@
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="X42" s="3" t="inlineStr">
-        <is>
           <t xml:space="preserve">194
 </t>
         </is>
       </c>
+      <c r="X42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">134
+</t>
+        </is>
+      </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1
 </t>
         </is>
       </c>
-      <c r="Z42" s="3" t="n"/>
+      <c r="Z42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">721
+</t>
+        </is>
+      </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
           <t>29</t>
@@ -6628,13 +6243,14 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>7345</t>
+          <t xml:space="preserve">276
+</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
@@ -6645,93 +6261,116 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
-</t>
-        </is>
-      </c>
-      <c r="G43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">925
-</t>
-        </is>
-      </c>
-      <c r="H43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">697
-</t>
-        </is>
-      </c>
-      <c r="I43" s="3" t="n"/>
-      <c r="J43" s="3" t="n"/>
-      <c r="K43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1615
+          <t xml:space="preserve">267
+</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">213
+</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="n"/>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">65
+</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
-        </is>
-      </c>
-      <c r="N43" s="3" t="n"/>
+          <t xml:space="preserve">711797
+127
+</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">99
+118
+</t>
+        </is>
+      </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">798
 </t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
-        </is>
-      </c>
-      <c r="R43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5
-</t>
-        </is>
-      </c>
-      <c r="S43" s="3" t="n"/>
+          <t xml:space="preserve">221
+</t>
+        </is>
+      </c>
+      <c r="R43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">031
+</t>
+        </is>
+      </c>
+      <c r="S43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">199
+</t>
+        </is>
+      </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t>777</t>
+          <t xml:space="preserve">555
+</t>
         </is>
       </c>
       <c r="U43" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">088
+          <t xml:space="preserve">16868
 </t>
         </is>
       </c>
       <c r="V43" s="3" t="n"/>
-      <c r="W43" s="3" t="n"/>
-      <c r="X43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">217
-</t>
-        </is>
-      </c>
+      <c r="W43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="X43" s="3" t="n"/>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t>377</t>
-        </is>
-      </c>
-      <c r="Z43" s="3" t="n"/>
+          <t xml:space="preserve">236
+</t>
+        </is>
+      </c>
+      <c r="Z43" s="3" t="inlineStr">
+        <is>
+          <t>577</t>
+        </is>
+      </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
           <t>30</t>
@@ -6747,26 +6386,32 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">24
+60292929572
 </t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
-        </is>
-      </c>
-      <c r="F44" s="3" t="n"/>
-      <c r="G44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">925
+          <t xml:space="preserve">773
+</t>
+        </is>
+      </c>
+      <c r="F44" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">577
+</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">55
 </t>
         </is>
       </c>
@@ -6776,105 +6421,92 @@
 </t>
         </is>
       </c>
-      <c r="I44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">614
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1642
+24749414
 </t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="L44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">902
+          <t xml:space="preserve">77
+</t>
+        </is>
+      </c>
+      <c r="L44" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">878
 </t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">796
+          <t xml:space="preserve">42
 </t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">99
+118
 </t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4055
-</t>
-        </is>
-      </c>
-      <c r="P44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">185
-</t>
-        </is>
-      </c>
-      <c r="Q44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">291
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">727
+</t>
+        </is>
+      </c>
+      <c r="P44" s="3" t="n"/>
+      <c r="Q44" s="3" t="n"/>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">808
+          <t xml:space="preserve">71
 </t>
         </is>
       </c>
       <c r="S44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">808
+          <t xml:space="preserve">728
 </t>
         </is>
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">660
-</t>
-        </is>
-      </c>
-      <c r="U44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5566
-</t>
-        </is>
-      </c>
-      <c r="V44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">210
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">7773
+</t>
+        </is>
+      </c>
+      <c r="U44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">028
+</t>
+        </is>
+      </c>
+      <c r="V44" s="3" t="n"/>
       <c r="W44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">985
 </t>
         </is>
       </c>
       <c r="X44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="Y44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">836
+          <t xml:space="preserve">47
 </t>
         </is>
       </c>
@@ -6894,13 +6526,12 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3679
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">397
 </t>
         </is>
       </c>
@@ -6912,13 +6543,14 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>451</t>
+          <t xml:space="preserve">1791287
+</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
@@ -6929,19 +6561,19 @@
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">52
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">51
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -6953,11 +6585,17 @@
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
-        </is>
-      </c>
-      <c r="N45" s="3" t="n"/>
+          <t xml:space="preserve">79
+</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4
+1
+</t>
+        </is>
+      </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">811
@@ -6966,55 +6604,61 @@
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t>341</t>
+          <t>521</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">251
 </t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">808
+          <t xml:space="preserve">2628
 </t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">808
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">660
+          <t xml:space="preserve">6
 </t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>4638</t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">4224574
+1
 </t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
-        </is>
-      </c>
-      <c r="X45" s="3" t="n"/>
+          <t xml:space="preserve">62
+</t>
+        </is>
+      </c>
+      <c r="X45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+1
+</t>
+        </is>
+      </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">47
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
@@ -7034,84 +6678,123 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="n"/>
-      <c r="E46" s="3" t="n"/>
-      <c r="F46" s="3" t="n"/>
-      <c r="G46" s="3" t="n"/>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">269
+</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1817857
+1 1
+1
+3
+6
+</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">35
+</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">526
+</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7
+</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">159
+</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">16
 </t>
         </is>
       </c>
-      <c r="I46" s="3" t="n"/>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="K46" s="3" t="n"/>
-      <c r="L46" s="3" t="n"/>
-      <c r="M46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">146
-</t>
-        </is>
-      </c>
-      <c r="N46" s="3" t="n"/>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="P46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="n"/>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
-      <c r="R46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="R46" s="3" t="n"/>
       <c r="S46" s="3" t="n"/>
       <c r="T46" s="3" t="n"/>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
-      </c>
-      <c r="V46" s="3" t="n"/>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="V46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
       <c r="W46" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">62
+</t>
+        </is>
+      </c>
+      <c r="X46" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="X46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">111
+1
 </t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">1145
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/905/905_197311_SF.JPG_stage_digit_manipulation.xlsx
+++ b/results/05_transient_transcription_output/905/905_197311_SF.JPG_stage_digit_manipulation.xlsx
@@ -737,13 +737,13 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23898
-</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">283
+          <t xml:space="preserve">3898
+</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
@@ -753,7 +753,7 @@
 </t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">221
 </t>
@@ -761,15 +761,22 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t xml:space="preserve">125
+</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="n"/>
+          <t xml:space="preserve">125
+</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">38
+</t>
+        </is>
+      </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">55
@@ -778,24 +785,26 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="M4" s="8" t="inlineStr">
+          <t xml:space="preserve">279
+</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">168
 </t>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t>1951</t>
+      <c r="N4" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">885
+</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
@@ -806,7 +815,7 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
@@ -818,11 +827,16 @@
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
-        </is>
-      </c>
-      <c r="S4" s="3" t="n"/>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">250
+</t>
+        </is>
+      </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">851
@@ -837,7 +851,7 @@
       </c>
       <c r="V4" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8208
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
@@ -855,13 +869,13 @@
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2861
+          <t xml:space="preserve">861
 </t>
         </is>
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
+          <t xml:space="preserve">93
 </t>
         </is>
       </c>
@@ -880,13 +894,13 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14286
+          <t xml:space="preserve">4386
 </t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
@@ -898,39 +912,49 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">110
-</t>
-        </is>
-      </c>
-      <c r="H5" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">258
-</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="n"/>
+          <t xml:space="preserve">285
+</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">060
+</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2214 4
+</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">35
 </t>
         </is>
       </c>
-      <c r="K5" s="8" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">223
 </t>
         </is>
       </c>
-      <c r="L5" s="3" t="n"/>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">183
+</t>
+        </is>
+      </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">876
 </t>
         </is>
       </c>
@@ -942,42 +966,43 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1931
-</t>
-        </is>
-      </c>
-      <c r="P5" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">694
-</t>
-        </is>
-      </c>
-      <c r="Q5" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2248
-</t>
-        </is>
-      </c>
-      <c r="R5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">013
-</t>
-        </is>
-      </c>
-      <c r="S5" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11012
+          <t xml:space="preserve">931
+</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">248
+</t>
+        </is>
+      </c>
+      <c r="R5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">213
+</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">233
 </t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t>131</t>
+          <t xml:space="preserve">843
+</t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">811
 </t>
         </is>
       </c>
@@ -989,7 +1014,8 @@
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t xml:space="preserve">172
+</t>
         </is>
       </c>
       <c r="X5" s="3" t="inlineStr">
@@ -1004,12 +1030,7 @@
 </t>
         </is>
       </c>
-      <c r="Z5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
+      <c r="Z5" s="3" t="n"/>
       <c r="AA5" s="3" t="inlineStr">
         <is>
           <t>2</t>
@@ -1030,21 +1051,21 @@
         </is>
       </c>
       <c r="D6" s="3" t="n"/>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">270
-</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">261
-</t>
-        </is>
-      </c>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">269
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">229
+</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
@@ -1056,32 +1077,37 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">098
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">157
 </t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="n"/>
+          <t xml:space="preserve">008
+</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
-        </is>
-      </c>
-      <c r="N6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="N6" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">651
 </t>
         </is>
       </c>
@@ -1091,16 +1117,21 @@
 </t>
         </is>
       </c>
-      <c r="P6" s="3" t="n"/>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">268
 </t>
         </is>
       </c>
-      <c r="R6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">203
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
@@ -1112,7 +1143,8 @@
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t>64</t>
+          <t xml:space="preserve">690
+</t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
@@ -1127,13 +1159,13 @@
 </t>
         </is>
       </c>
-      <c r="W6" s="8" t="inlineStr">
+      <c r="W6" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">192
 </t>
         </is>
       </c>
-      <c r="X6" s="8" t="inlineStr">
+      <c r="X6" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">216
 </t>
@@ -1147,7 +1179,7 @@
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -1164,10 +1196,15 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C7" s="3" t="n"/>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">282
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2744
+</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">542
 </t>
         </is>
       </c>
@@ -1177,16 +1214,14 @@
 </t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">202
-</t>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>615</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
@@ -1201,28 +1236,28 @@
 </t>
         </is>
       </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">48
-</t>
-        </is>
-      </c>
+      <c r="J7" s="3" t="n"/>
       <c r="K7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">02
 </t>
         </is>
       </c>
-      <c r="L7" s="3" t="n"/>
-      <c r="M7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">279
-</t>
-        </is>
-      </c>
-      <c r="N7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">698
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
@@ -1238,28 +1273,43 @@
 </t>
         </is>
       </c>
-      <c r="Q7" s="3" t="n"/>
+      <c r="Q7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">882
+</t>
+        </is>
+      </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">227
 </t>
         </is>
       </c>
-      <c r="S7" s="3" t="n"/>
+      <c r="S7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">249
+</t>
+        </is>
+      </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">688
-</t>
-        </is>
-      </c>
-      <c r="U7" s="3" t="n"/>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
       <c r="V7" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">208
 </t>
         </is>
       </c>
-      <c r="W7" s="8" t="inlineStr">
+      <c r="W7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">196
 </t>
@@ -1279,7 +1329,7 @@
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -1296,7 +1346,12 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C8" s="3" t="n"/>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12602
+</t>
+        </is>
+      </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">284
@@ -1309,15 +1364,15 @@
 </t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">821
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">271
 </t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
@@ -1335,13 +1390,13 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
+          <t xml:space="preserve">39
 </t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">41
 </t>
         </is>
       </c>
@@ -1359,7 +1414,7 @@
       </c>
       <c r="N8" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">082
+          <t xml:space="preserve">692
 </t>
         </is>
       </c>
@@ -1369,23 +1424,33 @@
 </t>
         </is>
       </c>
-      <c r="P8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">212
-</t>
-        </is>
-      </c>
-      <c r="Q8" s="3" t="n"/>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">245
+</t>
+        </is>
+      </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">228
 </t>
         </is>
       </c>
-      <c r="S8" s="3" t="n"/>
+      <c r="S8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">268
+</t>
+        </is>
+      </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">881
+          <t xml:space="preserve">871
 </t>
         </is>
       </c>
@@ -1397,7 +1462,7 @@
       </c>
       <c r="V8" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">096
+          <t xml:space="preserve">296
 </t>
         </is>
       </c>
@@ -1438,30 +1503,51 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C9" s="3" t="n"/>
-      <c r="D9" s="3" t="n"/>
-      <c r="E9" s="3" t="n"/>
-      <c r="F9" s="3" t="n"/>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1404
+</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">820
+</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8291
+</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1124
+</t>
+        </is>
+      </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2598
+          <t xml:space="preserve">391
 </t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>7221</t>
+          <t xml:space="preserve">617
+</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">2218
 </t>
         </is>
       </c>
@@ -1473,7 +1559,8 @@
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>310</t>
+          <t xml:space="preserve">818
+</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
@@ -1482,21 +1569,42 @@
 </t>
         </is>
       </c>
-      <c r="N9" s="3" t="n"/>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2123
+</t>
+        </is>
+      </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">342201
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="Q9" s="3" t="n"/>
-      <c r="R9" s="3" t="n"/>
-      <c r="S9" s="3" t="n"/>
+          <t xml:space="preserve">94
+</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1271
+</t>
+        </is>
+      </c>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1109
+</t>
+        </is>
+      </c>
+      <c r="S9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4124
+</t>
+        </is>
+      </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">3842
@@ -1505,21 +1613,31 @@
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19385
-</t>
-        </is>
-      </c>
-      <c r="V9" s="3" t="n"/>
+          <t xml:space="preserve">0285
+</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9289
+</t>
+        </is>
+      </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9271031
-</t>
-        </is>
-      </c>
-      <c r="X9" s="3" t="n"/>
+          <t xml:space="preserve">127
+</t>
+        </is>
+      </c>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11201
+</t>
+        </is>
+      </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194451
+          <t xml:space="preserve">94451
 </t>
         </is>
       </c>
@@ -1548,71 +1666,135 @@
 </t>
         </is>
       </c>
-      <c r="D10" s="3" t="n"/>
-      <c r="E10" s="3" t="n"/>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">284
+</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">825
-</t>
-        </is>
-      </c>
-      <c r="G10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">135
-</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="n"/>
-      <c r="J10" s="3" t="n"/>
-      <c r="K10" s="3" t="n"/>
+          <t xml:space="preserve">229
+</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111 8
+</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">821
+</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>466</t>
+        </is>
+      </c>
+      <c r="K10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1411
+</t>
+        </is>
+      </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
-      <c r="M10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">220171
-</t>
-        </is>
-      </c>
-      <c r="N10" s="3" t="n"/>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">214
+</t>
+        </is>
+      </c>
+      <c r="N10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8211
+</t>
+        </is>
+      </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9061
-</t>
-        </is>
-      </c>
-      <c r="P10" s="3" t="n"/>
-      <c r="Q10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">299
-</t>
-        </is>
-      </c>
-      <c r="R10" s="3" t="n"/>
-      <c r="S10" s="3" t="n"/>
-      <c r="T10" s="3" t="n"/>
+          <t xml:space="preserve">906
+</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">289
+</t>
+        </is>
+      </c>
+      <c r="Q10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">254
+</t>
+        </is>
+      </c>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">628
+</t>
+        </is>
+      </c>
+      <c r="S10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
+      <c r="T10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">768
+</t>
+        </is>
+      </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">77
 </t>
         </is>
       </c>
-      <c r="V10" s="3" t="n"/>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">898
+</t>
+        </is>
+      </c>
       <c r="W10" s="3" t="n"/>
-      <c r="X10" s="3" t="n"/>
-      <c r="Y10" s="3" t="n"/>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="Y10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">890
+</t>
+        </is>
+      </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">2151
 </t>
         </is>
       </c>
@@ -1631,11 +1813,11 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12996
-</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
+          <t xml:space="preserve">2996
+</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">265
 </t>
@@ -1649,7 +1831,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
@@ -1661,67 +1843,73 @@
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
-</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="J11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">241
+</t>
+        </is>
+      </c>
+      <c r="I11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">014
+</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">51
 </t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
-        </is>
-      </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t>4168</t>
+          <t xml:space="preserve">104
+</t>
+        </is>
+      </c>
+      <c r="L11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
+</t>
         </is>
       </c>
       <c r="M11" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
-</t>
-        </is>
-      </c>
-      <c r="N11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="O11" s="3" t="n"/>
+          <t xml:space="preserve">810
+</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">281
+</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">980
+</t>
+        </is>
+      </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
-        </is>
-      </c>
-      <c r="Q11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">660
+          <t xml:space="preserve">064
+</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
       <c r="S11" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
@@ -1731,29 +1919,39 @@
 </t>
         </is>
       </c>
-      <c r="U11" s="3" t="inlineStr">
+      <c r="U11" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">106
 </t>
         </is>
       </c>
-      <c r="V11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">217
-</t>
-        </is>
-      </c>
-      <c r="W11" s="3" t="inlineStr">
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">211
+</t>
+        </is>
+      </c>
+      <c r="W11" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">198
 </t>
         </is>
       </c>
-      <c r="X11" s="3" t="n"/>
-      <c r="Y11" s="3" t="n"/>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">220
+</t>
+        </is>
+      </c>
+      <c r="Y11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">845
+</t>
+        </is>
+      </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
@@ -1772,7 +1970,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23436
+          <t xml:space="preserve">03436
 </t>
         </is>
       </c>
@@ -1784,19 +1982,19 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">878
 </t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
@@ -1814,13 +2012,13 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
-        </is>
-      </c>
-      <c r="K12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">284
+          <t xml:space="preserve">84
+</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
@@ -1836,26 +2034,27 @@
 </t>
         </is>
       </c>
-      <c r="N12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">036
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1921
+          <t xml:space="preserve">921
 </t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t xml:space="preserve">166
+</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
@@ -1867,12 +2066,13 @@
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t xml:space="preserve">222
+</t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1930
+          <t xml:space="preserve">930
 </t>
         </is>
       </c>
@@ -1882,7 +2082,7 @@
 </t>
         </is>
       </c>
-      <c r="V12" s="8" t="inlineStr">
+      <c r="V12" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">215
 </t>
@@ -1890,20 +2090,25 @@
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
-        </is>
-      </c>
-      <c r="X12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">829
-</t>
-        </is>
-      </c>
-      <c r="Y12" s="3" t="n"/>
+          <t xml:space="preserve">202
+</t>
+        </is>
+      </c>
+      <c r="X12" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">129
+</t>
+        </is>
+      </c>
+      <c r="Y12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">891
+</t>
+        </is>
+      </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -1922,7 +2127,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23238
+          <t xml:space="preserve">293238
 </t>
         </is>
       </c>
@@ -1944,24 +2149,35 @@
 </t>
         </is>
       </c>
-      <c r="G13" s="3" t="n"/>
-      <c r="H13" s="3" t="n"/>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">105
+</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="J13" s="3" t="n"/>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>41</t>
+          <t xml:space="preserve">877
+</t>
         </is>
       </c>
       <c r="M13" s="8" t="inlineStr">
@@ -1972,7 +2188,7 @@
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
@@ -1982,15 +2198,10 @@
 </t>
         </is>
       </c>
-      <c r="P13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">815
-</t>
-        </is>
-      </c>
-      <c r="Q13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">164
+      <c r="P13" s="3" t="n"/>
+      <c r="Q13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
@@ -2008,7 +2219,7 @@
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">275
 </t>
         </is>
       </c>
@@ -2024,9 +2235,9 @@
 </t>
         </is>
       </c>
-      <c r="W13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">994
+      <c r="W13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
@@ -2038,13 +2249,13 @@
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">958
 </t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
@@ -2063,8 +2274,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2600
-</t>
+          <t>86004</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -2075,43 +2285,59 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>484</t>
+          <t xml:space="preserve">174
+</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="n"/>
-      <c r="H14" s="3" t="n"/>
+          <t xml:space="preserve">211
+</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">914
+</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">126
 </t>
         </is>
       </c>
-      <c r="J14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">212
-</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="n"/>
-      <c r="L14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">183
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07
+</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
-        </is>
-      </c>
-      <c r="N14" s="8" t="inlineStr">
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">189
 </t>
@@ -2125,13 +2351,13 @@
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
@@ -2149,13 +2375,13 @@
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1958
+          <t xml:space="preserve">956
 </t>
         </is>
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -2173,14 +2399,19 @@
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
-        </is>
-      </c>
-      <c r="Y14" s="3" t="n"/>
+          <t xml:space="preserve">225
+</t>
+        </is>
+      </c>
+      <c r="Y14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">90
+</t>
+        </is>
+      </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
@@ -2199,7 +2430,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23348
+          <t xml:space="preserve">9348
 </t>
         </is>
       </c>
@@ -2217,31 +2448,41 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
-        </is>
-      </c>
-      <c r="G15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">017
-</t>
-        </is>
-      </c>
-      <c r="H15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">144
-</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="n"/>
-      <c r="J15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0914
-</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="n"/>
-      <c r="L15" s="8" t="inlineStr">
+          <t xml:space="preserve">029
+</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">814
+</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">211
+</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">34
+</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">246
+</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">172
 </t>
@@ -2249,7 +2490,7 @@
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
@@ -2267,17 +2508,17 @@
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
-        </is>
-      </c>
-      <c r="R15" s="8" t="inlineStr">
+          <t xml:space="preserve">276
+</t>
+        </is>
+      </c>
+      <c r="R15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">214
 </t>
@@ -2291,26 +2532,31 @@
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1993
-</t>
-        </is>
-      </c>
-      <c r="U15" s="8" t="inlineStr">
+          <t xml:space="preserve">9953
+</t>
+        </is>
+      </c>
+      <c r="U15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">160
 </t>
         </is>
       </c>
-      <c r="V15" s="3" t="inlineStr">
+      <c r="V15" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">192
 </t>
         </is>
       </c>
-      <c r="W15" s="3" t="n"/>
+      <c r="W15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
       <c r="X15" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">060
+          <t xml:space="preserve">023
 </t>
         </is>
       </c>
@@ -2322,7 +2568,7 @@
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -2341,13 +2587,13 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101618
+          <t xml:space="preserve">02688
 </t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1348
+          <t xml:space="preserve">14281
 </t>
         </is>
       </c>
@@ -2365,13 +2611,13 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14814
+          <t xml:space="preserve">4814
 </t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">720
+          <t xml:space="preserve">1908
 </t>
         </is>
       </c>
@@ -2383,13 +2629,13 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">1149
 </t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118126
+          <t xml:space="preserve">981
 </t>
         </is>
       </c>
@@ -2399,40 +2645,63 @@
 </t>
         </is>
       </c>
-      <c r="M16" s="3" t="n"/>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">853
+</t>
+        </is>
+      </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">956
 </t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>86531</t>
+          <t xml:space="preserve">14659
+</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>619</t>
-        </is>
-      </c>
-      <c r="Q16" s="3" t="n"/>
-      <c r="R16" s="3" t="n"/>
-      <c r="S16" s="3" t="n"/>
+          <t xml:space="preserve">69
+</t>
+        </is>
+      </c>
+      <c r="Q16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">109
+</t>
+        </is>
+      </c>
+      <c r="R16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0169
+</t>
+        </is>
+      </c>
+      <c r="S16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3114
+</t>
+        </is>
+      </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t>4196</t>
+          <t xml:space="preserve">99208
+</t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133591
+          <t xml:space="preserve">358
 </t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11018
+          <t xml:space="preserve">1018
 </t>
         </is>
       </c>
@@ -2444,13 +2713,13 @@
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1097
+          <t xml:space="preserve">1087
 </t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4574
+          <t xml:space="preserve">46584
 </t>
         </is>
       </c>
@@ -2473,54 +2742,114 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C17" s="3" t="n"/>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">268
-</t>
-        </is>
-      </c>
-      <c r="E17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9113
-</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">171
-</t>
-        </is>
-      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3124
+</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">816
+</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20117
+</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="n"/>
       <c r="H17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">146
 </t>
         </is>
       </c>
-      <c r="I17" s="3" t="n"/>
-      <c r="J17" s="3" t="n"/>
-      <c r="K17" s="3" t="n"/>
-      <c r="L17" s="3" t="n"/>
-      <c r="M17" s="3" t="n"/>
-      <c r="N17" s="3" t="n"/>
-      <c r="O17" s="3" t="n"/>
-      <c r="P17" s="3" t="n"/>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30
+</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="M17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="N17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">932
+</t>
+        </is>
+      </c>
+      <c r="P17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">239
 </t>
         </is>
       </c>
-      <c r="R17" s="3" t="n"/>
-      <c r="S17" s="3" t="n"/>
-      <c r="T17" s="3" t="n"/>
-      <c r="U17" s="3" t="n"/>
+      <c r="R17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">691
+</t>
+        </is>
+      </c>
+      <c r="S17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">298
+</t>
+        </is>
+      </c>
+      <c r="T17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7884
+</t>
+        </is>
+      </c>
+      <c r="U17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70
+</t>
+        </is>
+      </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">204
@@ -2529,13 +2858,28 @@
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
-      <c r="X17" s="3" t="n"/>
-      <c r="Y17" s="3" t="n"/>
-      <c r="Z17" s="3" t="n"/>
+          <t xml:space="preserve">294
+</t>
+        </is>
+      </c>
+      <c r="X17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">219
+</t>
+        </is>
+      </c>
+      <c r="Y17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">915
+</t>
+        </is>
+      </c>
+      <c r="Z17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">211
+</t>
+        </is>
+      </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -2551,19 +2895,20 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9546
-</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">29546
+</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">771
 </t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>180</t>
+          <t xml:space="preserve">170
+</t>
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr">
@@ -2580,79 +2925,109 @@
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="n"/>
-      <c r="J18" s="3" t="n"/>
-      <c r="K18" s="3" t="n"/>
+          <t xml:space="preserve">130
+</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30
+</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">55
+</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
       <c r="L18" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">082
-</t>
-        </is>
-      </c>
-      <c r="M18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="N18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="M18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">868
+</t>
+        </is>
+      </c>
+      <c r="N18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">883
 </t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">814
-</t>
-        </is>
-      </c>
-      <c r="P18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">207
-</t>
-        </is>
-      </c>
-      <c r="Q18" s="8" t="inlineStr">
+          <t xml:space="preserve">871
+</t>
+        </is>
+      </c>
+      <c r="P18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">267
 </t>
         </is>
       </c>
-      <c r="R18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
+      <c r="R18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="S18" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
-        </is>
-      </c>
-      <c r="T18" s="3" t="n"/>
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
+      <c r="T18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165
+</t>
+        </is>
+      </c>
       <c r="U18" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
-        </is>
-      </c>
-      <c r="V18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">069
-</t>
-        </is>
-      </c>
-      <c r="W18" s="3" t="n"/>
-      <c r="X18" s="3" t="n"/>
+          <t xml:space="preserve">41487
+</t>
+        </is>
+      </c>
+      <c r="V18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">209
+</t>
+        </is>
+      </c>
+      <c r="W18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="X18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">267
+</t>
+        </is>
+      </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">835
+          <t xml:space="preserve">800
 </t>
         </is>
       </c>
@@ -2675,7 +3050,12 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C19" s="3" t="n"/>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1194
+</t>
+        </is>
+      </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">274
@@ -2688,57 +3068,72 @@
 </t>
         </is>
       </c>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">288
+</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">212
+</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">146
+</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">88
+</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">253
+</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="M19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">874
+</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">155
+</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">940
+</t>
+        </is>
+      </c>
+      <c r="P19" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">218
 </t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="n"/>
-      <c r="I19" s="3" t="n"/>
-      <c r="J19" s="3" t="n"/>
-      <c r="K19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23
-</t>
-        </is>
-      </c>
-      <c r="L19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="M19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">279
-</t>
-        </is>
-      </c>
-      <c r="N19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">089
-</t>
-        </is>
-      </c>
-      <c r="O19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">940
-</t>
-        </is>
-      </c>
-      <c r="P19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">238
@@ -2751,25 +3146,36 @@
 </t>
         </is>
       </c>
-      <c r="S19" s="3" t="inlineStr">
-        <is>
-          <t>416</t>
-        </is>
-      </c>
-      <c r="T19" s="3" t="n"/>
+      <c r="S19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">080
+</t>
+        </is>
+      </c>
+      <c r="T19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">131
+</t>
+        </is>
+      </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">79
 </t>
         </is>
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
-        </is>
-      </c>
-      <c r="W19" s="3" t="n"/>
+          <t xml:space="preserve">234
+</t>
+        </is>
+      </c>
+      <c r="W19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">199
+</t>
+        </is>
+      </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">212
@@ -2778,13 +3184,13 @@
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">736
 </t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
+          <t xml:space="preserve">71
 </t>
         </is>
       </c>
@@ -2801,14 +3207,19 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="3" t="n"/>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">534
+</t>
+        </is>
+      </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">268
 </t>
         </is>
       </c>
-      <c r="E20" s="8" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">178
 </t>
@@ -2816,20 +3227,41 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="n"/>
-      <c r="H20" s="3" t="n"/>
-      <c r="I20" s="3" t="n"/>
-      <c r="J20" s="3" t="n"/>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">91
+</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">160
+</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="J20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">219
+</t>
+        </is>
+      </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L20" s="8" t="inlineStr">
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">182
 </t>
@@ -2843,14 +3275,19 @@
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="O20" s="3" t="n"/>
+          <t xml:space="preserve">212
+</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">970
+</t>
+        </is>
+      </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
@@ -2872,10 +3309,14 @@
 </t>
         </is>
       </c>
-      <c r="T20" s="3" t="n"/>
-      <c r="U20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">231
+      <c r="T20" s="3" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="U20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">31
 </t>
         </is>
       </c>
@@ -2885,10 +3326,15 @@
 </t>
         </is>
       </c>
-      <c r="W20" s="3" t="n"/>
+      <c r="W20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">202
+</t>
+        </is>
+      </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
@@ -2900,7 +3346,7 @@
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -2919,19 +3365,20 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12848
-</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">18246
+</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">018
 </t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>170</t>
+          <t xml:space="preserve">170
+</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -2940,24 +3387,39 @@
 </t>
         </is>
       </c>
-      <c r="G21" s="3" t="n"/>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">711
+</t>
+        </is>
+      </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="n"/>
-      <c r="J21" s="3" t="n"/>
+          <t xml:space="preserve">870
+</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">282
+</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">32
+</t>
+        </is>
+      </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
       <c r="L21" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">680
 </t>
         </is>
       </c>
@@ -2967,8 +3429,18 @@
 </t>
         </is>
       </c>
-      <c r="N21" s="3" t="n"/>
-      <c r="O21" s="3" t="n"/>
+      <c r="N21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">289
+</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">940
+</t>
+        </is>
+      </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">182
@@ -2987,28 +3459,33 @@
 </t>
         </is>
       </c>
-      <c r="S21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">226
-</t>
-        </is>
-      </c>
-      <c r="T21" s="3" t="n"/>
-      <c r="U21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">262
-</t>
-        </is>
-      </c>
-      <c r="V21" s="8" t="inlineStr">
+      <c r="S21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">286
+</t>
+        </is>
+      </c>
+      <c r="T21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">911
+</t>
+        </is>
+      </c>
+      <c r="U21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="V21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">220
 </t>
         </is>
       </c>
-      <c r="W21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">206
+      <c r="W21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
@@ -3020,12 +3497,13 @@
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t>961</t>
+          <t xml:space="preserve">968
+</t>
         </is>
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
@@ -3044,7 +3522,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23392
+          <t xml:space="preserve">3392
 </t>
         </is>
       </c>
@@ -3068,47 +3546,52 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">106 2
 </t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
-        </is>
-      </c>
-      <c r="I22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">846
+</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">42
 </t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L22" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">180
 </t>
         </is>
       </c>
-      <c r="M22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">171
-</t>
-        </is>
-      </c>
-      <c r="N22" s="3" t="n"/>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">177
+</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">214
+</t>
+        </is>
+      </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">980
@@ -3117,13 +3600,14 @@
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t xml:space="preserve">251
+</t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
@@ -3140,7 +3624,7 @@
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">840
 </t>
         </is>
       </c>
@@ -3152,13 +3636,13 @@
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
-        </is>
-      </c>
-      <c r="W22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">236
+</t>
+        </is>
+      </c>
+      <c r="W22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2190
 </t>
         </is>
       </c>
@@ -3176,7 +3660,7 @@
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">87
 </t>
         </is>
       </c>
@@ -3193,36 +3677,57 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="n"/>
-      <c r="D23" s="3" t="n"/>
-      <c r="E23" s="3" t="n"/>
-      <c r="F23" s="3" t="n"/>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>364</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">216
+</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">850
+</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">121
+</t>
+        </is>
+      </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t xml:space="preserve">926
+</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">748
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11212
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1699
+          <t xml:space="preserve">1299
 </t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>661</t>
+          <t xml:space="preserve">66
+</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
@@ -3233,51 +3738,83 @@
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>8894</t>
-        </is>
-      </c>
-      <c r="N23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">98
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">818
+</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="n"/>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14691
+          <t xml:space="preserve">2691
 </t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="Q23" s="3" t="n"/>
-      <c r="R23" s="3" t="n"/>
-      <c r="S23" s="3" t="n"/>
+          <t xml:space="preserve">620
+</t>
+        </is>
+      </c>
+      <c r="Q23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">199
+</t>
+        </is>
+      </c>
+      <c r="R23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="S23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">81158
+</t>
+        </is>
+      </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3938
+          <t xml:space="preserve">2991
 </t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23992
+          <t xml:space="preserve">992
 </t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1103
-</t>
-        </is>
-      </c>
-      <c r="W23" s="3" t="n"/>
-      <c r="X23" s="3" t="n"/>
-      <c r="Y23" s="3" t="n"/>
-      <c r="Z23" s="3" t="n"/>
+          <t xml:space="preserve">1100
+</t>
+        </is>
+      </c>
+      <c r="W23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1996
+</t>
+        </is>
+      </c>
+      <c r="X23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2100
+</t>
+        </is>
+      </c>
+      <c r="Y23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4068
+</t>
+        </is>
+      </c>
+      <c r="Z23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1229
+</t>
+        </is>
+      </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -3299,126 +3836,129 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
+          <t xml:space="preserve">275
 </t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">701
 </t>
         </is>
       </c>
       <c r="F24" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">221
+</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18 051
+</t>
+        </is>
+      </c>
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
+      <c r="I24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">541
+</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">291
+</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="n"/>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">181
 </t>
         </is>
       </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">150
-</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">119
-</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27
-</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">86
-</t>
-        </is>
-      </c>
-      <c r="L24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="M24" s="3" t="inlineStr">
-        <is>
-          <t>485</t>
-        </is>
-      </c>
-      <c r="N24" s="3" t="n"/>
+      <c r="M24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">741
+</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">268
+</t>
+        </is>
+      </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>940</t>
+          <t xml:space="preserve">9381
+</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
-        </is>
-      </c>
-      <c r="Q24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">13
+</t>
+        </is>
+      </c>
+      <c r="Q24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">391
 </t>
         </is>
       </c>
       <c r="R24" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
-        </is>
-      </c>
-      <c r="S24" s="3" t="inlineStr">
+          <t xml:space="preserve">101
+</t>
+        </is>
+      </c>
+      <c r="S24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">321
+</t>
+        </is>
+      </c>
+      <c r="T24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="U24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">66
+</t>
+        </is>
+      </c>
+      <c r="V24" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">221
 </t>
         </is>
       </c>
-      <c r="T24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">825
-</t>
-        </is>
-      </c>
-      <c r="U24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">47
-</t>
-        </is>
-      </c>
-      <c r="V24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">281
-</t>
-        </is>
-      </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="X24" s="3" t="n"/>
-      <c r="Y24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7130
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">299
+</t>
+        </is>
+      </c>
+      <c r="X24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11834
+</t>
+        </is>
+      </c>
+      <c r="Y24" s="3" t="n"/>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
+          <t xml:space="preserve">45
 </t>
         </is>
       </c>
@@ -3435,101 +3975,110 @@
           <t>16</t>
         </is>
       </c>
-      <c r="C25" s="3" t="n"/>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2798
+</t>
+        </is>
+      </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">247
 </t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">79
+</t>
+        </is>
+      </c>
+      <c r="H25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">895
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
-        </is>
-      </c>
-      <c r="L25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">170
-</t>
-        </is>
-      </c>
-      <c r="M25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">167
-</t>
-        </is>
-      </c>
-      <c r="N25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">888
-</t>
+          <t xml:space="preserve">004
+</t>
+        </is>
+      </c>
+      <c r="L25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t>45</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
+          <t xml:space="preserve">940
 </t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
-        </is>
-      </c>
-      <c r="Q25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="Q25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
-      </c>
-      <c r="S25" s="3" t="n"/>
+          <t xml:space="preserve">201
+</t>
+        </is>
+      </c>
+      <c r="S25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">221
+</t>
+        </is>
+      </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">839
+          <t xml:space="preserve">825
 </t>
         </is>
       </c>
@@ -3539,33 +4088,33 @@
 </t>
         </is>
       </c>
-      <c r="V25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">206
+      <c r="V25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1920
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">63
 </t>
         </is>
       </c>
@@ -3584,119 +4133,145 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3700
+          <t xml:space="preserve">3414
 </t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">203
+</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">91
+</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">229
+</t>
+        </is>
+      </c>
+      <c r="I26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">253
+</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">37
+</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="L26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">167
 </t>
         </is>
       </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">217
-</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">101
-</t>
-        </is>
-      </c>
-      <c r="H26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">160
-</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">395
-</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="L26" s="3" t="inlineStr">
-        <is>
-          <t>1681</t>
-        </is>
-      </c>
-      <c r="M26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">611
-</t>
-        </is>
-      </c>
-      <c r="N26" s="3" t="n"/>
+      <c r="N26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">828
+</t>
+        </is>
+      </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1930
+          <t xml:space="preserve">970
 </t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
-        </is>
-      </c>
-      <c r="R26" s="3" t="n"/>
-      <c r="S26" s="3" t="n"/>
-      <c r="T26" s="3" t="n"/>
+          <t xml:space="preserve">227
+</t>
+        </is>
+      </c>
+      <c r="R26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">416
+</t>
+        </is>
+      </c>
+      <c r="S26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">246
+</t>
+        </is>
+      </c>
+      <c r="T26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">839
+</t>
+        </is>
+      </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">47
 </t>
         </is>
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
-        </is>
-      </c>
-      <c r="W26" s="3" t="n"/>
-      <c r="X26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="W26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">197
+</t>
+        </is>
+      </c>
+      <c r="X26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">836
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -3715,119 +4290,142 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14536
+          <t xml:space="preserve">3700
 </t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>518</t>
+          <t>461</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">217
+</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">101
+</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">160
+</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">35
+</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>464</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">251
+</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">930
+</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13
+</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">255
+</t>
+        </is>
+      </c>
+      <c r="R27" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">219
 </t>
         </is>
       </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">138
-</t>
-        </is>
-      </c>
-      <c r="H27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">33
-</t>
-        </is>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">53
-</t>
-        </is>
-      </c>
-      <c r="K27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">06
-</t>
-        </is>
-      </c>
-      <c r="L27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">167
-</t>
-        </is>
-      </c>
-      <c r="M27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">150
-</t>
-        </is>
-      </c>
-      <c r="N27" s="3" t="n"/>
-      <c r="O27" s="3" t="n"/>
-      <c r="P27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">31
-</t>
-        </is>
-      </c>
-      <c r="Q27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2068
-</t>
-        </is>
-      </c>
-      <c r="R27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">878
-</t>
-        </is>
-      </c>
-      <c r="S27" s="3" t="n"/>
-      <c r="T27" s="3" t="n"/>
+      <c r="S27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">287
+</t>
+        </is>
+      </c>
+      <c r="T27" s="3" t="inlineStr">
+        <is>
+          <t>6364</t>
+        </is>
+      </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">062
+          <t xml:space="preserve">909
 </t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="W27" s="3" t="n"/>
+          <t xml:space="preserve">209
+</t>
+        </is>
+      </c>
+      <c r="W27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">785
+          <t xml:space="preserve">836
 </t>
         </is>
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
@@ -3846,135 +4444,143 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23436
-</t>
-        </is>
-      </c>
-      <c r="D28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">263
-</t>
-        </is>
-      </c>
-      <c r="E28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1160
+          <t xml:space="preserve">4536
+</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">288
+</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">933
 </t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
-      <c r="M28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">167
+</t>
+        </is>
+      </c>
+      <c r="M28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">814
-</t>
-        </is>
-      </c>
-      <c r="O28" s="3" t="n"/>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">840
+</t>
+        </is>
+      </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
-      </c>
-      <c r="Q28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2920
+          <t xml:space="preserve">31
+</t>
+        </is>
+      </c>
+      <c r="Q28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
-        </is>
-      </c>
-      <c r="S28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">38116
-</t>
-        </is>
-      </c>
-      <c r="T28" s="3" t="n"/>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="S28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="T28" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
-      <c r="V28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">68
+</t>
+        </is>
+      </c>
+      <c r="V28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="X28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">264
+</t>
+        </is>
+      </c>
+      <c r="X28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">131
 </t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
+          <t xml:space="preserve">785
 </t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -3993,101 +4599,138 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17884
+          <t xml:space="preserve">3436
 </t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">584
-</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="n"/>
-      <c r="F29" s="3" t="n"/>
+          <t xml:space="preserve">265
+</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">162
+</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">214
+</t>
+        </is>
+      </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">500
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>7023</t>
-        </is>
-      </c>
-      <c r="I29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">630
+          <t xml:space="preserve">140
+</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
-        </is>
-      </c>
-      <c r="K29" s="3" t="n"/>
-      <c r="L29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">859
+          <t xml:space="preserve">48
+</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">619
+</t>
+        </is>
+      </c>
+      <c r="L29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
       <c r="N29" s="3" t="n"/>
-      <c r="O29" s="3" t="inlineStr">
-        <is>
-          <t>4545</t>
-        </is>
-      </c>
+      <c r="O29" s="3" t="n"/>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
-</t>
-        </is>
-      </c>
-      <c r="Q29" s="3" t="n"/>
-      <c r="R29" s="3" t="n"/>
-      <c r="S29" s="3" t="n"/>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="Q29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">220
+</t>
+        </is>
+      </c>
+      <c r="R29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">197
+</t>
+        </is>
+      </c>
+      <c r="S29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">816
+</t>
+        </is>
+      </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3922
-</t>
-        </is>
-      </c>
-      <c r="U29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">300
-</t>
-        </is>
-      </c>
-      <c r="V29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">815
+</t>
+        </is>
+      </c>
+      <c r="U29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">48
+</t>
+        </is>
+      </c>
+      <c r="V29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
-</t>
-        </is>
-      </c>
-      <c r="X29" s="3" t="n"/>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="X29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">209
+</t>
+        </is>
+      </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120080
-</t>
-        </is>
-      </c>
-      <c r="Z29" s="3" t="n"/>
+          <t xml:space="preserve">880
+</t>
+        </is>
+      </c>
+      <c r="Z29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
           <t>20</t>
@@ -4101,50 +4744,145 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C30" s="3" t="n"/>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1869
+</t>
+        </is>
+      </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80101
-</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="n"/>
-      <c r="F30" s="3" t="n"/>
-      <c r="G30" s="3" t="n"/>
+          <t xml:space="preserve">244
+</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">817
+</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1004
+</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">200
+</t>
+        </is>
+      </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
-        </is>
-      </c>
-      <c r="I30" s="3" t="n"/>
-      <c r="J30" s="3" t="n"/>
-      <c r="K30" s="3" t="n"/>
-      <c r="L30" s="3" t="n"/>
+          <t xml:space="preserve">7009
+</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1200
+</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1190
+</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8939
+</t>
+        </is>
+      </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101811
-</t>
-        </is>
-      </c>
-      <c r="N30" s="3" t="n"/>
-      <c r="O30" s="3" t="n"/>
-      <c r="P30" s="3" t="n"/>
-      <c r="Q30" s="3" t="n"/>
+          <t xml:space="preserve">812
+</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8 10
+</t>
+        </is>
+      </c>
+      <c r="O30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14249
+</t>
+        </is>
+      </c>
+      <c r="P30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">89
+</t>
+        </is>
+      </c>
+      <c r="Q30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1112
+</t>
+        </is>
+      </c>
       <c r="R30" s="3" t="n"/>
-      <c r="S30" s="3" t="n"/>
-      <c r="T30" s="3" t="n"/>
-      <c r="U30" s="3" t="n"/>
-      <c r="V30" s="3" t="n"/>
-      <c r="W30" s="3" t="n"/>
+      <c r="S30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">81094
+</t>
+        </is>
+      </c>
+      <c r="T30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2222
+</t>
+        </is>
+      </c>
+      <c r="U30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">909
+</t>
+        </is>
+      </c>
+      <c r="V30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1118
+</t>
+        </is>
+      </c>
+      <c r="W30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">918
+</t>
+        </is>
+      </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
-        </is>
-      </c>
-      <c r="Y30" s="3" t="n"/>
-      <c r="Z30" s="3" t="n"/>
+          <t xml:space="preserve">9998
+</t>
+        </is>
+      </c>
+      <c r="Y30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1161
+</t>
+        </is>
+      </c>
+      <c r="Z30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1200
+</t>
+        </is>
+      </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -4160,129 +4898,140 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12666
-</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>46</t>
+          <t xml:space="preserve">23577
+</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2862
+</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">163
 </t>
         </is>
       </c>
       <c r="F31" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">867
-</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">93
+          <t xml:space="preserve">215
+</t>
+        </is>
+      </c>
+      <c r="G31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11001
 </t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
-        </is>
-      </c>
-      <c r="I31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">822
+          <t xml:space="preserve">141
+</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">018
-</t>
-        </is>
-      </c>
-      <c r="K31" s="3" t="n"/>
-      <c r="L31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="M31" s="3" t="n"/>
+          <t xml:space="preserve">9 9
+</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="L31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1721
+</t>
+        </is>
+      </c>
+      <c r="M31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01208101
+</t>
+        </is>
+      </c>
       <c r="N31" s="3" t="n"/>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7920
+          <t xml:space="preserve">909
 </t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">010
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
-        </is>
-      </c>
-      <c r="R31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="S31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
+      <c r="R31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12 66
+</t>
+        </is>
+      </c>
+      <c r="S31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">784
 </t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
+          <t xml:space="preserve">611
 </t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="W31" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">841
 </t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19406
+          <t xml:space="preserve">832
 </t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">401
 </t>
         </is>
       </c>
@@ -4301,18 +5050,23 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14008
-</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="n"/>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="F32" s="8" t="inlineStr">
+          <t xml:space="preserve">2666
+</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">264
+</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">291
+</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">217
 </t>
@@ -4320,86 +5074,121 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">816
 </t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
-        </is>
-      </c>
-      <c r="I32" s="3" t="n"/>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">919
+          <t xml:space="preserve">894
+</t>
+        </is>
+      </c>
+      <c r="I32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">856
+</t>
+        </is>
+      </c>
+      <c r="J32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">014
 </t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
-</t>
-        </is>
-      </c>
-      <c r="L32" s="3" t="n"/>
-      <c r="M32" s="3" t="n"/>
+          <t xml:space="preserve">27
+</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">154
+</t>
+        </is>
+      </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="O32" s="3" t="n"/>
+          <t xml:space="preserve">129
+</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">920
+</t>
+        </is>
+      </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
-        </is>
-      </c>
-      <c r="Q32" s="3" t="n"/>
-      <c r="R32" s="3" t="n"/>
-      <c r="S32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">010
+</t>
+        </is>
+      </c>
+      <c r="Q32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="R32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="S32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2064
 </t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2794
+          <t xml:space="preserve">910
 </t>
         </is>
       </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">896
-</t>
-        </is>
-      </c>
-      <c r="W32" s="3" t="n"/>
-      <c r="X32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">175
+</t>
+        </is>
+      </c>
+      <c r="W32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">162
+</t>
+        </is>
+      </c>
+      <c r="X32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">081
 </t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">865
+          <t xml:space="preserve">940
 </t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">1820
 </t>
         </is>
       </c>
@@ -4418,105 +5207,145 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13502
-</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="n"/>
-      <c r="E33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">170
-</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">209
-</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">78
-</t>
-        </is>
-      </c>
-      <c r="H33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">256
-</t>
-        </is>
-      </c>
-      <c r="I33" s="3" t="n"/>
+          <t xml:space="preserve">14008
+</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">273
+</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">162
+</t>
+        </is>
+      </c>
+      <c r="F33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">217
+</t>
+        </is>
+      </c>
+      <c r="G33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">138
+</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">297
+          <t xml:space="preserve">241
 </t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="L33" s="3" t="n"/>
+          <t xml:space="preserve">58
+</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">171
+</t>
+        </is>
+      </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
-      <c r="N33" s="3" t="n"/>
-      <c r="O33" s="3" t="n"/>
+          <t xml:space="preserve">018
+</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="O33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">811
+</t>
+        </is>
+      </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="Q33" s="3" t="n"/>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
+      <c r="Q33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">000
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">748
+          <t xml:space="preserve">774
 </t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
       <c r="V33" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">018
-</t>
-        </is>
-      </c>
-      <c r="W33" s="3" t="n"/>
-      <c r="X33" s="3" t="n"/>
+          <t xml:space="preserve">896
+</t>
+        </is>
+      </c>
+      <c r="W33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">880
+</t>
+        </is>
+      </c>
+      <c r="X33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">127
+</t>
+        </is>
+      </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
+          <t xml:space="preserve">868
 </t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2938
+          <t xml:space="preserve">821
 </t>
         </is>
       </c>
@@ -4535,98 +5364,147 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12688
-</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="n"/>
+          <t xml:space="preserve">23502
+</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">248
+</t>
+        </is>
+      </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">209
+</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79
+</t>
+        </is>
+      </c>
+      <c r="H34" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">156
+</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">175
+</t>
+        </is>
+      </c>
+      <c r="M34" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">166
 </t>
         </is>
       </c>
-      <c r="F34" s="3" t="n"/>
-      <c r="G34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">82
-</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="n"/>
-      <c r="I34" s="3" t="n"/>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">290
-</t>
-        </is>
-      </c>
-      <c r="K34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08
-</t>
-        </is>
-      </c>
-      <c r="L34" s="3" t="n"/>
-      <c r="M34" s="3" t="n"/>
-      <c r="N34" s="3" t="n"/>
+      <c r="N34" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">800
-</t>
-        </is>
-      </c>
-      <c r="P34" s="3" t="n"/>
+          <t xml:space="preserve">918
+</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">233
 </t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">860
+          <t xml:space="preserve">748
 </t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
-        </is>
-      </c>
-      <c r="V34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
-      </c>
-      <c r="W34" s="3" t="n"/>
+          <t xml:space="preserve">78
+</t>
+        </is>
+      </c>
+      <c r="V34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">207
+</t>
+        </is>
+      </c>
+      <c r="W34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">081
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1164
-</t>
-        </is>
-      </c>
-      <c r="Z34" s="3" t="n"/>
+          <t xml:space="preserve">840
+</t>
+        </is>
+      </c>
+      <c r="Z34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
           <t>23</t>
@@ -4642,67 +5520,95 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13568
-</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="n"/>
-      <c r="E35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">160
-</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="n"/>
+          <t xml:space="preserve">2688
+</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">248
+</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">207
+</t>
+        </is>
+      </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="n"/>
+          <t xml:space="preserve">89
+</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">800
+</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">40
 </t>
         </is>
       </c>
-      <c r="L35" s="3" t="n"/>
-      <c r="M35" s="3" t="n"/>
-      <c r="N35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="O35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">790
-</t>
-        </is>
-      </c>
-      <c r="P35" s="3" t="n"/>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">068
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
@@ -4714,38 +5620,43 @@
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1602
+          <t xml:space="preserve">860
 </t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="X35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">226
-</t>
-        </is>
-      </c>
-      <c r="Y35" s="3" t="n"/>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="X35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">211
+</t>
+        </is>
+      </c>
+      <c r="Y35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">892
+</t>
+        </is>
+      </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">2441
 </t>
         </is>
       </c>
@@ -4762,100 +5673,145 @@
           <t>25</t>
         </is>
       </c>
-      <c r="C36" s="3" t="n"/>
-      <c r="D36" s="3" t="n"/>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3568
+</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">281
+</t>
+        </is>
+      </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">829
-</t>
-        </is>
-      </c>
-      <c r="F36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1071
+          <t xml:space="preserve">160
+</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">485
-</t>
-        </is>
-      </c>
-      <c r="H36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7106
+          <t xml:space="preserve">121
+</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
-</t>
-        </is>
-      </c>
-      <c r="J36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1667
-</t>
-        </is>
-      </c>
-      <c r="K36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">606
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">31
+</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">883
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="N36" s="3" t="n"/>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182980
-</t>
-        </is>
-      </c>
-      <c r="P36" s="8" t="inlineStr">
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
+      <c r="P36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165
+</t>
+        </is>
+      </c>
+      <c r="Q36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">267
+</t>
+        </is>
+      </c>
+      <c r="R36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">208
 </t>
         </is>
       </c>
-      <c r="Q36" s="3" t="n"/>
-      <c r="R36" s="3" t="n"/>
-      <c r="S36" s="3" t="n"/>
+      <c r="S36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208594
-</t>
-        </is>
-      </c>
-      <c r="U36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">342
-</t>
-        </is>
-      </c>
-      <c r="V36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">981
-</t>
-        </is>
-      </c>
-      <c r="W36" s="3" t="n"/>
-      <c r="X36" s="3" t="n"/>
-      <c r="Y36" s="3" t="n"/>
-      <c r="Z36" s="3" t="n"/>
+          <t xml:space="preserve">602
+</t>
+        </is>
+      </c>
+      <c r="U36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">139
+</t>
+        </is>
+      </c>
+      <c r="V36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
+      <c r="W36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="X36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">226
+</t>
+        </is>
+      </c>
+      <c r="Y36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">952
+</t>
+        </is>
+      </c>
+      <c r="Z36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
           <t>25</t>
@@ -4869,76 +5825,135 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C37" s="3" t="n"/>
-      <c r="D37" s="3" t="n"/>
-      <c r="E37" s="3" t="n"/>
-      <c r="F37" s="3" t="n"/>
-      <c r="G37" s="3" t="n"/>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16402
+</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16211
+</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13011
+</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">485
+</t>
+        </is>
+      </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1141
-</t>
-        </is>
-      </c>
-      <c r="I37" s="3" t="n"/>
-      <c r="J37" s="3" t="n"/>
-      <c r="K37" s="3" t="n"/>
-      <c r="L37" s="3" t="n"/>
-      <c r="M37" s="3" t="n"/>
-      <c r="N37" s="3" t="n"/>
+          <t xml:space="preserve">106
+</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">109
+</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1067
+</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16006
+</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">880
+</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">860
+</t>
+        </is>
+      </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7961
+          <t xml:space="preserve">2980
 </t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">1808
 </t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">1229
 </t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">1461
 </t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
-        </is>
-      </c>
-      <c r="T37" s="3" t="n"/>
-      <c r="U37" s="3" t="n"/>
+          <t xml:space="preserve">1008
+</t>
+        </is>
+      </c>
+      <c r="T37" s="3" t="inlineStr">
+        <is>
+          <t>6805</t>
+        </is>
+      </c>
+      <c r="U37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1942
+</t>
+        </is>
+      </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">296
+          <t xml:space="preserve">981
 </t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
-        </is>
-      </c>
-      <c r="X37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2061
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">9212
+</t>
+        </is>
+      </c>
+      <c r="X37" s="3" t="n"/>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">897
+          <t xml:space="preserve">44817
 </t>
         </is>
       </c>
@@ -4956,109 +5971,135 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">122644
-</t>
-        </is>
-      </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">254
-</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">160
-</t>
-        </is>
-      </c>
-      <c r="F38" s="3" t="n"/>
-      <c r="G38" s="3" t="n"/>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">132
+      <c r="C38" s="3" t="n"/>
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">631
+</t>
+        </is>
+      </c>
+      <c r="E38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">661
+</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">214
+</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">971
+</t>
+        </is>
+      </c>
+      <c r="H38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>925</t>
-        </is>
-      </c>
-      <c r="J38" s="3" t="n"/>
+          <t xml:space="preserve">211
+</t>
+        </is>
+      </c>
+      <c r="J38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">231
+</t>
+        </is>
+      </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="L38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="M38" s="3" t="n"/>
+          <t xml:space="preserve">4
+</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">177
+</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">154
+</t>
+        </is>
+      </c>
       <c r="N38" s="3" t="n"/>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1850
+          <t xml:space="preserve">7961
 </t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">930
+          <t xml:space="preserve">42
 </t>
         </is>
       </c>
       <c r="Q38" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
-</t>
-        </is>
-      </c>
-      <c r="R38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="R38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">117 8
 </t>
         </is>
       </c>
       <c r="S38" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">397
-</t>
-        </is>
-      </c>
-      <c r="T38" s="3" t="n"/>
-      <c r="U38" s="3" t="n"/>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
+      <c r="T38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7711
+</t>
+        </is>
+      </c>
+      <c r="U38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">464
+</t>
+        </is>
+      </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="W38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">059
-</t>
-        </is>
-      </c>
-      <c r="X38" s="3" t="inlineStr">
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="W38" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">180
 </t>
         </is>
       </c>
-      <c r="Y38" s="3" t="n"/>
-      <c r="Z38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2114
-</t>
-        </is>
-      </c>
+      <c r="X38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">086
+</t>
+        </is>
+      </c>
+      <c r="Y38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">891
+</t>
+        </is>
+      </c>
+      <c r="Z38" s="3" t="n"/>
       <c r="AA38" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -5074,13 +6115,14 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12864
+          <t xml:space="preserve">2864
 </t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>9564</t>
+          <t xml:space="preserve">256
+</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -5091,7 +6133,7 @@
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">807
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -5104,7 +6146,7 @@
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -5122,25 +6164,26 @@
       </c>
       <c r="L39" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">877
+          <t xml:space="preserve">077
 </t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="N39" s="3" t="n"/>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>8466</t>
-        </is>
-      </c>
-      <c r="P39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">885
+</t>
+        </is>
+      </c>
+      <c r="P39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
@@ -5150,15 +6193,15 @@
 </t>
         </is>
       </c>
-      <c r="R39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
+      <c r="R39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
@@ -5169,7 +6212,7 @@
         </is>
       </c>
       <c r="U39" s="3" t="n"/>
-      <c r="V39" s="8" t="inlineStr">
+      <c r="V39" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">200
 </t>
@@ -5181,19 +6224,9 @@
 </t>
         </is>
       </c>
-      <c r="X39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">210
-</t>
-        </is>
-      </c>
+      <c r="X39" s="3" t="n"/>
       <c r="Y39" s="3" t="n"/>
-      <c r="Z39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">214
-</t>
-        </is>
-      </c>
+      <c r="Z39" s="3" t="n"/>
       <c r="AA39" s="3" t="inlineStr">
         <is>
           <t>26</t>
@@ -5209,7 +6242,7 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123590
+          <t xml:space="preserve">53590
 </t>
         </is>
       </c>
@@ -5219,59 +6252,69 @@
 </t>
         </is>
       </c>
-      <c r="E40" s="8" t="inlineStr">
+      <c r="E40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">156
 </t>
         </is>
       </c>
-      <c r="F40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">162
-</t>
-        </is>
-      </c>
-      <c r="G40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">169
-</t>
-        </is>
-      </c>
+      <c r="F40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1116
+</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="n"/>
       <c r="H40" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">138
 </t>
         </is>
       </c>
-      <c r="I40" s="3" t="n"/>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">859
+</t>
+        </is>
+      </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
-</t>
-        </is>
-      </c>
-      <c r="K40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">58
+</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="n"/>
       <c r="L40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">180
 </t>
         </is>
       </c>
-      <c r="M40" s="3" t="n"/>
-      <c r="N40" s="3" t="n"/>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">762
-</t>
-        </is>
-      </c>
-      <c r="P40" s="3" t="n"/>
-      <c r="Q40" s="8" t="inlineStr">
+          <t xml:space="preserve">862
+</t>
+        </is>
+      </c>
+      <c r="P40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
+      <c r="Q40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">258
 </t>
@@ -5301,9 +6344,9 @@
 </t>
         </is>
       </c>
-      <c r="V40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">012
+      <c r="V40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
@@ -5315,12 +6358,22 @@
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
-        </is>
-      </c>
-      <c r="Y40" s="3" t="n"/>
-      <c r="Z40" s="3" t="n"/>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="Y40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">862
+</t>
+        </is>
+      </c>
+      <c r="Z40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">814
+</t>
+        </is>
+      </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
           <t>27</t>
@@ -5336,8 +6389,7 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14866
-</t>
+          <t>88664</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
@@ -5346,24 +6398,29 @@
 </t>
         </is>
       </c>
-      <c r="E41" s="3" t="n"/>
-      <c r="F41" s="3" t="n"/>
-      <c r="G41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">119
-</t>
-        </is>
-      </c>
-      <c r="H41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">146
-</t>
-        </is>
-      </c>
-      <c r="I41" s="3" t="n"/>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">221
+</t>
+        </is>
+      </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">63
+          <t xml:space="preserve">163
 </t>
         </is>
       </c>
@@ -5373,16 +6430,36 @@
 </t>
         </is>
       </c>
-      <c r="L41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">177
-</t>
-        </is>
-      </c>
-      <c r="M41" s="3" t="n"/>
-      <c r="N41" s="3" t="n"/>
-      <c r="O41" s="3" t="n"/>
-      <c r="P41" s="3" t="n"/>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">277
+</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">157
+</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">167
+</t>
+        </is>
+      </c>
+      <c r="O41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">820
+</t>
+        </is>
+      </c>
+      <c r="P41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">500
+</t>
+        </is>
+      </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">260
@@ -5401,10 +6478,15 @@
 </t>
         </is>
       </c>
-      <c r="T41" s="3" t="n"/>
+      <c r="T41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">579
+</t>
+        </is>
+      </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
@@ -5414,20 +6496,25 @@
 </t>
         </is>
       </c>
-      <c r="W41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
-</t>
-        </is>
-      </c>
+      <c r="W41" s="3" t="n"/>
       <c r="X41" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">202
 </t>
         </is>
       </c>
-      <c r="Y41" s="3" t="n"/>
-      <c r="Z41" s="3" t="n"/>
+      <c r="Y41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">734
+</t>
+        </is>
+      </c>
+      <c r="Z41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">84
+</t>
+        </is>
+      </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
           <t>28</t>
@@ -5443,7 +6530,7 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19426
+          <t xml:space="preserve">9426
 </t>
         </is>
       </c>
@@ -5453,10 +6540,15 @@
 </t>
         </is>
       </c>
-      <c r="E42" s="3" t="n"/>
-      <c r="F42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">175
+</t>
+        </is>
+      </c>
+      <c r="F42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">019
 </t>
         </is>
       </c>
@@ -5466,48 +6558,58 @@
 </t>
         </is>
       </c>
-      <c r="H42" s="3" t="inlineStr">
+      <c r="H42" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="I42" s="3" t="n"/>
-      <c r="J42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">928
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="L42" s="8" t="inlineStr">
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">180
 </t>
         </is>
       </c>
-      <c r="M42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">801
-</t>
-        </is>
-      </c>
-      <c r="N42" s="3" t="n"/>
-      <c r="O42" s="3" t="n"/>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">157
+</t>
+        </is>
+      </c>
+      <c r="N42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">160
+</t>
+        </is>
+      </c>
+      <c r="O42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">798
+</t>
+        </is>
+      </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="Q42" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">781
+          <t xml:space="preserve">841
 </t>
         </is>
       </c>
@@ -5517,19 +6619,24 @@
 </t>
         </is>
       </c>
-      <c r="S42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
+      <c r="S42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="U42" s="3" t="n"/>
+          <t xml:space="preserve">555
+</t>
+        </is>
+      </c>
+      <c r="U42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">222
@@ -5544,17 +6651,22 @@
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">897
 </t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">134
+</t>
+        </is>
+      </c>
+      <c r="Z42" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">71
 </t>
         </is>
       </c>
-      <c r="Z42" s="3" t="n"/>
       <c r="AA42" s="3" t="inlineStr">
         <is>
           <t>29</t>
@@ -5569,50 +6681,57 @@
         </is>
       </c>
       <c r="C43" s="3" t="n"/>
-      <c r="D43" s="3" t="n"/>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="F43" s="3" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="G43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">525
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">948
+</t>
+        </is>
+      </c>
+      <c r="E43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">109
+</t>
+        </is>
+      </c>
+      <c r="F43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">081
+</t>
+        </is>
+      </c>
+      <c r="G43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">697
-</t>
-        </is>
-      </c>
-      <c r="I43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">914
+</t>
+        </is>
+      </c>
+      <c r="I43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">619
 </t>
         </is>
       </c>
       <c r="J43" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">681
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">908
+          <t xml:space="preserve">902
 </t>
         </is>
       </c>
@@ -5625,32 +6744,67 @@
       <c r="N43" s="3" t="n"/>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12055
-</t>
-        </is>
-      </c>
-      <c r="P43" s="8" t="inlineStr">
+          <t xml:space="preserve">1055
+</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">195
 </t>
         </is>
       </c>
-      <c r="Q43" s="3" t="n"/>
-      <c r="R43" s="3" t="n"/>
-      <c r="S43" s="3" t="n"/>
-      <c r="T43" s="3" t="n"/>
-      <c r="U43" s="3" t="n"/>
+      <c r="Q43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">251
+</t>
+        </is>
+      </c>
+      <c r="R43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
+      <c r="S43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16 16
+</t>
+        </is>
+      </c>
+      <c r="T43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">200
+</t>
+        </is>
+      </c>
+      <c r="U43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">536
+</t>
+        </is>
+      </c>
       <c r="V43" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">048
 </t>
         </is>
       </c>
-      <c r="W43" s="3" t="n"/>
-      <c r="X43" s="3" t="n"/>
+      <c r="W43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">193
+</t>
+        </is>
+      </c>
+      <c r="X43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201 10
+</t>
+        </is>
+      </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">4 067
 </t>
         </is>
       </c>
@@ -5668,7 +6822,12 @@
           <t>31</t>
         </is>
       </c>
-      <c r="C44" s="3" t="n"/>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="D44" s="3" t="n"/>
       <c r="E44" s="3" t="n"/>
       <c r="F44" s="3" t="n"/>
@@ -5707,7 +6866,7 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23689
+          <t xml:space="preserve">3629
 </t>
         </is>
       </c>
@@ -5719,19 +6878,25 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">809
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>946</t>
-        </is>
-      </c>
-      <c r="G45" s="3" t="n"/>
+          <t xml:space="preserve">216
+</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">105
+</t>
+        </is>
+      </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
@@ -5747,12 +6912,27 @@
 </t>
         </is>
       </c>
-      <c r="K45" s="3" t="n"/>
-      <c r="L45" s="3" t="n"/>
-      <c r="M45" s="3" t="n"/>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1180
+</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15 9
+</t>
+        </is>
+      </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
@@ -5764,29 +6944,64 @@
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">821
+          <t xml:space="preserve">251
 </t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">802
-</t>
-        </is>
-      </c>
-      <c r="S45" s="3" t="n"/>
-      <c r="T45" s="3" t="n"/>
-      <c r="U45" s="3" t="n"/>
-      <c r="V45" s="3" t="n"/>
-      <c r="W45" s="3" t="n"/>
-      <c r="X45" s="3" t="n"/>
-      <c r="Y45" s="3" t="n"/>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
+      <c r="S45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
+      <c r="T45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">660
+</t>
+        </is>
+      </c>
+      <c r="U45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
+      <c r="V45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">210
+</t>
+        </is>
+      </c>
+      <c r="W45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="X45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">202
+</t>
+        </is>
+      </c>
+      <c r="Y45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">47
+</t>
+        </is>
+      </c>
       <c r="Z45" s="3" t="n"/>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -5802,47 +7017,122 @@
         </is>
       </c>
       <c r="C46" s="3" t="n"/>
-      <c r="D46" s="3" t="n"/>
-      <c r="E46" s="3" t="n"/>
-      <c r="F46" s="3" t="n"/>
-      <c r="G46" s="3" t="n"/>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8
+</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
-</t>
-        </is>
-      </c>
-      <c r="I46" s="3" t="n"/>
-      <c r="J46" s="3" t="n"/>
-      <c r="K46" s="3" t="n"/>
-      <c r="L46" s="3" t="n"/>
-      <c r="M46" s="3" t="n"/>
-      <c r="N46" s="3" t="n"/>
-      <c r="O46" s="3" t="n"/>
-      <c r="P46" s="3" t="n"/>
+          <t xml:space="preserve">014
+</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4
+</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">48
+</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">159
+</t>
+        </is>
+      </c>
+      <c r="N46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4107
+</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">86
+</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="R46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">285
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">4
+</t>
+        </is>
+      </c>
+      <c r="R46" s="3" t="n"/>
       <c r="S46" s="3" t="n"/>
-      <c r="T46" s="3" t="n"/>
-      <c r="U46" s="3" t="n"/>
-      <c r="V46" s="3" t="n"/>
-      <c r="W46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">110
-</t>
-        </is>
-      </c>
-      <c r="X46" s="3" t="n"/>
+      <c r="T46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4
+</t>
+        </is>
+      </c>
+      <c r="U46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8
+</t>
+        </is>
+      </c>
+      <c r="V46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8
+</t>
+        </is>
+      </c>
+      <c r="W46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="X46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4
+</t>
+        </is>
+      </c>
       <c r="Y46" s="3" t="n"/>
       <c r="Z46" s="3" t="n"/>
       <c r="AA46" s="3" t="inlineStr">

--- a/results/05_transient_transcription_output/905/905_197311_SF.JPG_stage_digit_manipulation.xlsx
+++ b/results/05_transient_transcription_output/905/905_197311_SF.JPG_stage_digit_manipulation.xlsx
@@ -743,11 +743,11 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
-</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="inlineStr">
+          <t xml:space="preserve">883
+</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">158
 </t>
@@ -761,16 +761,16 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">825
+</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">125
 </t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">125
-</t>
-        </is>
-      </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">38
@@ -785,13 +785,13 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
@@ -815,7 +815,7 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -831,7 +831,7 @@
 </t>
         </is>
       </c>
-      <c r="S4" s="3" t="inlineStr">
+      <c r="S4" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">250
 </t>
@@ -849,9 +849,9 @@
 </t>
         </is>
       </c>
-      <c r="V4" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">203
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">803
 </t>
         </is>
       </c>
@@ -875,8 +875,7 @@
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
-</t>
+          <t>336</t>
         </is>
       </c>
       <c r="AA4" s="3" t="inlineStr">
@@ -894,14 +893,13 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4386
+          <t xml:space="preserve">94326
 </t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>49</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -918,13 +916,13 @@
       </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">060
-</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2214 4
+          <t xml:space="preserve">2150
+</t>
+        </is>
+      </c>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
@@ -940,7 +938,7 @@
 </t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="K5" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">223
 </t>
@@ -952,9 +950,9 @@
 </t>
         </is>
       </c>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">876
+      <c r="M5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
@@ -966,7 +964,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">931
+          <t xml:space="preserve">981
 </t>
         </is>
       </c>
@@ -982,7 +980,7 @@
 </t>
         </is>
       </c>
-      <c r="R5" s="8" t="inlineStr">
+      <c r="R5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">213
 </t>
@@ -996,7 +994,7 @@
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">843
+          <t xml:space="preserve">743
 </t>
         </is>
       </c>
@@ -1089,7 +1087,7 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">008
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
@@ -1101,22 +1099,17 @@
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="N6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">651
-</t>
-        </is>
-      </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">920
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">164
+</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">281
+</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="n"/>
       <c r="P6" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">16
@@ -1198,13 +1191,13 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2744
+          <t xml:space="preserve">3844
 </t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">542
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
@@ -1216,12 +1209,14 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>615</t>
+          <t xml:space="preserve">222
+</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t xml:space="preserve">120
+</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
@@ -1236,7 +1231,11 @@
 </t>
         </is>
       </c>
-      <c r="J7" s="3" t="n"/>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">02
@@ -1257,14 +1256,13 @@
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">898
-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
@@ -1273,9 +1271,9 @@
 </t>
         </is>
       </c>
-      <c r="Q7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">882
+      <c r="Q7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">273
 </t>
         </is>
       </c>
@@ -1293,7 +1291,7 @@
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">687
 </t>
         </is>
       </c>
@@ -1303,7 +1301,7 @@
 </t>
         </is>
       </c>
-      <c r="V7" s="8" t="inlineStr">
+      <c r="V7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">208
 </t>
@@ -1348,7 +1346,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12602
+          <t xml:space="preserve">2602
 </t>
         </is>
       </c>
@@ -1364,9 +1362,9 @@
 </t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">271
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
@@ -1390,79 +1388,79 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">33
+</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">41
+</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="N8" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">672
+</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">882
+</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">245
+</t>
+        </is>
+      </c>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">268
+</t>
+        </is>
+      </c>
+      <c r="T8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">871
+</t>
+        </is>
+      </c>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">39
 </t>
         </is>
       </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">41
-</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">170
-</t>
-        </is>
-      </c>
-      <c r="M8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="N8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">692
-</t>
-        </is>
-      </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">882
-</t>
-        </is>
-      </c>
-      <c r="P8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="Q8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">245
-</t>
-        </is>
-      </c>
-      <c r="R8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
-      </c>
-      <c r="S8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">268
-</t>
-        </is>
-      </c>
-      <c r="T8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">871
-</t>
-        </is>
-      </c>
-      <c r="U8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">39
-</t>
-        </is>
-      </c>
-      <c r="V8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">296
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
@@ -1505,37 +1503,36 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1404
-</t>
+          <t>34405</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">18248
 </t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8291
+          <t xml:space="preserve">291
 </t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1124
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">391
+          <t xml:space="preserve">991
 </t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">617
+          <t xml:space="preserve">618
 </t>
         </is>
       </c>
@@ -1547,19 +1544,19 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2218
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
+          <t xml:space="preserve">814
 </t>
         </is>
       </c>
@@ -1571,13 +1568,13 @@
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2123
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
@@ -1595,16 +1592,11 @@
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1109
-</t>
-        </is>
-      </c>
-      <c r="S9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4124
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">0912
+</t>
+        </is>
+      </c>
+      <c r="S9" s="3" t="n"/>
       <c r="T9" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">3842
@@ -1613,13 +1605,13 @@
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0285
+          <t xml:space="preserve">385
 </t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9289
+          <t xml:space="preserve">989
 </t>
         </is>
       </c>
@@ -1631,19 +1623,19 @@
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11201
+          <t xml:space="preserve">1628
 </t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94451
+          <t xml:space="preserve">4458
 </t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">1228
 </t>
         </is>
       </c>
@@ -1666,9 +1658,9 @@
 </t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">284
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">891
 </t>
         </is>
       </c>
@@ -1680,23 +1672,21 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>85</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111 8
-</t>
-        </is>
-      </c>
-      <c r="H10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
+          <t>468</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">135
+</t>
+        </is>
+      </c>
+      <c r="I10" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">821
 </t>
@@ -1704,30 +1694,30 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>466</t>
-        </is>
-      </c>
-      <c r="K10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1411
+          <t xml:space="preserve">146
+</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>43</t>
         </is>
       </c>
       <c r="N10" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8211
+          <t xml:space="preserve">6878
 </t>
         </is>
       </c>
@@ -1739,25 +1729,25 @@
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
-</t>
-        </is>
-      </c>
-      <c r="Q10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">254
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">628
-</t>
-        </is>
-      </c>
-      <c r="S10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">221
+</t>
+        </is>
+      </c>
+      <c r="S10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
@@ -1773,9 +1763,9 @@
 </t>
         </is>
       </c>
-      <c r="V10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">898
+      <c r="V10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">981
 </t>
         </is>
       </c>
@@ -1794,7 +1784,7 @@
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2151
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -1825,62 +1815,60 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">868
 </t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
-</t>
-        </is>
-      </c>
-      <c r="H11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">241
-</t>
-        </is>
-      </c>
-      <c r="I11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">014
-</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">51
+          <t>911</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">145
+</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="J11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311
 </t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
-        </is>
-      </c>
-      <c r="L11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192
-</t>
-        </is>
-      </c>
-      <c r="M11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">810
+          <t xml:space="preserve">04
+</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
-</t>
+          <t>414</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
@@ -1891,7 +1879,7 @@
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">064
+          <t xml:space="preserve">084
 </t>
         </is>
       </c>
@@ -1901,15 +1889,15 @@
 </t>
         </is>
       </c>
-      <c r="R11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">205
+      <c r="R11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">163
 </t>
         </is>
       </c>
       <c r="S11" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
@@ -1927,7 +1915,7 @@
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
@@ -1939,7 +1927,7 @@
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
@@ -1970,7 +1958,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03436
+          <t xml:space="preserve">3436
 </t>
         </is>
       </c>
@@ -1982,13 +1970,13 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">878
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
@@ -2018,7 +2006,7 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
@@ -2042,19 +2030,19 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
+          <t xml:space="preserve">926
 </t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
@@ -2066,13 +2054,12 @@
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>086</t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">930
+          <t xml:space="preserve">9230
 </t>
         </is>
       </c>
@@ -2094,9 +2081,9 @@
 </t>
         </is>
       </c>
-      <c r="X12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">129
+      <c r="X12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
@@ -2108,7 +2095,7 @@
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -2127,7 +2114,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293238
+          <t xml:space="preserve">23238
 </t>
         </is>
       </c>
@@ -2139,7 +2126,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">870
 </t>
         </is>
       </c>
@@ -2170,17 +2157,17 @@
       <c r="J13" s="3" t="n"/>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">877
-</t>
-        </is>
-      </c>
-      <c r="M13" s="8" t="inlineStr">
+          <t xml:space="preserve">177
+</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">169
 </t>
@@ -2188,16 +2175,11 @@
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
-      <c r="O13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">922
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">138
+</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="n"/>
       <c r="P13" s="3" t="n"/>
       <c r="Q13" s="3" t="inlineStr">
         <is>
@@ -2219,7 +2201,7 @@
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
@@ -2229,7 +2211,7 @@
 </t>
         </is>
       </c>
-      <c r="V13" s="8" t="inlineStr">
+      <c r="V13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">198
 </t>
@@ -2237,11 +2219,11 @@
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
-      <c r="X13" s="3" t="inlineStr">
+          <t xml:space="preserve">294
+</t>
+        </is>
+      </c>
+      <c r="X13" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">222
 </t>
@@ -2274,7 +2256,8 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>86004</t>
+          <t xml:space="preserve">2600
+</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -2297,13 +2280,13 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">914
+          <t xml:space="preserve">984
 </t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
@@ -2313,9 +2296,9 @@
 </t>
         </is>
       </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">182
+      <c r="J14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
@@ -2327,17 +2310,17 @@
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="N14" s="3" t="inlineStr">
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="N14" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">189
 </t>
@@ -2351,7 +2334,7 @@
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -2381,7 +2364,7 @@
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
@@ -2405,7 +2388,7 @@
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">970
 </t>
         </is>
       </c>
@@ -2430,7 +2413,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9348
+          <t xml:space="preserve">2348
 </t>
         </is>
       </c>
@@ -2448,25 +2431,25 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">029
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">18 7
 </t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">814
+          <t xml:space="preserve">1 44 1
 </t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -2490,7 +2473,7 @@
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
@@ -2532,7 +2515,7 @@
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9953
+          <t xml:space="preserve">593
 </t>
         </is>
       </c>
@@ -2542,7 +2525,7 @@
 </t>
         </is>
       </c>
-      <c r="V15" s="8" t="inlineStr">
+      <c r="V15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">192
 </t>
@@ -2554,15 +2537,15 @@
 </t>
         </is>
       </c>
-      <c r="X15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">023
+      <c r="X15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
@@ -2587,13 +2570,13 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02688
+          <t xml:space="preserve">03618
 </t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14281
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
@@ -2611,13 +2594,13 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4814
+          <t xml:space="preserve">24814
 </t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1908
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
@@ -2627,40 +2610,33 @@
 </t>
         </is>
       </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1149
-</t>
-        </is>
-      </c>
+      <c r="J16" s="3" t="n"/>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">981
+          <t xml:space="preserve">989
 </t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
-</t>
+          <t>688</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">853
+          <t xml:space="preserve">833
 </t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">956
+          <t xml:space="preserve">950
 </t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14659
-</t>
+          <t>659</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
@@ -2671,55 +2647,53 @@
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
+      <c r="R16" s="3" t="inlineStr">
+        <is>
+          <t>71603</t>
+        </is>
+      </c>
+      <c r="S16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11 29
+</t>
+        </is>
+      </c>
+      <c r="T16" s="3" t="inlineStr">
+        <is>
+          <t>415</t>
+        </is>
+      </c>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">831
+</t>
+        </is>
+      </c>
+      <c r="V16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1018
+</t>
+        </is>
+      </c>
+      <c r="W16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">869
+</t>
+        </is>
+      </c>
+      <c r="X16" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">109
 </t>
         </is>
       </c>
-      <c r="R16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0169
-</t>
-        </is>
-      </c>
-      <c r="S16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3114
-</t>
-        </is>
-      </c>
-      <c r="T16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">99208
-</t>
-        </is>
-      </c>
-      <c r="U16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">358
-</t>
-        </is>
-      </c>
-      <c r="V16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1018
-</t>
-        </is>
-      </c>
-      <c r="W16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">969
-</t>
-        </is>
-      </c>
-      <c r="X16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1087
-</t>
-        </is>
-      </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46584
+          <t xml:space="preserve">4584
 </t>
         </is>
       </c>
@@ -2750,19 +2724,19 @@
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">816
+          <t xml:space="preserve">601
 </t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
-        </is>
-      </c>
-      <c r="F17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20117
+          <t xml:space="preserve">171
+</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
@@ -2775,7 +2749,7 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>4816</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -2786,7 +2760,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -2796,15 +2770,15 @@
 </t>
         </is>
       </c>
-      <c r="M17" s="8" t="inlineStr">
+      <c r="M17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">178
 </t>
         </is>
       </c>
-      <c r="N17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
@@ -2814,9 +2788,9 @@
 </t>
         </is>
       </c>
-      <c r="P17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">111
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
@@ -2840,7 +2814,7 @@
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7884
+          <t xml:space="preserve">1887
 </t>
         </is>
       </c>
@@ -2856,7 +2830,7 @@
 </t>
         </is>
       </c>
-      <c r="W17" s="3" t="inlineStr">
+      <c r="W17" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">294
 </t>
@@ -2870,13 +2844,13 @@
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">915
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -2895,13 +2869,13 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29546
-</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">771
+          <t xml:space="preserve">2546
+</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">277
 </t>
         </is>
       </c>
@@ -2911,129 +2885,121 @@
 </t>
         </is>
       </c>
-      <c r="F18" s="8" t="inlineStr">
+      <c r="F18" s="3" t="n"/>
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">867
+</t>
+        </is>
+      </c>
+      <c r="H18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">150
+</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>506</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08
+</t>
+        </is>
+      </c>
+      <c r="L18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">183
+</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">811
+</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">207
+</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">267
+</t>
+        </is>
+      </c>
+      <c r="R18" s="3" t="inlineStr">
+        <is>
+          <t>8491</t>
+        </is>
+      </c>
+      <c r="S18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">293
+</t>
+        </is>
+      </c>
+      <c r="T18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1665
+</t>
+        </is>
+      </c>
+      <c r="U18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">418
+</t>
+        </is>
+      </c>
+      <c r="V18" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">209
 </t>
         </is>
       </c>
-      <c r="G18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">167
-</t>
-        </is>
-      </c>
-      <c r="H18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">130
-</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30
-</t>
-        </is>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">55
-</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">108
-</t>
-        </is>
-      </c>
-      <c r="L18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
-      <c r="M18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">868
-</t>
-        </is>
-      </c>
-      <c r="N18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">883
-</t>
-        </is>
-      </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">871
-</t>
-        </is>
-      </c>
-      <c r="P18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="Q18" s="3" t="inlineStr">
+      <c r="W18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="X18" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">267
 </t>
         </is>
       </c>
-      <c r="R18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="S18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
-      </c>
-      <c r="T18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">165
-</t>
-        </is>
-      </c>
-      <c r="U18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">41487
-</t>
-        </is>
-      </c>
-      <c r="V18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">209
-</t>
-        </is>
-      </c>
-      <c r="W18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="X18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">267
-</t>
-        </is>
-      </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">800
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">41
 </t>
         </is>
       </c>
@@ -3052,7 +3018,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1194
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
@@ -3070,118 +3036,118 @@
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">088
 </t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">88
+</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">33
+</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23
+</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">274
+</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">135
+</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">940
+</t>
+        </is>
+      </c>
+      <c r="P19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">881
+</t>
+        </is>
+      </c>
+      <c r="Q19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">238
+</t>
+        </is>
+      </c>
+      <c r="R19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">202
+</t>
+        </is>
+      </c>
+      <c r="S19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="T19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">131
+</t>
+        </is>
+      </c>
+      <c r="U19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">89
+</t>
+        </is>
+      </c>
+      <c r="V19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">234
+</t>
+        </is>
+      </c>
+      <c r="W19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">199
+</t>
+        </is>
+      </c>
+      <c r="X19" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">212
 </t>
         </is>
       </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">146
-</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="K19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">253
-</t>
-        </is>
-      </c>
-      <c r="L19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="M19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">874
-</t>
-        </is>
-      </c>
-      <c r="N19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">155
-</t>
-        </is>
-      </c>
-      <c r="O19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">940
-</t>
-        </is>
-      </c>
-      <c r="P19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="Q19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
-      <c r="R19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">202
-</t>
-        </is>
-      </c>
-      <c r="S19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">080
-</t>
-        </is>
-      </c>
-      <c r="T19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">131
-</t>
-        </is>
-      </c>
-      <c r="U19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">79
-</t>
-        </is>
-      </c>
-      <c r="V19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">234
-</t>
-        </is>
-      </c>
-      <c r="W19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
-      <c r="X19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">212
-</t>
-        </is>
-      </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">736
@@ -3190,7 +3156,7 @@
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
@@ -3207,12 +3173,7 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">534
-</t>
-        </is>
-      </c>
+      <c r="C20" s="3" t="n"/>
       <c r="D20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">268
@@ -3225,15 +3186,10 @@
 </t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
+      <c r="F20" s="3" t="n"/>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
@@ -3249,9 +3205,9 @@
 </t>
         </is>
       </c>
-      <c r="J20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">219
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">911
 </t>
         </is>
       </c>
@@ -3263,8 +3219,7 @@
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>491</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
@@ -3275,7 +3230,7 @@
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
@@ -3303,17 +3258,13 @@
 </t>
         </is>
       </c>
-      <c r="S20" s="8" t="inlineStr">
+      <c r="S20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">247
 </t>
         </is>
       </c>
-      <c r="T20" s="3" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
-      </c>
+      <c r="T20" s="3" t="n"/>
       <c r="U20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">31
@@ -3365,13 +3316,13 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18246
+          <t xml:space="preserve">12546
 </t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">018
+          <t xml:space="preserve">881
 </t>
         </is>
       </c>
@@ -3387,21 +3338,21 @@
 </t>
         </is>
       </c>
-      <c r="G21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">711
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
+          <t xml:space="preserve">840
 </t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
@@ -3413,13 +3364,13 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
-        </is>
-      </c>
-      <c r="L21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">680
+          <t xml:space="preserve">235
+</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
@@ -3431,7 +3382,7 @@
       </c>
       <c r="N21" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
@@ -3467,13 +3418,13 @@
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">911
+          <t xml:space="preserve">961
 </t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -3546,13 +3497,13 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106 2
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">846
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
@@ -3564,7 +3515,7 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
@@ -3588,13 +3539,13 @@
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">970
 </t>
         </is>
       </c>
@@ -3616,7 +3567,7 @@
 </t>
         </is>
       </c>
-      <c r="S22" s="8" t="inlineStr">
+      <c r="S22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">236
 </t>
@@ -3624,7 +3575,7 @@
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
@@ -3636,13 +3587,13 @@
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
-        </is>
-      </c>
-      <c r="W22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2190
+          <t xml:space="preserve">231
+</t>
+        </is>
+      </c>
+      <c r="W22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
@@ -3660,7 +3611,7 @@
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -3677,15 +3628,10 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>364</t>
-        </is>
-      </c>
+      <c r="C23" s="3" t="n"/>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>76</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -3696,7 +3642,7 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
@@ -3720,39 +3666,36 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1299
+          <t xml:space="preserve">1290
 </t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">606
 </t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">904
-</t>
+          <t>9076</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
+          <t xml:space="preserve">812
 </t>
         </is>
       </c>
       <c r="N23" s="3" t="n"/>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2691
-</t>
+          <t>469</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">620
-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
@@ -3763,7 +3706,7 @@
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
@@ -3775,46 +3718,40 @@
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2991
+          <t xml:space="preserve">3931
 </t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">992
+          <t xml:space="preserve">932
 </t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1100
+          <t xml:space="preserve">1103
 </t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1996
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2100
-</t>
+          <t>7713</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4068
-</t>
-        </is>
-      </c>
-      <c r="Z23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1229
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">416
+</t>
+        </is>
+      </c>
+      <c r="Z23" s="3" t="n"/>
       <c r="AA23" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -3830,7 +3767,7 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23097
+          <t xml:space="preserve">3097
 </t>
         </is>
       </c>
@@ -3840,37 +3777,35 @@
 </t>
         </is>
       </c>
-      <c r="E24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">701
-</t>
-        </is>
-      </c>
-      <c r="F24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">221
-</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18 051
-</t>
-        </is>
-      </c>
-      <c r="H24" s="8" t="inlineStr">
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="G24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">105
+</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">148
 </t>
         </is>
       </c>
-      <c r="I24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">541
-</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">241
+</t>
+        </is>
+      </c>
+      <c r="J24" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">291
 </t>
@@ -3891,7 +3826,7 @@
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
@@ -3919,16 +3854,15 @@
 </t>
         </is>
       </c>
-      <c r="S24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">321
+      <c r="S24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>8746</t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
@@ -3939,26 +3873,26 @@
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="X24" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">11834
+          <t xml:space="preserve">211834
 </t>
         </is>
       </c>
       <c r="Y24" s="3" t="n"/>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -3999,122 +3933,101 @@
 </t>
         </is>
       </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">79
-</t>
-        </is>
-      </c>
-      <c r="H25" s="8" t="inlineStr">
+      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="n"/>
+      <c r="J25" s="3" t="n"/>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">31
+</t>
+        </is>
+      </c>
+      <c r="L25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="n"/>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
+      <c r="Q25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222
+</t>
+        </is>
+      </c>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
+      <c r="S25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">221
+</t>
+        </is>
+      </c>
+      <c r="T25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">825
+</t>
+        </is>
+      </c>
+      <c r="U25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">47
+</t>
+        </is>
+      </c>
+      <c r="V25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">211
+</t>
+        </is>
+      </c>
+      <c r="W25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="X25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="Y25" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">150
 </t>
         </is>
       </c>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">119
-</t>
-        </is>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27
-</t>
-        </is>
-      </c>
-      <c r="K25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">004
-</t>
-        </is>
-      </c>
-      <c r="L25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="M25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
-      <c r="N25" s="3" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="O25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">940
-</t>
-        </is>
-      </c>
-      <c r="P25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="Q25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="R25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
-      </c>
-      <c r="S25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">221
-</t>
-        </is>
-      </c>
-      <c r="T25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">825
-</t>
-        </is>
-      </c>
-      <c r="U25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">47
-</t>
-        </is>
-      </c>
-      <c r="V25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">211
-</t>
-        </is>
-      </c>
-      <c r="W25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="X25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="Y25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">130
-</t>
-        </is>
-      </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">63
+          <t xml:space="preserve">163
 </t>
         </is>
       </c>
@@ -4133,7 +4046,7 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3414
+          <t xml:space="preserve">3714
 </t>
         </is>
       </c>
@@ -4151,13 +4064,13 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
@@ -4167,9 +4080,9 @@
 </t>
         </is>
       </c>
-      <c r="I26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">253
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
@@ -4181,11 +4094,11 @@
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
-        </is>
-      </c>
-      <c r="L26" s="8" t="inlineStr">
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">170
 </t>
@@ -4197,33 +4110,32 @@
 </t>
         </is>
       </c>
-      <c r="N26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">828
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
-        </is>
-      </c>
-      <c r="Q26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">227
-</t>
-        </is>
-      </c>
-      <c r="R26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">416
+          <t xml:space="preserve">07
+</t>
+        </is>
+      </c>
+      <c r="Q26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">327
+</t>
+        </is>
+      </c>
+      <c r="R26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
@@ -4245,7 +4157,7 @@
 </t>
         </is>
       </c>
-      <c r="V26" s="3" t="inlineStr">
+      <c r="V26" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">206
 </t>
@@ -4302,7 +4214,7 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>46</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
@@ -4319,8 +4231,7 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>4605</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
@@ -4337,11 +4248,11 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="L27" s="3" t="inlineStr">
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="L27" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">168
 </t>
@@ -4349,15 +4260,11 @@
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>464</t>
-        </is>
-      </c>
-      <c r="N27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">251
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">161
+</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="n"/>
       <c r="O27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">930
@@ -4366,7 +4273,7 @@
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">113
 </t>
         </is>
       </c>
@@ -4378,7 +4285,7 @@
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
@@ -4388,14 +4295,10 @@
 </t>
         </is>
       </c>
-      <c r="T27" s="3" t="inlineStr">
-        <is>
-          <t>6364</t>
-        </is>
-      </c>
+      <c r="T27" s="3" t="n"/>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">909
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
@@ -4419,7 +4322,7 @@
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">836
+          <t xml:space="preserve">8386
 </t>
         </is>
       </c>
@@ -4456,125 +4359,121 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">250
+</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">219
+</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15 8
+</t>
+        </is>
+      </c>
+      <c r="H28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">028
+</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">53
+</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">801
+</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">167
+</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">150
 </t>
         </is>
       </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">219
-</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="H28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">933
-</t>
-        </is>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">288
-</t>
-        </is>
-      </c>
-      <c r="K28" s="3" t="inlineStr">
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8408
+</t>
+        </is>
+      </c>
+      <c r="P28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">801
+</t>
+        </is>
+      </c>
+      <c r="Q28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">068
+</t>
+        </is>
+      </c>
+      <c r="R28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="S28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="T28" s="3" t="n"/>
+      <c r="U28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">621
+</t>
+        </is>
+      </c>
+      <c r="V28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="W28" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">268
 </t>
         </is>
       </c>
-      <c r="L28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">167
-</t>
-        </is>
-      </c>
-      <c r="M28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">150
-</t>
-        </is>
-      </c>
-      <c r="N28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="O28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">840
-</t>
-        </is>
-      </c>
-      <c r="P28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">31
-</t>
-        </is>
-      </c>
-      <c r="Q28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">208
-</t>
-        </is>
-      </c>
-      <c r="R28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="S28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="T28" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">68
-</t>
-        </is>
-      </c>
-      <c r="V28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="W28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">264
-</t>
-        </is>
-      </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">785
+          <t xml:space="preserve">775
 </t>
         </is>
       </c>
@@ -4599,13 +4498,13 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3436
-</t>
-        </is>
-      </c>
-      <c r="D29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">23436
+</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
@@ -4617,14 +4516,13 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">101 4
 </t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>918</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
@@ -4647,24 +4545,28 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">619
-</t>
-        </is>
-      </c>
-      <c r="L29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">166
-</t>
+          <t xml:space="preserve">09
+</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>466</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
       <c r="N29" s="3" t="n"/>
-      <c r="O29" s="3" t="n"/>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">865
+</t>
+        </is>
+      </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">26
@@ -4679,19 +4581,19 @@
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">816
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">815
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
@@ -4713,9 +4615,9 @@
 </t>
         </is>
       </c>
-      <c r="X29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">209
+      <c r="X29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">069
 </t>
         </is>
       </c>
@@ -4746,61 +4648,50 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1869
-</t>
+          <t>788</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">817
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1121
+</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="n"/>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1004
+          <t xml:space="preserve">609
 </t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7009
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">500
+</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="n"/>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1200
+          <t xml:space="preserve">1100
 </t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">79
 </t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8939
+          <t xml:space="preserve">859
 </t>
         </is>
       </c>
@@ -4812,14 +4703,13 @@
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8 10
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14249
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
@@ -4830,32 +4720,31 @@
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1112
+          <t xml:space="preserve">428
 </t>
         </is>
       </c>
       <c r="R30" s="3" t="n"/>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81094
+          <t xml:space="preserve">21094
 </t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2222
+          <t xml:space="preserve">3222
 </t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">909
-</t>
+          <t>303</t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
+          <t xml:space="preserve">16818
 </t>
         </is>
       </c>
@@ -4867,20 +4756,14 @@
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9998
-</t>
-        </is>
-      </c>
-      <c r="Y30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1161
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">999
+</t>
+        </is>
+      </c>
+      <c r="Y30" s="3" t="n"/>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1200
-</t>
+          <t>004</t>
         </is>
       </c>
       <c r="AA30" s="3" t="inlineStr">
@@ -4902,15 +4785,14 @@
 </t>
         </is>
       </c>
-      <c r="D31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2862
-</t>
-        </is>
-      </c>
-      <c r="E31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">163
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>963</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
@@ -4922,7 +4804,7 @@
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">11001
+          <t xml:space="preserve">1100
 </t>
         </is>
       </c>
@@ -4934,31 +4816,31 @@
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9 9
+          <t xml:space="preserve">2 9
 </t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="L31" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1721
+          <t xml:space="preserve">721
 </t>
         </is>
       </c>
       <c r="M31" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">01208101
+          <t xml:space="preserve">0218101
 </t>
         </is>
       </c>
@@ -4971,7 +4853,7 @@
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -4983,13 +4865,13 @@
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12 66
-</t>
-        </is>
-      </c>
-      <c r="S31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">200
+</t>
+        </is>
+      </c>
+      <c r="S31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
@@ -5001,13 +4883,13 @@
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">611
+          <t xml:space="preserve">61
 </t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
@@ -5054,15 +4936,10 @@
 </t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">264
-</t>
-        </is>
-      </c>
-      <c r="E32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">291
+      <c r="D32" s="3" t="n"/>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
@@ -5074,31 +4951,31 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">816
-</t>
-        </is>
-      </c>
-      <c r="H32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">894
-</t>
-        </is>
-      </c>
-      <c r="I32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">856
-</t>
-        </is>
-      </c>
-      <c r="J32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">014
+          <t xml:space="preserve">210
+</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">134
+</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -5110,76 +4987,76 @@
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">151
 </t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">010
-</t>
-        </is>
-      </c>
-      <c r="Q32" s="8" t="inlineStr">
+          <t xml:space="preserve">62
+</t>
+        </is>
+      </c>
+      <c r="Q32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="R32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="S32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
+      <c r="T32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">980
+</t>
+        </is>
+      </c>
+      <c r="U32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">107
+</t>
+        </is>
+      </c>
+      <c r="V32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">175
+</t>
+        </is>
+      </c>
+      <c r="W32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
+      <c r="X32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">189
 </t>
         </is>
       </c>
-      <c r="R32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="S32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2064
-</t>
-        </is>
-      </c>
-      <c r="T32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">910
-</t>
-        </is>
-      </c>
-      <c r="U32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">104
-</t>
-        </is>
-      </c>
-      <c r="V32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">175
-</t>
-        </is>
-      </c>
-      <c r="W32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">162
-</t>
-        </is>
-      </c>
-      <c r="X32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">081
-</t>
-        </is>
-      </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">940
@@ -5188,7 +5065,7 @@
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1820
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
@@ -5207,7 +5084,7 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14008
+          <t xml:space="preserve">4008
 </t>
         </is>
       </c>
@@ -5223,13 +5100,13 @@
 </t>
         </is>
       </c>
-      <c r="F33" s="8" t="inlineStr">
+      <c r="F33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">217
 </t>
         </is>
       </c>
-      <c r="G33" s="8" t="inlineStr">
+      <c r="G33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">111
 </t>
@@ -5243,16 +5120,10 @@
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">241
-</t>
-        </is>
-      </c>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="n"/>
       <c r="K33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">58
@@ -5267,31 +5138,31 @@
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">018
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
-      <c r="Q33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">143
+</t>
+        </is>
+      </c>
+      <c r="Q33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
@@ -5319,15 +5190,15 @@
 </t>
         </is>
       </c>
-      <c r="V33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">896
+      <c r="V33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="W33" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
@@ -5345,7 +5216,7 @@
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">821
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
@@ -5394,7 +5265,7 @@
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
+          <t xml:space="preserve">656
 </t>
         </is>
       </c>
@@ -5406,28 +5277,24 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">397
+</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="n"/>
       <c r="L34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">175
 </t>
         </is>
       </c>
-      <c r="M34" s="8" t="inlineStr">
+      <c r="M34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">166
 </t>
         </is>
       </c>
-      <c r="N34" s="8" t="inlineStr">
+      <c r="N34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">119
 </t>
@@ -5435,7 +5302,7 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">918
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
@@ -5447,8 +5314,7 @@
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
-</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
@@ -5457,12 +5323,7 @@
 </t>
         </is>
       </c>
-      <c r="S34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">214
-</t>
-        </is>
-      </c>
+      <c r="S34" s="3" t="n"/>
       <c r="T34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">748
@@ -5471,13 +5332,13 @@
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
@@ -5501,7 +5362,7 @@
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -5562,7 +5423,7 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
@@ -5580,17 +5441,18 @@
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>450</t>
+          <t xml:space="preserve">15
+</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>17</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">800
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
@@ -5608,7 +5470,7 @@
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
@@ -5626,7 +5488,7 @@
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -5650,13 +5512,13 @@
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">892
+          <t xml:space="preserve">895
 </t>
         </is>
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2441
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
@@ -5705,7 +5567,7 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">137
 </t>
         </is>
       </c>
@@ -5717,7 +5579,7 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
@@ -5742,13 +5604,13 @@
       <c r="N36" s="3" t="n"/>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">45
 </t>
         </is>
       </c>
@@ -5766,7 +5628,7 @@
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
@@ -5782,15 +5644,15 @@
 </t>
         </is>
       </c>
-      <c r="V36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">208
+      <c r="V36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">808
 </t>
         </is>
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -5808,7 +5670,7 @@
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -5827,25 +5689,25 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16402
+          <t xml:space="preserve">16452
 </t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16211
+          <t xml:space="preserve">11828
 </t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">821
 </t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13011
+          <t xml:space="preserve">16091
 </t>
         </is>
       </c>
@@ -5857,25 +5719,24 @@
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">7106
 </t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1067
+          <t xml:space="preserve">1167
 </t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16006
+          <t xml:space="preserve">1606
 </t>
         </is>
       </c>
@@ -5885,39 +5746,34 @@
 </t>
         </is>
       </c>
-      <c r="M37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">110
-</t>
-        </is>
-      </c>
+      <c r="M37" s="3" t="n"/>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">860
+          <t xml:space="preserve">868
 </t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2980
+          <t xml:space="preserve">2280
 </t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1808
+          <t xml:space="preserve">1208
 </t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1229
+          <t xml:space="preserve">18123
 </t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1461
+          <t xml:space="preserve">911
 </t>
         </is>
       </c>
@@ -5929,12 +5785,13 @@
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t xml:space="preserve">2894
+</t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1942
+          <t xml:space="preserve">942
 </t>
         </is>
       </c>
@@ -5946,14 +5803,13 @@
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9212
-</t>
+          <t>914</t>
         </is>
       </c>
       <c r="X37" s="3" t="n"/>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44817
+          <t xml:space="preserve">4188
 </t>
         </is>
       </c>
@@ -5971,17 +5827,21 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C38" s="3" t="n"/>
-      <c r="D38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">631
-</t>
-        </is>
-      </c>
-      <c r="E38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">661
-</t>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12928
+</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">62
+</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>6341</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
@@ -5992,11 +5852,11 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">971
-</t>
-        </is>
-      </c>
-      <c r="H38" s="8" t="inlineStr">
+          <t xml:space="preserve">970
+</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">141
 </t>
@@ -6008,9 +5868,9 @@
 </t>
         </is>
       </c>
-      <c r="J38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">231
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">331
 </t>
         </is>
       </c>
@@ -6045,15 +5905,14 @@
 </t>
         </is>
       </c>
-      <c r="Q38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">122
-</t>
+      <c r="Q38" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117 8
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
@@ -6065,37 +5924,32 @@
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7711
-</t>
-        </is>
-      </c>
-      <c r="U38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">464
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">771
+</t>
+        </is>
+      </c>
+      <c r="U38" s="3" t="n"/>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="X38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">086
+          <t xml:space="preserve">183
+</t>
+        </is>
+      </c>
+      <c r="X38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">891
+          <t xml:space="preserve">897
 </t>
         </is>
       </c>
@@ -6115,8 +5969,7 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2864
-</t>
+          <t>9864</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
@@ -6133,7 +5986,7 @@
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
@@ -6158,26 +6011,26 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">077
+          <t xml:space="preserve">800
+</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">177
 </t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
       <c r="N39" s="3" t="n"/>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
+          <t xml:space="preserve">880
 </t>
         </is>
       </c>
@@ -6195,13 +6048,13 @@
       </c>
       <c r="R39" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
@@ -6242,7 +6095,7 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">53590
+          <t xml:space="preserve">3590
 </t>
         </is>
       </c>
@@ -6260,7 +6113,7 @@
       </c>
       <c r="F40" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1116
+          <t xml:space="preserve">1816
 </t>
         </is>
       </c>
@@ -6273,7 +6126,7 @@
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">859
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -6283,7 +6136,12 @@
 </t>
         </is>
       </c>
-      <c r="K40" s="3" t="n"/>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">180
@@ -6304,73 +6162,72 @@
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">762
+</t>
+        </is>
+      </c>
+      <c r="P40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">48
+</t>
+        </is>
+      </c>
+      <c r="Q40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">258
+</t>
+        </is>
+      </c>
+      <c r="R40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">202
+</t>
+        </is>
+      </c>
+      <c r="S40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
+      <c r="T40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">684
+</t>
+        </is>
+      </c>
+      <c r="U40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="V40" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
+      <c r="X40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="Y40" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">862
 </t>
         </is>
       </c>
-      <c r="P40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
-      <c r="Q40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">258
-</t>
-        </is>
-      </c>
-      <c r="R40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">202
-</t>
-        </is>
-      </c>
-      <c r="S40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
-      <c r="T40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">614
-</t>
-        </is>
-      </c>
-      <c r="U40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="V40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">212
-</t>
-        </is>
-      </c>
-      <c r="W40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="X40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="Y40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">862
-</t>
-        </is>
-      </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">814
+          <t xml:space="preserve">324
 </t>
         </is>
       </c>
@@ -6389,7 +6246,7 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>88664</t>
+          <t>48664</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
@@ -6406,7 +6263,7 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">818
 </t>
         </is>
       </c>
@@ -6414,13 +6271,13 @@
       <c r="H41" s="3" t="n"/>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
+          <t xml:space="preserve">63
 </t>
         </is>
       </c>
@@ -6432,7 +6289,7 @@
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">277
+          <t xml:space="preserve">177
 </t>
         </is>
       </c>
@@ -6444,23 +6301,23 @@
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">500
-</t>
-        </is>
-      </c>
-      <c r="Q41" s="3" t="inlineStr">
+          <t xml:space="preserve">86
+</t>
+        </is>
+      </c>
+      <c r="Q41" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">260
 </t>
@@ -6530,7 +6387,7 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9426
+          <t xml:space="preserve">2426
 </t>
         </is>
       </c>
@@ -6546,9 +6403,9 @@
 </t>
         </is>
       </c>
-      <c r="F42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">019
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
@@ -6558,7 +6415,7 @@
 </t>
         </is>
       </c>
-      <c r="H42" s="8" t="inlineStr">
+      <c r="H42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">148
 </t>
@@ -6567,7 +6424,7 @@
       <c r="I42" s="3" t="n"/>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
@@ -6589,7 +6446,7 @@
 </t>
         </is>
       </c>
-      <c r="N42" s="8" t="inlineStr">
+      <c r="N42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">160
 </t>
@@ -6603,25 +6460,25 @@
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
-        </is>
-      </c>
-      <c r="Q42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">841
+          <t xml:space="preserve">42
+</t>
+        </is>
+      </c>
+      <c r="Q42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">271
 </t>
         </is>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
-        </is>
-      </c>
-      <c r="S42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">299
+          <t xml:space="preserve">202
+</t>
+        </is>
+      </c>
+      <c r="S42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">899
 </t>
         </is>
       </c>
@@ -6631,12 +6488,7 @@
 </t>
         </is>
       </c>
-      <c r="U42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
+      <c r="U42" s="3" t="n"/>
       <c r="V42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">222
@@ -6651,13 +6503,13 @@
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">897
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">234
 </t>
         </is>
       </c>
@@ -6680,16 +6532,21 @@
           <t>30</t>
         </is>
       </c>
-      <c r="C43" s="3" t="n"/>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">948
-</t>
-        </is>
-      </c>
-      <c r="E43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">109
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6
+</t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">281
+</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">809
 </t>
         </is>
       </c>
@@ -6699,33 +6556,33 @@
 </t>
         </is>
       </c>
-      <c r="G43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">211
-</t>
-        </is>
-      </c>
-      <c r="H43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">914
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">525
+</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">094
 </t>
         </is>
       </c>
       <c r="I43" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">619
-</t>
-        </is>
-      </c>
-      <c r="J43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">261
+          <t xml:space="preserve">618
+</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
@@ -6744,7 +6601,7 @@
       <c r="N43" s="3" t="n"/>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1055
+          <t xml:space="preserve">4055
 </t>
         </is>
       </c>
@@ -6754,21 +6611,21 @@
 </t>
         </is>
       </c>
-      <c r="Q43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">251
-</t>
-        </is>
-      </c>
-      <c r="R43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">102
+      <c r="Q43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">221
+</t>
+        </is>
+      </c>
+      <c r="R43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">616
 </t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16 16
+          <t xml:space="preserve">10 9
 </t>
         </is>
       </c>
@@ -6780,7 +6637,7 @@
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">536
+          <t xml:space="preserve">556
 </t>
         </is>
       </c>
@@ -6790,21 +6647,16 @@
 </t>
         </is>
       </c>
-      <c r="W43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">193
-</t>
-        </is>
-      </c>
+      <c r="W43" s="3" t="n"/>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201 10
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4 067
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
@@ -6908,19 +6760,19 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">52
 </t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
@@ -6932,7 +6784,7 @@
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">016
 </t>
         </is>
       </c>
@@ -6950,22 +6802,22 @@
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">851
 </t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">2028
+</t>
+        </is>
+      </c>
+      <c r="S45" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">208
 </t>
         </is>
       </c>
-      <c r="S45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">208
-</t>
-        </is>
-      </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">660
@@ -6998,7 +6850,7 @@
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">47
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
@@ -7031,31 +6883,31 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">014
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
@@ -7077,35 +6929,30 @@
 </t>
         </is>
       </c>
-      <c r="N46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4107
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
-      <c r="Q46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="Q46" s="3" t="n"/>
       <c r="R46" s="3" t="n"/>
       <c r="S46" s="3" t="n"/>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
@@ -7117,22 +6964,17 @@
       </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="X46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="X46" s="3" t="n"/>
       <c r="Y46" s="3" t="n"/>
       <c r="Z46" s="3" t="n"/>
       <c r="AA46" s="3" t="inlineStr">

--- a/results/05_transient_transcription_output/905/905_197311_SF.JPG_stage_digit_manipulation.xlsx
+++ b/results/05_transient_transcription_output/905/905_197311_SF.JPG_stage_digit_manipulation.xlsx
@@ -755,13 +755,13 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">825
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -795,21 +795,21 @@
 </t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="M4" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">168
 </t>
         </is>
       </c>
-      <c r="N4" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">885
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
+          <t xml:space="preserve">2900
 </t>
         </is>
       </c>
@@ -831,7 +831,7 @@
 </t>
         </is>
       </c>
-      <c r="S4" s="8" t="inlineStr">
+      <c r="S4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">250
 </t>
@@ -845,13 +845,13 @@
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">43
+          <t xml:space="preserve">143
 </t>
         </is>
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">803
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
@@ -873,11 +873,7 @@
 </t>
         </is>
       </c>
-      <c r="Z4" s="3" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
+      <c r="Z4" s="3" t="n"/>
       <c r="AA4" s="3" t="inlineStr">
         <is>
           <t>1</t>
@@ -893,13 +889,13 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94326
+          <t xml:space="preserve">4386
 </t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>986</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -910,19 +906,18 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
-</t>
+          <t>425</t>
         </is>
       </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2150
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="H5" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">1210
 </t>
         </is>
       </c>
@@ -938,9 +933,9 @@
 </t>
         </is>
       </c>
-      <c r="K5" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">223
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
@@ -950,7 +945,7 @@
 </t>
         </is>
       </c>
-      <c r="M5" s="8" t="inlineStr">
+      <c r="M5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">176
 </t>
@@ -958,13 +953,13 @@
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">981
+          <t xml:space="preserve">931
 </t>
         </is>
       </c>
@@ -994,13 +989,13 @@
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">743
+          <t xml:space="preserve">843
 </t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
@@ -1016,7 +1011,7 @@
 </t>
         </is>
       </c>
-      <c r="X5" s="3" t="inlineStr">
+      <c r="X5" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">191
 </t>
@@ -1028,7 +1023,12 @@
 </t>
         </is>
       </c>
-      <c r="Z5" s="3" t="n"/>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">33
+</t>
+        </is>
+      </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
           <t>2</t>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4844
+          <t xml:space="preserve">4944
 </t>
         </is>
       </c>
@@ -1067,15 +1067,15 @@
 </t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">152
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
@@ -1105,11 +1105,16 @@
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
-</t>
-        </is>
-      </c>
-      <c r="O6" s="3" t="n"/>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">920
+</t>
+        </is>
+      </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">16
@@ -1152,7 +1157,7 @@
 </t>
         </is>
       </c>
-      <c r="W6" s="3" t="inlineStr">
+      <c r="W6" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">192
 </t>
@@ -1160,7 +1165,7 @@
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -1172,7 +1177,7 @@
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
@@ -1195,12 +1200,7 @@
 </t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">281
-</t>
-        </is>
-      </c>
+      <c r="D7" s="3" t="n"/>
       <c r="E7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">162
@@ -1227,13 +1227,14 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>48</t>
+          <t xml:space="preserve">48
+</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
@@ -1256,13 +1257,14 @@
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">898
+</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
@@ -1291,7 +1293,7 @@
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">687
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
@@ -1315,19 +1317,19 @@
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">216
+</t>
+        </is>
+      </c>
+      <c r="Y7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">910
+</t>
+        </is>
+      </c>
+      <c r="Z7" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">221
-</t>
-        </is>
-      </c>
-      <c r="Y7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">900
-</t>
-        </is>
-      </c>
-      <c r="Z7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -1346,7 +1348,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2602
+          <t xml:space="preserve">4602
 </t>
         </is>
       </c>
@@ -1410,9 +1412,9 @@
 </t>
         </is>
       </c>
-      <c r="N8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">672
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -1424,7 +1426,7 @@
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
@@ -1478,13 +1480,13 @@
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">900
+</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">860
-</t>
-        </is>
-      </c>
-      <c r="Z8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">32
 </t>
         </is>
       </c>
@@ -1503,18 +1505,19 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>34405</t>
+          <t xml:space="preserve">22404
+</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18248
+          <t xml:space="preserve">1420
 </t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">8291
 </t>
         </is>
       </c>
@@ -1526,13 +1529,13 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">991
+          <t xml:space="preserve">2591
 </t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">618
+          <t xml:space="preserve">6717
 </t>
         </is>
       </c>
@@ -1556,8 +1559,7 @@
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">814
-</t>
+          <t>39801</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
@@ -1566,15 +1568,10 @@
 </t>
         </is>
       </c>
-      <c r="N9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">123
-</t>
-        </is>
-      </c>
+      <c r="N9" s="3" t="n"/>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">3433
 </t>
         </is>
       </c>
@@ -1586,17 +1583,22 @@
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1271
+          <t xml:space="preserve">12721
 </t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0912
-</t>
-        </is>
-      </c>
-      <c r="S9" s="3" t="n"/>
+          <t xml:space="preserve">1109
+</t>
+        </is>
+      </c>
+      <c r="S9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1243
+</t>
+        </is>
+      </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">3842
@@ -1611,31 +1613,31 @@
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">989
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">927
+</t>
+        </is>
+      </c>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">638
+</t>
+        </is>
+      </c>
+      <c r="Y9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4451
+</t>
+        </is>
+      </c>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">127
-</t>
-        </is>
-      </c>
-      <c r="X9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1628
-</t>
-        </is>
-      </c>
-      <c r="Y9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4458
-</t>
-        </is>
-      </c>
-      <c r="Z9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1228
 </t>
         </is>
       </c>
@@ -1658,35 +1660,37 @@
 </t>
         </is>
       </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">891
-</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">166
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">284
+</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">661
 </t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>85</t>
+          <t xml:space="preserve">225
+</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>468</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">135
-</t>
-        </is>
-      </c>
-      <c r="I10" s="8" t="inlineStr">
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">821
 </t>
@@ -1700,27 +1704,23 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
+      <c r="L10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="N10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6878
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="n"/>
       <c r="O10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">906
@@ -1729,31 +1729,31 @@
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">264
 </t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">104 14
 </t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">768
+          <t xml:space="preserve">769
 </t>
         </is>
       </c>
@@ -1763,13 +1763,18 @@
 </t>
         </is>
       </c>
-      <c r="V10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">981
-</t>
-        </is>
-      </c>
-      <c r="W10" s="3" t="n"/>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="W10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">206
@@ -1784,7 +1789,7 @@
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">16 14
 </t>
         </is>
       </c>
@@ -1815,45 +1820,40 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">868
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>911</t>
+          <t xml:space="preserve">197
+</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="J11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311
-</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">04
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">140
+</t>
+        </is>
+      </c>
+      <c r="I11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">928
+</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="n"/>
       <c r="L11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">172
@@ -1868,7 +1868,8 @@
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>414</t>
+          <t xml:space="preserve">85
+</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
@@ -1877,25 +1878,20 @@
 </t>
         </is>
       </c>
-      <c r="P11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">084
-</t>
-        </is>
-      </c>
+      <c r="P11" s="3" t="n"/>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
-</t>
-        </is>
-      </c>
-      <c r="R11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">163
-</t>
-        </is>
-      </c>
-      <c r="S11" s="8" t="inlineStr">
+          <t xml:space="preserve">260
+</t>
+        </is>
+      </c>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">215
+</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">230
 </t>
@@ -1907,7 +1903,7 @@
 </t>
         </is>
       </c>
-      <c r="U11" s="8" t="inlineStr">
+      <c r="U11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">106
 </t>
@@ -1915,19 +1911,19 @@
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="W11" s="8" t="inlineStr">
+          <t xml:space="preserve">217
+</t>
+        </is>
+      </c>
+      <c r="W11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">198
 </t>
         </is>
       </c>
-      <c r="X11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">820
+      <c r="X11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8220
 </t>
         </is>
       </c>
@@ -2000,19 +1996,19 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
-</t>
-        </is>
-      </c>
-      <c r="L12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="L12" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">814
 </t>
         </is>
       </c>
@@ -2030,7 +2026,7 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">926
+          <t xml:space="preserve">921
 </t>
         </is>
       </c>
@@ -2046,20 +2042,21 @@
 </t>
         </is>
       </c>
-      <c r="R12" s="3" t="inlineStr">
+      <c r="R12" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">195
 </t>
         </is>
       </c>
-      <c r="S12" s="3" t="inlineStr">
-        <is>
-          <t>086</t>
+      <c r="S12" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222
+</t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9230
+          <t xml:space="preserve">930
 </t>
         </is>
       </c>
@@ -2083,7 +2080,7 @@
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
@@ -2114,7 +2111,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23238
+          <t xml:space="preserve">3238
 </t>
         </is>
       </c>
@@ -2126,7 +2123,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
@@ -2136,7 +2133,7 @@
 </t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G13" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">105
 </t>
@@ -2148,13 +2145,13 @@
 </t>
         </is>
       </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="J13" s="3" t="n"/>
+      <c r="I13" s="3" t="n"/>
+      <c r="J13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">210
+</t>
+        </is>
+      </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">140
@@ -2167,7 +2164,7 @@
 </t>
         </is>
       </c>
-      <c r="M13" s="3" t="inlineStr">
+      <c r="M13" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">169
 </t>
@@ -2175,12 +2172,22 @@
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
-        </is>
-      </c>
-      <c r="O13" s="3" t="n"/>
-      <c r="P13" s="3" t="n"/>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">922
+</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">244
@@ -2201,13 +2208,13 @@
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">275
 </t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
@@ -2219,11 +2226,11 @@
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
-</t>
-        </is>
-      </c>
-      <c r="X13" s="8" t="inlineStr">
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="X13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">222
 </t>
@@ -2272,15 +2279,15 @@
 </t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">211
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8211
 </t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">984
+          <t xml:space="preserve">74
 </t>
         </is>
       </c>
@@ -2290,15 +2297,10 @@
 </t>
         </is>
       </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="J14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222
+      <c r="I14" s="3" t="n"/>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 2
 </t>
         </is>
       </c>
@@ -2320,9 +2322,9 @@
 </t>
         </is>
       </c>
-      <c r="N14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -2364,7 +2366,7 @@
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -2382,13 +2384,13 @@
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
+          <t xml:space="preserve">910
 </t>
         </is>
       </c>
@@ -2413,7 +2415,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2348
+          <t xml:space="preserve">3348
 </t>
         </is>
       </c>
@@ -2429,27 +2431,27 @@
 </t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">229
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">085
 </t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18 7
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 44 1
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -2461,7 +2463,7 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">986
 </t>
         </is>
       </c>
@@ -2479,7 +2481,7 @@
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
@@ -2497,7 +2499,7 @@
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
@@ -2509,7 +2511,7 @@
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
@@ -2519,7 +2521,7 @@
 </t>
         </is>
       </c>
-      <c r="U15" s="3" t="inlineStr">
+      <c r="U15" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">160
 </t>
@@ -2551,7 +2553,7 @@
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
@@ -2570,19 +2572,19 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03618
+          <t xml:space="preserve">13618
 </t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">1340
 </t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">856
 </t>
         </is>
       </c>
@@ -2594,13 +2596,13 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24814
+          <t xml:space="preserve">4814
 </t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">730
 </t>
         </is>
       </c>
@@ -2610,33 +2612,40 @@
 </t>
         </is>
       </c>
-      <c r="J16" s="3" t="n"/>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">149
+</t>
+        </is>
+      </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">989
+          <t xml:space="preserve">926
 </t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>688</t>
+          <t xml:space="preserve">888
+</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">833
+          <t xml:space="preserve">853
 </t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">950
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>659</t>
+          <t xml:space="preserve">14659
+</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
@@ -2647,47 +2656,49 @@
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">10893
 </t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>71603</t>
+          <t xml:space="preserve">1043
+</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11 29
+          <t xml:space="preserve">21166
 </t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t>415</t>
+          <t xml:space="preserve">1998
+</t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">831
+          <t xml:space="preserve">351
 </t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1018
+          <t xml:space="preserve">1019
 </t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">869
+          <t xml:space="preserve">9691
 </t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">0987
 </t>
         </is>
       </c>
@@ -2697,12 +2708,7 @@
 </t>
         </is>
       </c>
-      <c r="Z16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">104
-</t>
-        </is>
-      </c>
+      <c r="Z16" s="3" t="n"/>
       <c r="AA16" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -2718,13 +2724,13 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3124
+          <t xml:space="preserve">23124
 </t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">601
+          <t xml:space="preserve">401
 </t>
         </is>
       </c>
@@ -2736,11 +2742,16 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="n"/>
+          <t xml:space="preserve">920
+</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">297
+</t>
+        </is>
+      </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">146
@@ -2749,7 +2760,8 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>4816</t>
+          <t xml:space="preserve">22
+</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -2760,40 +2772,40 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">4
+</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">932
+</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">14
 </t>
         </is>
       </c>
-      <c r="L17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="M17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="N17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">932
-</t>
-        </is>
-      </c>
-      <c r="P17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">141
-</t>
-        </is>
-      </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">239
@@ -2802,19 +2814,19 @@
       </c>
       <c r="R17" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">691
-</t>
-        </is>
-      </c>
-      <c r="S17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">298
+          <t xml:space="preserve">1891
+</t>
+        </is>
+      </c>
+      <c r="S17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1887
+          <t xml:space="preserve">7891
 </t>
         </is>
       </c>
@@ -2824,27 +2836,27 @@
 </t>
         </is>
       </c>
-      <c r="V17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
-      <c r="W17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">294
+      <c r="V17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2116
+</t>
+        </is>
+      </c>
+      <c r="W17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">28 12 1
 </t>
         </is>
       </c>
@@ -2869,7 +2881,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2546
+          <t xml:space="preserve">3546
 </t>
         </is>
       </c>
@@ -2885,10 +2897,15 @@
 </t>
         </is>
       </c>
-      <c r="F18" s="3" t="n"/>
-      <c r="G18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">867
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">909
+</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
@@ -2900,7 +2917,7 @@
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>506</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -2910,11 +2927,11 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
-        </is>
-      </c>
-      <c r="L18" s="8" t="inlineStr">
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">182
 </t>
@@ -2928,7 +2945,7 @@
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -2946,13 +2963,13 @@
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>8491</t>
+          <t xml:space="preserve">218
+</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
@@ -2967,39 +2984,39 @@
 </t>
         </is>
       </c>
-      <c r="U18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">418
+      <c r="U18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">147
 </t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">224 884
+</t>
+        </is>
+      </c>
+      <c r="W18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11 11
+</t>
+        </is>
+      </c>
+      <c r="X18" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">209
 </t>
         </is>
       </c>
-      <c r="W18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="X18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">267
-</t>
-        </is>
-      </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">1189
 </t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
@@ -3018,7 +3035,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">2194
 </t>
         </is>
       </c>
@@ -3034,9 +3051,9 @@
 </t>
         </is>
       </c>
-      <c r="F19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">088
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
@@ -3048,13 +3065,13 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
@@ -3066,7 +3083,7 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
@@ -3078,13 +3095,13 @@
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
+          <t xml:space="preserve">874
 </t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -3094,9 +3111,9 @@
 </t>
         </is>
       </c>
-      <c r="P19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">881
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -3108,13 +3125,13 @@
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
-        </is>
-      </c>
-      <c r="S19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">205
+</t>
+        </is>
+      </c>
+      <c r="S19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">086
 </t>
         </is>
       </c>
@@ -3126,7 +3143,7 @@
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
@@ -3150,13 +3167,13 @@
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">736
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">76
 </t>
         </is>
       </c>
@@ -3173,8 +3190,12 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="3" t="n"/>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>3588</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">268
 </t>
@@ -3186,7 +3207,12 @@
 </t>
         </is>
       </c>
-      <c r="F20" s="3" t="n"/>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223
+</t>
+        </is>
+      </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">90
@@ -3201,25 +3227,25 @@
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">911
+          <t xml:space="preserve">531
 </t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>491</t>
+          <t xml:space="preserve">182
+</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
@@ -3230,7 +3256,7 @@
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -3258,13 +3284,18 @@
 </t>
         </is>
       </c>
-      <c r="S20" s="3" t="inlineStr">
+      <c r="S20" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">247
 </t>
         </is>
       </c>
-      <c r="T20" s="3" t="n"/>
+      <c r="T20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18918
+</t>
+        </is>
+      </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">31
@@ -3316,14 +3347,13 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12546
-</t>
-        </is>
-      </c>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">881
-</t>
+          <t xml:space="preserve">22842
+</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>681</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -3338,21 +3368,21 @@
 </t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">171
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">718
 </t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -3364,7 +3394,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
@@ -3380,9 +3410,9 @@
 </t>
         </is>
       </c>
-      <c r="N21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">280
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -3398,12 +3428,7 @@
 </t>
         </is>
       </c>
-      <c r="Q21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">209
-</t>
-        </is>
-      </c>
+      <c r="Q21" s="3" t="n"/>
       <c r="R21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">199
@@ -3418,13 +3443,13 @@
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">961
+          <t xml:space="preserve">911
 </t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -3479,7 +3504,7 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
+          <t xml:space="preserve">976
 </t>
         </is>
       </c>
@@ -3491,7 +3516,7 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">923
 </t>
         </is>
       </c>
@@ -3515,7 +3540,7 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
@@ -3525,7 +3550,7 @@
 </t>
         </is>
       </c>
-      <c r="L22" s="8" t="inlineStr">
+      <c r="L22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">180
 </t>
@@ -3539,7 +3564,7 @@
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -3575,7 +3600,7 @@
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">7240
 </t>
         </is>
       </c>
@@ -3611,7 +3636,7 @@
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">87
 </t>
         </is>
       </c>
@@ -3628,10 +3653,16 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="n"/>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15426
+</t>
+        </is>
+      </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>76</t>
+          <t xml:space="preserve">1376
+</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -3642,19 +3673,19 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">926
+          <t xml:space="preserve">3526
 </t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">748
 </t>
         </is>
       </c>
@@ -3666,65 +3697,56 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1290
+          <t xml:space="preserve">1193
 </t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">606
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>9076</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">812
-</t>
-        </is>
-      </c>
-      <c r="N23" s="3" t="n"/>
+          <t xml:space="preserve">878
+</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9
+</t>
+        </is>
+      </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
           <t>469</t>
         </is>
       </c>
-      <c r="P23" s="3" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="Q23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
-      <c r="R23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">248
-</t>
-        </is>
-      </c>
+      <c r="P23" s="3" t="n"/>
+      <c r="Q23" s="3" t="n"/>
+      <c r="R23" s="3" t="n"/>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81158
+          <t xml:space="preserve">2158
 </t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3931
+          <t xml:space="preserve">2931
 </t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">932
+          <t xml:space="preserve">332
 </t>
         </is>
       </c>
@@ -3736,22 +3758,28 @@
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">996
 </t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t>7713</t>
+          <t xml:space="preserve">1109
+</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">416
-</t>
-        </is>
-      </c>
-      <c r="Z23" s="3" t="n"/>
+          <t xml:space="preserve">6068
+</t>
+        </is>
+      </c>
+      <c r="Z23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">221
+</t>
+        </is>
+      </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -3777,62 +3805,68 @@
 </t>
         </is>
       </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>38</t>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">701
+</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="G24" s="8" t="inlineStr">
+          <t xml:space="preserve">292
+</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">105
 </t>
         </is>
       </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1848
 </t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
-</t>
-        </is>
-      </c>
-      <c r="J24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">291
-</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="n"/>
+          <t xml:space="preserve">94
+</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">99
+</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="M24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">741
+          <t>481</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9381
+          <t xml:space="preserve">938
 </t>
         </is>
       </c>
@@ -3856,13 +3890,14 @@
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t>8746</t>
+          <t xml:space="preserve">787
+</t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
@@ -3873,7 +3908,7 @@
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
@@ -3885,14 +3920,19 @@
       </c>
       <c r="X24" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">211834
-</t>
-        </is>
-      </c>
-      <c r="Y24" s="3" t="n"/>
+          <t xml:space="preserve">81811
+</t>
+        </is>
+      </c>
+      <c r="Y24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">824
+</t>
+        </is>
+      </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
@@ -3911,8 +3951,7 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2798
-</t>
+          <t>4799</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -3933,17 +3972,23 @@
 </t>
         </is>
       </c>
-      <c r="G25" s="3" t="n"/>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">75
+</t>
+        </is>
+      </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>156</t>
+          <t xml:space="preserve">156
+</t>
         </is>
       </c>
       <c r="I25" s="3" t="n"/>
       <c r="J25" s="3" t="n"/>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
+          <t xml:space="preserve">51
 </t>
         </is>
       </c>
@@ -3953,13 +3998,18 @@
 </t>
         </is>
       </c>
-      <c r="M25" s="3" t="inlineStr">
+      <c r="M25" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">182
 </t>
         </is>
       </c>
-      <c r="N25" s="3" t="n"/>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
           <t>94</t>
@@ -3967,11 +4017,11 @@
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
-        </is>
-      </c>
-      <c r="Q25" s="8" t="inlineStr">
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="Q25" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">222
 </t>
@@ -3979,7 +4029,7 @@
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
@@ -3997,37 +4047,37 @@
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">47
-</t>
-        </is>
-      </c>
-      <c r="V25" s="3" t="inlineStr">
+          <t xml:space="preserve">97
+</t>
+        </is>
+      </c>
+      <c r="V25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">117
+</t>
+        </is>
+      </c>
+      <c r="W25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">514
+</t>
+        </is>
+      </c>
+      <c r="X25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">544
+</t>
+        </is>
+      </c>
+      <c r="Y25" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">211
 </t>
         </is>
       </c>
-      <c r="W25" s="3" t="inlineStr">
+      <c r="Z25" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="X25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="Y25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">150
-</t>
-        </is>
-      </c>
-      <c r="Z25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">163
 </t>
         </is>
       </c>
@@ -4046,7 +4096,7 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3714
+          <t xml:space="preserve">3411
 </t>
         </is>
       </c>
@@ -4064,19 +4114,19 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
@@ -4088,13 +4138,13 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">37
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -4112,13 +4162,14 @@
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>970</t>
+          <t xml:space="preserve">970
+</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
@@ -4127,9 +4178,9 @@
 </t>
         </is>
       </c>
-      <c r="Q26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">327
+      <c r="Q26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
@@ -4139,7 +4190,7 @@
 </t>
         </is>
       </c>
-      <c r="S26" s="3" t="inlineStr">
+      <c r="S26" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">246
 </t>
@@ -4171,7 +4222,7 @@
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
@@ -4214,7 +4265,8 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>46</t>
+          <t xml:space="preserve">167
+</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
@@ -4231,7 +4283,8 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>4605</t>
+          <t xml:space="preserve">160
+</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
@@ -4248,11 +4301,11 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="L27" s="8" t="inlineStr">
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">168
 </t>
@@ -4264,7 +4317,12 @@
 </t>
         </is>
       </c>
-      <c r="N27" s="3" t="n"/>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">930
@@ -4291,11 +4349,16 @@
       </c>
       <c r="S27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
-</t>
-        </is>
-      </c>
-      <c r="T27" s="3" t="n"/>
+          <t xml:space="preserve">227
+</t>
+        </is>
+      </c>
+      <c r="T27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">696
+</t>
+        </is>
+      </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">99
@@ -4314,15 +4377,15 @@
 </t>
         </is>
       </c>
-      <c r="X27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">208
+      <c r="X27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8386
+          <t xml:space="preserve">836
 </t>
         </is>
       </c>
@@ -4347,7 +4410,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4536
+          <t xml:space="preserve">453
 </t>
         </is>
       </c>
@@ -4357,12 +4420,7 @@
 </t>
         </is>
       </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">250
-</t>
-        </is>
-      </c>
+      <c r="E28" s="3" t="n"/>
       <c r="F28" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">219
@@ -4371,19 +4429,20 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15 8
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">028
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>33</t>
+          <t xml:space="preserve">33
+</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
@@ -4394,17 +4453,16 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">801
+          <t xml:space="preserve">01
 </t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
-        </is>
-      </c>
-      <c r="M28" s="3" t="inlineStr">
+          <t>461</t>
+        </is>
+      </c>
+      <c r="M28" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">150
 </t>
@@ -4412,31 +4470,31 @@
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8408
+          <t xml:space="preserve">8406
 </t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">801
-</t>
-        </is>
-      </c>
-      <c r="Q28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">068
+          <t xml:space="preserve">31
+</t>
+        </is>
+      </c>
+      <c r="Q28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -4446,10 +4504,15 @@
 </t>
         </is>
       </c>
-      <c r="T28" s="3" t="n"/>
-      <c r="U28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">621
+      <c r="T28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">747
+</t>
+        </is>
+      </c>
+      <c r="U28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
@@ -4459,15 +4522,15 @@
 </t>
         </is>
       </c>
-      <c r="W28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">268
+      <c r="W28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8641
 </t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
@@ -4479,7 +4542,7 @@
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
@@ -4498,7 +4561,7 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23436
+          <t xml:space="preserve">3436
 </t>
         </is>
       </c>
@@ -4508,7 +4571,7 @@
 </t>
         </is>
       </c>
-      <c r="E29" s="8" t="inlineStr">
+      <c r="E29" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">162
 </t>
@@ -4516,13 +4579,14 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101 4
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>918</t>
+          <t xml:space="preserve">98
+</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
@@ -4539,70 +4603,76 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">41
+</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09
+</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">152
+</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">865
+</t>
+        </is>
+      </c>
+      <c r="P29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="Q29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">220
+</t>
+        </is>
+      </c>
+      <c r="R29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">127
+</t>
+        </is>
+      </c>
+      <c r="S29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">216
+</t>
+        </is>
+      </c>
+      <c r="T29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">815
+</t>
+        </is>
+      </c>
+      <c r="U29" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">48
 </t>
         </is>
       </c>
-      <c r="K29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">09
-</t>
-        </is>
-      </c>
-      <c r="L29" s="3" t="inlineStr">
-        <is>
-          <t>466</t>
-        </is>
-      </c>
-      <c r="M29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">152
-</t>
-        </is>
-      </c>
-      <c r="N29" s="3" t="n"/>
-      <c r="O29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">865
-</t>
-        </is>
-      </c>
-      <c r="P29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26
-</t>
-        </is>
-      </c>
-      <c r="Q29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">220
-</t>
-        </is>
-      </c>
-      <c r="R29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">127
-</t>
-        </is>
-      </c>
-      <c r="S29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
-      </c>
-      <c r="T29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">215
-</t>
-        </is>
-      </c>
-      <c r="U29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">48
-</t>
-        </is>
-      </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">208
@@ -4615,9 +4685,9 @@
 </t>
         </is>
       </c>
-      <c r="X29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">069
+      <c r="X29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
@@ -4648,19 +4718,25 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>788</t>
+          <t xml:space="preserve">1788
+</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1121
-</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="n"/>
+          <t xml:space="preserve">1384
+</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">814
+</t>
+        </is>
+      </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">609
+          <t xml:space="preserve">1064
 </t>
         </is>
       </c>
@@ -4670,10 +4746,15 @@
 </t>
         </is>
       </c>
-      <c r="H30" s="3" t="n"/>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7107
+</t>
+        </is>
+      </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1100
+          <t xml:space="preserve">1890
 </t>
         </is>
       </c>
@@ -4703,31 +4784,37 @@
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">14345
+</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">5 82
 </t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">428
-</t>
-        </is>
-      </c>
-      <c r="R30" s="3" t="n"/>
+          <t xml:space="preserve">1142
+</t>
+        </is>
+      </c>
+      <c r="R30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2002
+</t>
+        </is>
+      </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21094
+          <t xml:space="preserve">1094
 </t>
         </is>
       </c>
@@ -4739,31 +4826,38 @@
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t>303</t>
+          <t xml:space="preserve">2303
+</t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16818
+          <t xml:space="preserve">1118
 </t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">918
+          <t xml:space="preserve">1918
 </t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">999
-</t>
-        </is>
-      </c>
-      <c r="Y30" s="3" t="n"/>
+          <t xml:space="preserve">9981
+</t>
+        </is>
+      </c>
+      <c r="Y30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4161
+</t>
+        </is>
+      </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t>004</t>
+          <t xml:space="preserve">200
+</t>
         </is>
       </c>
       <c r="AA30" s="3" t="inlineStr">
@@ -4781,30 +4875,31 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23577
-</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>963</t>
+          <t xml:space="preserve">3577
+</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">631
+</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
-        </is>
-      </c>
-      <c r="F31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">215
-</t>
-        </is>
-      </c>
-      <c r="G31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1100
+          <t xml:space="preserve">163
+</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">213
+</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
@@ -4814,46 +4909,46 @@
 </t>
         </is>
       </c>
-      <c r="I31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">261
+      <c r="I31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">961
 </t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 9
+          <t xml:space="preserve">28 9
 </t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
       <c r="L31" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">721
+          <t xml:space="preserve">3721
 </t>
         </is>
       </c>
       <c r="M31" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">0218101
+          <t xml:space="preserve">662
 </t>
         </is>
       </c>
       <c r="N31" s="3" t="n"/>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">909
+          <t xml:space="preserve">4 90
 </t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
@@ -4865,7 +4960,7 @@
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
@@ -4877,7 +4972,7 @@
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">784
+          <t xml:space="preserve">704
 </t>
         </is>
       </c>
@@ -4889,31 +4984,31 @@
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
-        </is>
-      </c>
-      <c r="W31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">841
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
+      <c r="W31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">832
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">401
+          <t xml:space="preserve">851
 </t>
         </is>
       </c>
@@ -4932,12 +5027,16 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2666
-</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="n"/>
-      <c r="E32" s="3" t="inlineStr">
+          <t>9566</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">264
+</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">171
 </t>
@@ -4945,49 +5044,38 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">21 7
 </t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">13 118
 </t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">214
-</t>
-        </is>
-      </c>
-      <c r="K32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="n"/>
+      <c r="K32" s="3" t="n"/>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>41</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
+          <t xml:space="preserve">157
 </t>
         </is>
       </c>
@@ -5003,49 +5091,44 @@
 </t>
         </is>
       </c>
-      <c r="P32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">62
-</t>
-        </is>
-      </c>
-      <c r="Q32" s="3" t="inlineStr">
+      <c r="P32" s="3" t="n"/>
+      <c r="Q32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">183
+</t>
+        </is>
+      </c>
+      <c r="R32" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">180
 </t>
         </is>
       </c>
-      <c r="R32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="S32" s="8" t="inlineStr">
+      <c r="S32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184415 18
+</t>
+        </is>
+      </c>
+      <c r="T32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">980
+</t>
+        </is>
+      </c>
+      <c r="U32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07
+</t>
+        </is>
+      </c>
+      <c r="V32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">204
 </t>
         </is>
       </c>
-      <c r="T32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
-      <c r="U32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">107
-</t>
-        </is>
-      </c>
-      <c r="V32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">175
-</t>
-        </is>
-      </c>
-      <c r="W32" s="3" t="inlineStr">
+      <c r="W32" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">169
 </t>
@@ -5065,7 +5148,7 @@
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">1175
 </t>
         </is>
       </c>
@@ -5100,9 +5183,9 @@
 </t>
         </is>
       </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">217
+      <c r="F33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">251
 </t>
         </is>
       </c>
@@ -5120,10 +5203,15 @@
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="J33" s="3" t="n"/>
+          <t>861</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">58
@@ -5138,25 +5226,25 @@
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">147
 </t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
+          <t xml:space="preserve">780
 </t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">43
 </t>
         </is>
       </c>
@@ -5186,11 +5274,11 @@
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
-        </is>
-      </c>
-      <c r="V33" s="3" t="inlineStr">
+          <t xml:space="preserve">87
+</t>
+        </is>
+      </c>
+      <c r="V33" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">196
 </t>
@@ -5210,13 +5298,13 @@
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">868
+          <t xml:space="preserve">2865
 </t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
@@ -5235,7 +5323,7 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23502
+          <t xml:space="preserve">3502
 </t>
         </is>
       </c>
@@ -5259,50 +5347,55 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">656
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">97
+</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">175
+</t>
+        </is>
+      </c>
+      <c r="M34" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">18
 </t>
         </is>
       </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">397
-</t>
-        </is>
-      </c>
-      <c r="K34" s="3" t="n"/>
-      <c r="L34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">175
-</t>
-        </is>
-      </c>
-      <c r="M34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
-      <c r="N34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">119
-</t>
-        </is>
-      </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">910
 </t>
         </is>
       </c>
@@ -5314,7 +5407,8 @@
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t xml:space="preserve">293
+</t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
@@ -5323,7 +5417,12 @@
 </t>
         </is>
       </c>
-      <c r="S34" s="3" t="n"/>
+      <c r="S34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">748
@@ -5332,7 +5431,7 @@
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">72
 </t>
         </is>
       </c>
@@ -5362,7 +5461,7 @@
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
@@ -5405,7 +5504,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
@@ -5433,26 +5532,27 @@
 </t>
         </is>
       </c>
-      <c r="L35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
+      <c r="L35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">886
 </t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t xml:space="preserve">18
+</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">800
 </t>
         </is>
       </c>
@@ -5470,46 +5570,46 @@
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
-        </is>
-      </c>
-      <c r="S35" s="3" t="inlineStr">
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="S35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">281
+</t>
+        </is>
+      </c>
+      <c r="T35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">860
+</t>
+        </is>
+      </c>
+      <c r="U35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">67
+</t>
+        </is>
+      </c>
+      <c r="V35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201
+</t>
+        </is>
+      </c>
+      <c r="W35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="X35" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">211
 </t>
         </is>
       </c>
-      <c r="T35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">860
-</t>
-        </is>
-      </c>
-      <c r="U35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
-      <c r="V35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
-      </c>
-      <c r="W35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="X35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">211
-</t>
-        </is>
-      </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">895
@@ -5518,7 +5618,7 @@
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -5537,7 +5637,7 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3568
+          <t xml:space="preserve">356
 </t>
         </is>
       </c>
@@ -5565,9 +5665,9 @@
 </t>
         </is>
       </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">137
+      <c r="H36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
@@ -5579,7 +5679,7 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
+          <t xml:space="preserve">31
 </t>
         </is>
       </c>
@@ -5601,10 +5701,15 @@
 </t>
         </is>
       </c>
-      <c r="N36" s="3" t="n"/>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">136
+</t>
+        </is>
+      </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">270
 </t>
         </is>
       </c>
@@ -5634,7 +5739,7 @@
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">602
+          <t xml:space="preserve">1682
 </t>
         </is>
       </c>
@@ -5646,13 +5751,13 @@
       </c>
       <c r="V36" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">808
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
@@ -5670,7 +5775,7 @@
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">418
 </t>
         </is>
       </c>
@@ -5689,25 +5794,25 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16452
+          <t xml:space="preserve">1643
 </t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11828
+          <t xml:space="preserve">2314
 </t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">821
+          <t xml:space="preserve">829
 </t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16091
+          <t xml:space="preserve">1071
 </t>
         </is>
       </c>
@@ -5725,95 +5830,101 @@
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1167
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">105
+</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="n"/>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1606
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
-</t>
-        </is>
-      </c>
-      <c r="M37" s="3" t="n"/>
+          <t xml:space="preserve">885
+</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">868
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2280
+          <t xml:space="preserve">8998
 </t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1208
+          <t xml:space="preserve">0120
 </t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18123
+          <t xml:space="preserve">2229
 </t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">911
+          <t xml:space="preserve">991
 </t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1008
+          <t xml:space="preserve">1038
 </t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2894
+          <t xml:space="preserve">93834
 </t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">942
-</t>
-        </is>
-      </c>
-      <c r="V37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">981
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">342
+</t>
+        </is>
+      </c>
+      <c r="V37" s="3" t="n"/>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t>914</t>
-        </is>
-      </c>
-      <c r="X37" s="3" t="n"/>
+          <t xml:space="preserve">9231
+</t>
+        </is>
+      </c>
+      <c r="X37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">029
+</t>
+        </is>
+      </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4188
-</t>
-        </is>
-      </c>
-      <c r="Z37" s="3" t="n"/>
+          <t xml:space="preserve">2187
+</t>
+        </is>
+      </c>
+      <c r="Z37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -5829,30 +5940,31 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12928
+          <t xml:space="preserve">3296
 </t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="inlineStr">
-        <is>
-          <t>6341</t>
+          <t xml:space="preserve">263
+</t>
+        </is>
+      </c>
+      <c r="E38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">661
+</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
@@ -5862,40 +5974,40 @@
 </t>
         </is>
       </c>
-      <c r="I38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">211
-</t>
-        </is>
-      </c>
+      <c r="I38" s="3" t="n"/>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">331
+          <t xml:space="preserve">33
 </t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
-</t>
-        </is>
-      </c>
-      <c r="L38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">177
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="L38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6889
 </t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
-        </is>
-      </c>
-      <c r="N38" s="3" t="n"/>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">162
+</t>
+        </is>
+      </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7961
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
@@ -5905,20 +6017,21 @@
 </t>
         </is>
       </c>
-      <c r="Q38" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
+      <c r="Q38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2251
+</t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="S38" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">0971
 </t>
         </is>
       </c>
@@ -5928,32 +6041,42 @@
 </t>
         </is>
       </c>
-      <c r="U38" s="3" t="n"/>
-      <c r="V38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="W38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">183
-</t>
-        </is>
-      </c>
-      <c r="X38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">206
+      <c r="U38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="V38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">904
+</t>
+        </is>
+      </c>
+      <c r="W38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">898
+</t>
+        </is>
+      </c>
+      <c r="X38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">005
 </t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">897
-</t>
-        </is>
-      </c>
-      <c r="Z38" s="3" t="n"/>
+          <t xml:space="preserve">89718
+</t>
+        </is>
+      </c>
+      <c r="Z38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">149
+</t>
+        </is>
+      </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -5969,80 +6092,78 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>9864</t>
+          <t xml:space="preserve">2644
+</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>854</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="G39" s="3" t="n"/>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>331</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">800
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
-        </is>
-      </c>
-      <c r="M39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">171
-</t>
-        </is>
-      </c>
-      <c r="N39" s="3" t="n"/>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="M39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
-</t>
-        </is>
-      </c>
-      <c r="P39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">36
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">850
+</t>
+        </is>
+      </c>
+      <c r="P39" s="3" t="n"/>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">298
 </t>
         </is>
       </c>
@@ -6054,31 +6175,36 @@
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
-</t>
-        </is>
-      </c>
-      <c r="T39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">744
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">231
+</t>
+        </is>
+      </c>
+      <c r="T39" s="3" t="n"/>
       <c r="U39" s="3" t="n"/>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="X39" s="3" t="n"/>
-      <c r="Y39" s="3" t="n"/>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
+      <c r="X39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">183
+</t>
+        </is>
+      </c>
+      <c r="Y39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">889
+</t>
+        </is>
+      </c>
       <c r="Z39" s="3" t="n"/>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -6095,30 +6221,35 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3590
+          <t xml:space="preserve">2864
 </t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
-        </is>
-      </c>
-      <c r="F40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1816
-</t>
-        </is>
-      </c>
-      <c r="G40" s="3" t="n"/>
-      <c r="H40" s="8" t="inlineStr">
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">287
+</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">138
 </t>
@@ -6126,25 +6257,25 @@
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="L40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">079
 </t>
         </is>
       </c>
@@ -6156,78 +6287,79 @@
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">6
 </t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">762
+          <t xml:space="preserve">825
 </t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
-        </is>
-      </c>
-      <c r="S40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
+      <c r="S40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">684
-</t>
-        </is>
-      </c>
-      <c r="U40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">744
+</t>
+        </is>
+      </c>
+      <c r="U40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
       <c r="V40" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">200
+</t>
         </is>
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">862
+          <t xml:space="preserve">897
 </t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">324
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
@@ -6246,129 +6378,138 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>48664</t>
+          <t xml:space="preserve">3590
+</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
-</t>
+          <t>515</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
-</t>
-        </is>
-      </c>
-      <c r="G41" s="3" t="n"/>
-      <c r="H41" s="3" t="n"/>
-      <c r="I41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">205
+</t>
+        </is>
+      </c>
+      <c r="G41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0169
+</t>
+        </is>
+      </c>
+      <c r="H41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">138
+</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="n"/>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">63
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
-        </is>
-      </c>
-      <c r="M41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">157
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="M41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">553
 </t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">762
 </t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
-        </is>
-      </c>
-      <c r="Q41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">48
+</t>
+        </is>
+      </c>
+      <c r="Q41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="S41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">202
+</t>
+        </is>
+      </c>
+      <c r="S41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">094
 </t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">579
-</t>
-        </is>
-      </c>
-      <c r="U41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">614
+</t>
+        </is>
+      </c>
+      <c r="U41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
-</t>
-        </is>
-      </c>
-      <c r="W41" s="3" t="n"/>
+          <t>044</t>
+        </is>
+      </c>
+      <c r="W41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">734
+          <t xml:space="preserve">862
 </t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">94
 </t>
         </is>
       </c>
@@ -6387,44 +6528,43 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2426
-</t>
+          <t>48561</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
+          <t xml:space="preserve">283
 </t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
       <c r="I42" s="3" t="n"/>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">63
 </t>
         </is>
       </c>
@@ -6436,7 +6576,7 @@
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">177
 </t>
         </is>
       </c>
@@ -6448,68 +6588,73 @@
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">798
+          <t xml:space="preserve">6820
 </t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="S42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">125
+</t>
+        </is>
+      </c>
+      <c r="T42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">579
+</t>
+        </is>
+      </c>
+      <c r="U42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">141
+</t>
+        </is>
+      </c>
+      <c r="V42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">233
+</t>
+        </is>
+      </c>
+      <c r="W42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="X42" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">202
 </t>
         </is>
       </c>
-      <c r="S42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">899
-</t>
-        </is>
-      </c>
-      <c r="T42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">555
-</t>
-        </is>
-      </c>
-      <c r="U42" s="3" t="n"/>
-      <c r="V42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="W42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="X42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">197
-</t>
-        </is>
-      </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
+          <t xml:space="preserve">285
 </t>
         </is>
       </c>
@@ -6534,133 +6679,143 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6
-</t>
-        </is>
-      </c>
-      <c r="D43" s="8" t="inlineStr">
+          <t xml:space="preserve">7426
+</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">276
+</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">175
+</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">225
+</t>
+        </is>
+      </c>
+      <c r="G43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">885
+</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="n"/>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">66
+</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">880
+</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">157
+</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="O43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">798
+</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">140
+</t>
+        </is>
+      </c>
+      <c r="Q43" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">281
 </t>
         </is>
       </c>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">809
-</t>
-        </is>
-      </c>
-      <c r="F43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">081
-</t>
-        </is>
-      </c>
-      <c r="G43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">525
-</t>
-        </is>
-      </c>
-      <c r="H43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">094
-</t>
-        </is>
-      </c>
-      <c r="I43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">618
-</t>
-        </is>
-      </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">268
-</t>
-        </is>
-      </c>
-      <c r="K43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="L43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">902
-</t>
-        </is>
-      </c>
-      <c r="M43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">796
-</t>
-        </is>
-      </c>
-      <c r="N43" s="3" t="n"/>
-      <c r="O43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4055
-</t>
-        </is>
-      </c>
-      <c r="P43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
-      <c r="Q43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">221
-</t>
-        </is>
-      </c>
-      <c r="R43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">616
+      <c r="R43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10 9
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
-        </is>
-      </c>
-      <c r="U43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">556
-</t>
-        </is>
-      </c>
-      <c r="V43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">048
-</t>
-        </is>
-      </c>
-      <c r="W43" s="3" t="n"/>
-      <c r="X43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">555
+</t>
+        </is>
+      </c>
+      <c r="U43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
+      <c r="V43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222
+</t>
+        </is>
+      </c>
+      <c r="W43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="X43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
-        </is>
-      </c>
-      <c r="Z43" s="3" t="n"/>
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
+      <c r="Z43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">71
+</t>
+        </is>
+      </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
           <t>30</t>
@@ -6718,143 +6873,143 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3629
+          <t xml:space="preserve">18890
 </t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">164
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1344
+</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="n"/>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">1081
 </t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">595
 </t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">697
 </t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
+          <t xml:space="preserve">1174
 </t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">52
+          <t xml:space="preserve">861
 </t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">909
 </t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15 9
+          <t xml:space="preserve">537
 </t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">016
+          <t xml:space="preserve">710
 </t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
+          <t xml:space="preserve">14055
 </t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">851
+          <t xml:space="preserve">12684
 </t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028
+          <t xml:space="preserve">1018
 </t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">1048
 </t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">660
+          <t xml:space="preserve">3300
 </t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">556
 </t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">1048
 </t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">985
 </t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">1182
 </t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
-      <c r="Z45" s="3" t="n"/>
+          <t xml:space="preserve">1088
+</t>
+        </is>
+      </c>
+      <c r="Z45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -6868,115 +7023,149 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C46" s="3" t="n"/>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3629
+</t>
+        </is>
+      </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">164
+</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">816
+</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>4398</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">85
+</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">52
+</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="M46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">659
+</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">811
+</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">99
+</t>
+        </is>
+      </c>
+      <c r="Q46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">251
+</t>
+        </is>
+      </c>
+      <c r="R46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">809
+</t>
+        </is>
+      </c>
+      <c r="S46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
+      <c r="T46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">814
+</t>
+        </is>
+      </c>
+      <c r="U46" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">1
 </t>
         </is>
       </c>
-      <c r="F46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
-      </c>
-      <c r="G46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">171
-</t>
-        </is>
-      </c>
-      <c r="H46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">104
-</t>
-        </is>
-      </c>
-      <c r="I46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">46
-</t>
-        </is>
-      </c>
-      <c r="K46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">48
-</t>
-        </is>
-      </c>
-      <c r="L46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="M46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">159
-</t>
-        </is>
-      </c>
-      <c r="N46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">169
-</t>
-        </is>
-      </c>
-      <c r="O46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2
-</t>
-        </is>
-      </c>
-      <c r="P46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="Q46" s="3" t="n"/>
-      <c r="R46" s="3" t="n"/>
-      <c r="S46" s="3" t="n"/>
-      <c r="T46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="U46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
-      </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="X46" s="3" t="n"/>
-      <c r="Y46" s="3" t="n"/>
-      <c r="Z46" s="3" t="n"/>
+          <t xml:space="preserve">4
+</t>
+        </is>
+      </c>
+      <c r="X46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
+      <c r="Y46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
+      <c r="Z46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>

--- a/results/05_transient_transcription_output/905/905_197311_SF.JPG_stage_digit_manipulation.xlsx
+++ b/results/05_transient_transcription_output/905/905_197311_SF.JPG_stage_digit_manipulation.xlsx
@@ -26,18 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FF9933"/>
-        <bgColor rgb="00FF9933"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="9">
@@ -107,7 +101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -122,9 +116,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -737,140 +728,117 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3898
-</t>
+          <t>3898</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">883
-</t>
+          <t>283</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
-</t>
+          <t>55</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
-        </is>
-      </c>
-      <c r="M4" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>168</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2900
-</t>
+          <t>900</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">851
-</t>
+          <t>851</t>
         </is>
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
+          <t>43</t>
         </is>
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">861
-</t>
+          <t>861</t>
         </is>
       </c>
       <c r="Z4" s="3" t="n"/>
@@ -889,8 +857,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4386
-</t>
+          <t>326</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -900,8 +867,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -909,124 +875,104 @@
           <t>425</t>
         </is>
       </c>
-      <c r="G5" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
-      <c r="H5" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1210
-</t>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>120</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
+          <t>123</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">931
-</t>
+          <t>931</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
-</t>
+          <t>233</t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">843
-</t>
+          <t>743</t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
-</t>
+          <t>80</t>
         </is>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
-        </is>
-      </c>
-      <c r="X5" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
-</t>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t>191</t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>920</t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AA5" s="3" t="inlineStr">
@@ -1044,141 +990,118 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4944
-</t>
+          <t>4844</t>
         </is>
       </c>
       <c r="D6" s="3" t="n"/>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
-        </is>
-      </c>
-      <c r="H6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">252
-</t>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>152</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
+          <t>57</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>920</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">690
-</t>
+          <t>690</t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
+          <t>109</t>
         </is>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
-        </is>
-      </c>
-      <c r="W6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192
-</t>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="W6" s="3" t="inlineStr">
+        <is>
+          <t>192</t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
-</t>
+          <t>910</t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AA6" s="3" t="inlineStr">
@@ -1196,141 +1119,118 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3844
-</t>
+          <t>3744</t>
         </is>
       </c>
       <c r="D7" s="3" t="n"/>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>120</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">898
-</t>
+          <t>898</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
-</t>
+          <t>273</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>687</t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
-</t>
+          <t>910</t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="AA7" s="3" t="inlineStr">
@@ -1348,146 +1248,122 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4602
-</t>
+          <t>602</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
-</t>
+          <t>284</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
-</t>
+          <t>41</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">882
-</t>
+          <t>882</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">871
-</t>
+          <t>871</t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
-</t>
+          <t>39</t>
         </is>
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
-</t>
+          <t>900</t>
         </is>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">860
-</t>
+          <t>860</t>
         </is>
       </c>
       <c r="AA8" s="3" t="inlineStr">
@@ -1505,56 +1381,47 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22404
-</t>
+          <t>1404</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1420
-</t>
+          <t>1420</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8291
-</t>
+          <t>8291</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2591
-</t>
+          <t>591</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6717
-</t>
+          <t>677</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
@@ -1564,81 +1431,68 @@
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">845
-</t>
+          <t>845</t>
         </is>
       </c>
       <c r="N9" s="3" t="n"/>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3433
-</t>
+          <t>3453</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
-</t>
+          <t>94</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12721
-</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1109
-</t>
+          <t>1109</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1243
-</t>
+          <t>1243</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3842
-</t>
+          <t>3842</t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">385
-</t>
+          <t>385</t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
-</t>
+          <t>989</t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">927
-</t>
+          <t>927</t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">638
-</t>
+          <t>031</t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4451
-</t>
+          <t>4451</t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="AA9" s="3" t="inlineStr">
@@ -1656,141 +1510,118 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4281
-</t>
+          <t>281</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
-</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">661
-</t>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>1661</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="H10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">185
-</t>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>135</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">821
-</t>
+          <t>321</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
-      <c r="L10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">179
-</t>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>179</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="N10" s="3" t="n"/>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">906
-</t>
+          <t>906</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104 14
-</t>
+          <t>101 14</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">769
-</t>
+          <t>768</t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
-</t>
+          <t>77</t>
         </is>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
+          <t>890</t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16 14
-</t>
+          <t>21 14</t>
         </is>
       </c>
       <c r="AA10" s="3" t="inlineStr">
@@ -1808,44 +1639,37 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2996
-</t>
+          <t>2996</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
-</t>
+          <t>265</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
-        </is>
-      </c>
-      <c r="I11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">928
-</t>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>28</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1856,87 +1680,73 @@
       <c r="K11" s="3" t="n"/>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P11" s="3" t="n"/>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">684
-</t>
+          <t>684</t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="X11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8220
-</t>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t>220</t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">845
-</t>
+          <t>845</t>
         </is>
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AA11" s="3" t="inlineStr">
@@ -1954,146 +1764,122 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3436
-</t>
+          <t>3436</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-</t>
+          <t>269</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
-</t>
+          <t>91</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
-      <c r="L12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">814
-</t>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>184</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
-</t>
+          <t>921</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
-        </is>
-      </c>
-      <c r="R12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
-      <c r="S12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222
-</t>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr">
+        <is>
+          <t>222</t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">930
-</t>
+          <t>930</t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">891
-</t>
+          <t>891</t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AA12" s="3" t="inlineStr">
@@ -2111,141 +1897,118 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3238
-</t>
+          <t>3238</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
-</t>
+          <t>275</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
-        </is>
-      </c>
-      <c r="G13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">105
-</t>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>105</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="I13" s="3" t="n"/>
-      <c r="J13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">210
-</t>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>22</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
-        </is>
-      </c>
-      <c r="M13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">169
-</t>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>169</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
-</t>
+          <t>922</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
-</t>
+          <t>775</t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">958
-</t>
+          <t>958</t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
+          <t>09</t>
         </is>
       </c>
       <c r="AA13" s="3" t="inlineStr">
@@ -2263,141 +2026,118 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2600
-</t>
+          <t>2600</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8211
-</t>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>211</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="I14" s="3" t="n"/>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 2
-</t>
+          <t>21 2</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">896
-</t>
+          <t>896</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
-        </is>
-      </c>
-      <c r="S14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">238
-</t>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr">
+        <is>
+          <t>238</t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">956
-</t>
+          <t>956</t>
         </is>
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="AA14" s="3" t="inlineStr">
@@ -2415,146 +2155,122 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3348
-</t>
+          <t>8348</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
-</t>
+          <t>283</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
-      <c r="F15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">085
-</t>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>225</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>117</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">986
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
-</t>
+          <t>940</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>276</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">593
-</t>
-        </is>
-      </c>
-      <c r="U15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">160
-</t>
+          <t>593</t>
+        </is>
+      </c>
+      <c r="U15" s="3" t="inlineStr">
+        <is>
+          <t>150</t>
         </is>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>910</t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AA15" s="3" t="inlineStr">
@@ -2572,140 +2288,117 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13618
-</t>
+          <t>15618</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1340
-</t>
+          <t>1340</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">856
-</t>
+          <t>856</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1099
-</t>
+          <t>1099</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4814
-</t>
+          <t>284</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">730
-</t>
+          <t>730</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">926
-</t>
+          <t>321</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
-</t>
+          <t>888</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">853
-</t>
+          <t>853</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>95</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14659
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
-</t>
+          <t>69</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10893
-</t>
+          <t>1193</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1043
-</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21166
-</t>
+          <t>1146</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1998
-</t>
+          <t>3938</t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">351
-</t>
+          <t>351</t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1019
-</t>
+          <t>1019</t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9691
-</t>
+          <t>969</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0987
-</t>
+          <t>097</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4584
-</t>
+          <t>4574</t>
         </is>
       </c>
       <c r="Z16" s="3" t="n"/>
@@ -2724,146 +2417,122 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23124
-</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">401
-</t>
+          <t>3124</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>268</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">297
-</t>
+          <t>297</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">932
-</t>
+          <t>932</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
-        </is>
-      </c>
-      <c r="R17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1891
-</t>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t>229</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7891
-</t>
+          <t>788</t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">70
-</t>
-        </is>
-      </c>
-      <c r="V17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2116
-</t>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="V17" s="3" t="inlineStr">
+        <is>
+          <t>204</t>
         </is>
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28 12 1
-</t>
+          <t>28 8 1</t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AA17" s="3" t="inlineStr">
@@ -2881,38 +2550,32 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3546
-</t>
+          <t>3546</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">277
-</t>
+          <t>277</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
-        </is>
-      </c>
-      <c r="F18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">909
-</t>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>223</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
-        </is>
-      </c>
-      <c r="H18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">150
-</t>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>150</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
@@ -2927,38 +2590,32 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
-</t>
+          <t>871</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>27</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
@@ -2968,56 +2625,47 @@
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
-</t>
+          <t>233</t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1665
-</t>
+          <t>665</t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>117</t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224 884
-</t>
+          <t>224 214</t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11 11
-</t>
+          <t>28 12</t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="AA18" s="3" t="inlineStr">
@@ -3035,146 +2683,122 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
-</t>
+          <t>274</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">874
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
-</t>
+          <t>940</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
-        </is>
-      </c>
-      <c r="S19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">086
-</t>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="S19" s="3" t="inlineStr">
+        <is>
+          <t>216</t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
+          <t>731</t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>79</t>
         </is>
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
-</t>
+          <t>234</t>
         </is>
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>736</t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
-</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AA19" s="3" t="inlineStr">
@@ -3195,34 +2819,29 @@
           <t>3588</t>
         </is>
       </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">268
-</t>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>268</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
@@ -3232,104 +2851,87 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">531
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
-        </is>
-      </c>
-      <c r="S20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">247
-</t>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="S20" s="3" t="inlineStr">
+        <is>
+          <t>247</t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18918
-</t>
+          <t>890</t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">938
-</t>
+          <t>938</t>
         </is>
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AA20" s="3" t="inlineStr">
@@ -3347,8 +2949,7 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22842
-</t>
+          <t>2846</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -3358,129 +2959,108 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
-        </is>
-      </c>
-      <c r="G21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">718
-</t>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>111</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
-</t>
+          <t>940</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q21" s="3" t="n"/>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">911
-</t>
+          <t>911</t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">968
-</t>
+          <t>968</t>
         </is>
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="AA21" s="3" t="inlineStr">
@@ -3498,146 +3078,122 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3392
-</t>
+          <t>3392</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">976
-</t>
+          <t>276</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">923
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
-</t>
+          <t>251</t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7240
-</t>
+          <t>740</t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
-</t>
+          <t>83</t>
         </is>
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">691
-</t>
+          <t>691</t>
         </is>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
-</t>
+          <t>87</t>
         </is>
       </c>
       <c r="AA22" s="3" t="inlineStr">
@@ -3655,56 +3211,47 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15426
-</t>
+          <t>15486</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1376
-</t>
+          <t>1376</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
-</t>
+          <t>850</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3526
-</t>
+          <t>526</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">748
-</t>
+          <t>742</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
@@ -3714,14 +3261,12 @@
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">878
-</t>
+          <t>872</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
-</t>
+          <t>94</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
@@ -3734,50 +3279,42 @@
       <c r="R23" s="3" t="n"/>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2158
-</t>
+          <t>1158</t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2931
-</t>
+          <t>937</t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">332
-</t>
+          <t>332</t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1103
-</t>
+          <t>1103</t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">996
-</t>
+          <t>996</t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1109
-</t>
+          <t>1034</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6068
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="AA23" s="3" t="inlineStr">
@@ -3795,56 +3332,47 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3097
-</t>
+          <t>3097</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
-</t>
-        </is>
-      </c>
-      <c r="E24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">701
-</t>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>170</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
-</t>
-        </is>
-      </c>
-      <c r="H24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1848
-</t>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>148</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
@@ -3854,86 +3382,72 @@
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">938
-</t>
+          <t>938</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
-      </c>
-      <c r="Q24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">391
-</t>
-        </is>
-      </c>
-      <c r="R24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">101
-</t>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="Q24" s="3" t="inlineStr">
+        <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="R24" s="3" t="inlineStr">
+        <is>
+          <t>210</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">787
-</t>
+          <t>787</t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
-</t>
+          <t>281</t>
         </is>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
-      <c r="X24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">81811
-</t>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="X24" s="3" t="inlineStr">
+        <is>
+          <t>21</t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">824
-</t>
+          <t>834</t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AA24" s="3" t="inlineStr">
@@ -3956,58 +3470,49 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
+          <t>247</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
-</t>
+          <t>73</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="I25" s="3" t="n"/>
       <c r="J25" s="3" t="n"/>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">51
-</t>
-        </is>
-      </c>
-      <c r="L25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="M25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">182
-</t>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>182</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
@@ -4017,68 +3522,57 @@
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">825
-</t>
+          <t>825</t>
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
-</t>
-        </is>
-      </c>
-      <c r="V25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">117
-</t>
-        </is>
-      </c>
-      <c r="W25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">514
-</t>
-        </is>
-      </c>
-      <c r="X25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">544
-</t>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="V25" s="3" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="W25" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X25" s="3" t="inlineStr">
+        <is>
+          <t>555</t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="AA25" s="3" t="inlineStr">
@@ -4096,146 +3590,122 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3411
-</t>
+          <t>3414</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>129</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
+          <t>167</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
-      </c>
-      <c r="S26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">246
-</t>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="S26" s="3" t="inlineStr">
+        <is>
+          <t>246</t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">839
-</t>
+          <t>839</t>
         </is>
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">47
-</t>
-        </is>
-      </c>
-      <c r="V26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">206
-</t>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="V26" s="3" t="inlineStr">
+        <is>
+          <t>206</t>
         </is>
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>920</t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AA26" s="3" t="inlineStr">
@@ -4253,146 +3723,122 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3700
-</t>
+          <t>3700</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
+          <t>167</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">930
-</t>
+          <t>930</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
+          <t>255</t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">696
-</t>
+          <t>696</t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="X27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">207
-</t>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="X27" s="3" t="inlineStr">
+        <is>
+          <t>207</t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">836
-</t>
+          <t>836</t>
         </is>
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AA27" s="3" t="inlineStr">
@@ -4410,51 +3856,43 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">453
-</t>
+          <t>4536</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>288</t>
         </is>
       </c>
       <c r="E28" s="3" t="n"/>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
-        </is>
-      </c>
-      <c r="H28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
-</t>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>128</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">53
-</t>
+          <t>53</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
@@ -4462,88 +3900,74 @@
           <t>461</t>
         </is>
       </c>
-      <c r="M28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">150
-</t>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>150</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8406
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">747
-</t>
+          <t>747</t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-</t>
+          <t>62</t>
         </is>
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="W28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8641
-</t>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="W28" s="3" t="inlineStr">
+        <is>
+          <t>164</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">775
-</t>
+          <t>775</t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
-</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AA28" s="3" t="inlineStr">
@@ -4561,146 +3985,122 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3436
-</t>
+          <t>3436</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>263</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
-</t>
+          <t>41</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
+          <t>09</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">865
-</t>
+          <t>865</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
-        </is>
-      </c>
-      <c r="S29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">216
-</t>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="S29" s="3" t="inlineStr">
+        <is>
+          <t>216</t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">815
-</t>
+          <t>815</t>
         </is>
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
-</t>
+          <t>880</t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AA29" s="3" t="inlineStr">
@@ -4718,146 +4118,122 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1788
-</t>
+          <t>17884</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1384
-</t>
+          <t>1314</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">814
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1064
-</t>
+          <t>1064</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">500
-</t>
+          <t>500</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7107
-</t>
+          <t>707</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1890
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
-</t>
+          <t>79</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">859
-</t>
+          <t>859</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">812
-</t>
+          <t>812</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>87</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14345
-</t>
+          <t>4545</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5 82
-</t>
+          <t>2 89</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1142
-</t>
+          <t>1142</t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2002
-</t>
+          <t>1002</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1094
-</t>
+          <t>1094</t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3222
-</t>
+          <t>922</t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2303
-</t>
+          <t>303</t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
-</t>
+          <t>1018</t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1918
-</t>
+          <t>918</t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9981
-</t>
+          <t>999</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4161
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="AA30" s="3" t="inlineStr">
@@ -4875,141 +4251,118 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3577
-</t>
-        </is>
-      </c>
-      <c r="D31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">631
-</t>
+          <t>3577</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>2631</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
-</t>
+          <t>163</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
-        </is>
-      </c>
-      <c r="I31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">961
-</t>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>26</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28 9
-</t>
+          <t>8 9</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
-</t>
-        </is>
-      </c>
-      <c r="L31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3721
-</t>
-        </is>
-      </c>
-      <c r="M31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">662
-</t>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>1721</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>162</t>
         </is>
       </c>
       <c r="N31" s="3" t="n"/>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4 90
-</t>
+          <t>12 90</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">704
-</t>
+          <t>784</t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
-</t>
+          <t>61</t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>251</t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">851
-</t>
+          <t>832</t>
         </is>
       </c>
       <c r="AA31" s="3" t="inlineStr">
@@ -5032,38 +4385,32 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
-        </is>
-      </c>
-      <c r="E32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">171
-</t>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>171</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21 7
-</t>
+          <t>21 7</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>93</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13 118
-</t>
+          <t>13 15</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J32" s="3" t="n"/>
@@ -5075,81 +4422,68 @@
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
+          <t>157</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>720</t>
         </is>
       </c>
       <c r="P32" s="3" t="n"/>
-      <c r="Q32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">183
-</t>
-        </is>
-      </c>
-      <c r="R32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
+      <c r="Q32" s="3" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="R32" s="3" t="inlineStr">
+        <is>
+          <t>180</t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184415 18
-</t>
+          <t>158 8</t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
-      <c r="W32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">169
-</t>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="W32" s="3" t="inlineStr">
+        <is>
+          <t>169</t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
-</t>
+          <t>940</t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1175
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="AA32" s="3" t="inlineStr">
@@ -5167,38 +4501,32 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4008
-</t>
+          <t>4008</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
-</t>
+          <t>273</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
-        </is>
-      </c>
-      <c r="F33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">251
-</t>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>217</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
@@ -5208,104 +4536,87 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
-</t>
+          <t>58</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">780
-</t>
+          <t>780</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">43
-</t>
+          <t>43</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">774
-</t>
+          <t>774</t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
-</t>
-        </is>
-      </c>
-      <c r="V33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="W33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">280
-</t>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="V33" s="3" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="W33" s="3" t="inlineStr">
+        <is>
+          <t>180</t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2865
-</t>
+          <t>860</t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AA33" s="3" t="inlineStr">
@@ -5323,146 +4634,122 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3502
-</t>
+          <t>3502</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="H34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">156
-</t>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>156</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
-</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
-        </is>
-      </c>
-      <c r="M34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">166
-</t>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>166</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
-</t>
+          <t>910</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
-</t>
+          <t>233</t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">748
-</t>
+          <t>748</t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
-</t>
+          <t>72</t>
         </is>
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
-</t>
+          <t>840</t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AA34" s="3" t="inlineStr">
@@ -5480,146 +4767,122 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2688
-</t>
+          <t>2688</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>82</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">886
-</t>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>186</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">800
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="S35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">281
-</t>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="S35" s="3" t="inlineStr">
+        <is>
+          <t>211</t>
         </is>
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">860
-</t>
+          <t>760</t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">67
-</t>
+          <t>67</t>
         </is>
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">895
-</t>
+          <t>895</t>
         </is>
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AA35" s="3" t="inlineStr">
@@ -5637,146 +4900,122 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">356
-</t>
+          <t>3568</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
-</t>
+          <t>281</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
-        </is>
-      </c>
-      <c r="H36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">134
-</t>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>134</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>131</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
-</t>
+          <t>770</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
-</t>
+          <t>267</t>
         </is>
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1682
-</t>
+          <t>602</t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
-        </is>
-      </c>
-      <c r="V36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">208
-</t>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="V36" s="3" t="inlineStr">
+        <is>
+          <t>202</t>
         </is>
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">952
-</t>
+          <t>952</t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">418
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AA36" s="3" t="inlineStr">
@@ -5794,44 +5033,37 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1643
-</t>
+          <t>6432</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2314
-</t>
+          <t>1314</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">829
-</t>
+          <t>829</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1071
-</t>
+          <t>1071</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">485
-</t>
+          <t>485</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7106
-</t>
+          <t>706</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
-</t>
+          <t>105</t>
         </is>
       </c>
       <c r="J37" s="3" t="n"/>
@@ -5842,87 +5074,73 @@
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
-</t>
+          <t>883</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>770</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>80</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8998
-</t>
+          <t>398</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0120
-</t>
+          <t>020</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2229
-</t>
+          <t>1125</t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">991
-</t>
+          <t>971</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1038
-</t>
+          <t>1038</t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93834
-</t>
+          <t>3854</t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">342
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="V37" s="3" t="n"/>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">029
-</t>
+          <t>029</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2187
-</t>
+          <t>487</t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AA37" s="3" t="inlineStr">
@@ -5940,141 +5158,118 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3296
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
-        </is>
-      </c>
-      <c r="E38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">661
-</t>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>166</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="I38" s="3" t="n"/>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="L38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6889
-</t>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>177</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
-</t>
-        </is>
-      </c>
-      <c r="Q38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2251
-</t>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="Q38" s="3" t="inlineStr">
+        <is>
+          <t>225</t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
-      <c r="S38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0971
-</t>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="S38" s="3" t="inlineStr">
+        <is>
+          <t>208</t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">771
-</t>
+          <t>771</t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="V38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">904
-</t>
-        </is>
-      </c>
-      <c r="W38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">898
-</t>
-        </is>
-      </c>
-      <c r="X38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">005
-</t>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="V38" s="3" t="inlineStr">
+        <is>
+          <t>1961</t>
+        </is>
+      </c>
+      <c r="W38" s="3" t="inlineStr">
+        <is>
+          <t>1851</t>
+        </is>
+      </c>
+      <c r="X38" s="3" t="inlineStr">
+        <is>
+          <t>202</t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89718
-</t>
+          <t>897</t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AA38" s="3" t="inlineStr">
@@ -6092,8 +5287,7 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2644
-</t>
+          <t>2644</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
@@ -6103,27 +5297,23 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="G39" s="3" t="n"/>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
@@ -6133,8 +5323,7 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
@@ -6142,67 +5331,57 @@
           <t>188</t>
         </is>
       </c>
-      <c r="M39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>171</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
-</t>
+          <t>850</t>
         </is>
       </c>
       <c r="P39" s="3" t="n"/>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
-</t>
-        </is>
-      </c>
-      <c r="R39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222
-</t>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="R39" s="3" t="inlineStr">
+        <is>
+          <t>212</t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="T39" s="3" t="n"/>
       <c r="U39" s="3" t="n"/>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">889
-</t>
+          <t>889</t>
         </is>
       </c>
       <c r="Z39" s="3" t="n"/>
@@ -6221,146 +5400,122 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2864
-</t>
+          <t>2864</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
-</t>
+          <t>287</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">079
-</t>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>177</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">825
-</t>
+          <t>825</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
-      <c r="S40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">207
-</t>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="S40" s="3" t="inlineStr">
+        <is>
+          <t>207</t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">744
-</t>
+          <t>744</t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
-</t>
+          <t>71</t>
         </is>
       </c>
       <c r="V40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">897
-</t>
+          <t>897</t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AA40" s="3" t="inlineStr">
@@ -6378,8 +5533,7 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3590
-</t>
+          <t>3590</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
@@ -6389,99 +5543,83 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
+          <t>156</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
-        </is>
-      </c>
-      <c r="G41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0169
-</t>
-        </is>
-      </c>
-      <c r="H41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">138
-</t>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>138</t>
         </is>
       </c>
       <c r="I41" s="3" t="n"/>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>58</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="M41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">553
-</t>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>153</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">762
-</t>
+          <t>762</t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
-        </is>
-      </c>
-      <c r="S41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">094
-</t>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="S41" s="3" t="inlineStr">
+        <is>
+          <t>204</t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">614
-</t>
-        </is>
-      </c>
-      <c r="U41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
+          <t>614</t>
+        </is>
+      </c>
+      <c r="U41" s="3" t="inlineStr">
+        <is>
+          <t>128</t>
         </is>
       </c>
       <c r="V41" s="3" t="inlineStr">
@@ -6491,26 +5629,22 @@
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">862
-</t>
+          <t>862</t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AA41" s="3" t="inlineStr">
@@ -6533,135 +5667,113 @@
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
-</t>
+          <t>283</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>113</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="I42" s="3" t="n"/>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">63
-</t>
+          <t>63</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
+          <t>157</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6820
-</t>
+          <t>620</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>136</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">579
-</t>
+          <t>579</t>
         </is>
       </c>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
-</t>
+          <t>233</t>
         </is>
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
-</t>
+          <t>705</t>
         </is>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
-</t>
+          <t>71</t>
         </is>
       </c>
       <c r="AA42" s="3" t="inlineStr">
@@ -6679,141 +5791,118 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7426
-</t>
+          <t>288</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
-</t>
+          <t>276</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
-        </is>
-      </c>
-      <c r="G43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">885
-</t>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>101</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="I43" s="3" t="n"/>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">880
-</t>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>180</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
+          <t>157</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">798
-</t>
+          <t>798</t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
-</t>
+          <t>271</t>
         </is>
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">555
-</t>
-        </is>
-      </c>
-      <c r="U43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">166
-</t>
+          <t>555</t>
+        </is>
+      </c>
+      <c r="U43" s="3" t="inlineStr">
+        <is>
+          <t>166</t>
         </is>
       </c>
       <c r="V43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="X43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">185
-</t>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="X43" s="3" t="inlineStr">
+        <is>
+          <t>197</t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
-</t>
+          <t>71</t>
         </is>
       </c>
       <c r="AA43" s="3" t="inlineStr">
@@ -6831,8 +5920,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D44" s="3" t="n"/>
@@ -6873,141 +5961,118 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18890
-</t>
+          <t>8390</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1344
-</t>
+          <t>1344</t>
         </is>
       </c>
       <c r="E45" s="3" t="n"/>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1081
-</t>
+          <t>1081</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">595
-</t>
+          <t>525</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">697
-</t>
+          <t>697</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">861
-</t>
+          <t>261</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">909
-</t>
+          <t>902</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">537
-</t>
+          <t>257</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">710
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14055
-</t>
+          <t>4055</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12684
-</t>
+          <t>1254</t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1018
-</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1048
-</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3300
-</t>
+          <t>3300</t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">556
-</t>
+          <t>556</t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1048
-</t>
+          <t>1048</t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">985
-</t>
+          <t>935</t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182
-</t>
+          <t>012</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1088
-</t>
+          <t>087</t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="AA45" s="3" t="inlineStr">
@@ -7025,32 +6090,27 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3629
-</t>
+          <t>3679</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-</t>
+          <t>269</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">816
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
@@ -7060,110 +6120,92 @@
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">52
-</t>
+          <t>52</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="M46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">659
-</t>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>159</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
-</t>
+          <t>811</t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>39</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
-</t>
+          <t>251</t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">809
-</t>
+          <t>800</t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">814
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="AA46" s="3" t="inlineStr">

--- a/results/05_transient_transcription_output/905/905_197311_SF.JPG_stage_digit_manipulation.xlsx
+++ b/results/05_transient_transcription_output/905/905_197311_SF.JPG_stage_digit_manipulation.xlsx
@@ -783,7 +783,7 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>118</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>4316</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>190</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>898</t>
+          <t>228</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
@@ -1248,12 +1248,12 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>4602</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>224</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>212</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>1404</t>
+          <t>21404</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>4281</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>1661</t>
+          <t>166</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>08</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t>101 14</t>
+          <t>01 214 1</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t>21 14</t>
+          <t>181 14</t>
         </is>
       </c>
       <c r="AA10" s="3" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>28</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
@@ -1948,7 +1948,7 @@
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
@@ -2057,7 +2057,7 @@
       <c r="I14" s="3" t="n"/>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>21 2</t>
+          <t>1 21 2</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>118</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>8348</t>
+          <t>3348</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>118</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>160</t>
         </is>
       </c>
       <c r="V15" s="3" t="inlineStr">
@@ -2308,7 +2308,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>484</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
@@ -2343,12 +2343,12 @@
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>99</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>4659</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
@@ -2492,17 +2492,17 @@
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
+          <t>269</t>
+        </is>
+      </c>
+      <c r="S17" s="3" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="S17" s="3" t="inlineStr">
-        <is>
-          <t>229</t>
-        </is>
-      </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t>788</t>
+          <t>7881</t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t>28 8 1</t>
+          <t>20 2 2</t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
@@ -2605,7 +2605,7 @@
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>118</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t>224 214</t>
+          <t>226 214</t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t>28 12</t>
+          <t>14 214</t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>3194</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>195</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t>890</t>
+          <t>282</t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>140</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
@@ -3004,7 +3004,7 @@
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>280</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>1112</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>99</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
@@ -3284,7 +3284,7 @@
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t>937</t>
+          <t>3937</t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t>1034</t>
+          <t>11034</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
@@ -3427,7 +3427,7 @@
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>221</t>
         </is>
       </c>
       <c r="W24" s="3" t="inlineStr">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2281</t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>215</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
@@ -3552,17 +3552,17 @@
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>2114</t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>214</t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>2624</t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
@@ -3635,7 +3635,7 @@
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>282</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>47</t>
         </is>
       </c>
       <c r="V26" s="3" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>282</t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
@@ -4040,7 +4040,7 @@
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>184</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>8141</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>859</t>
+          <t>288</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>88</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t>922</t>
+          <t>3922</t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t>1018</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
@@ -4228,7 +4228,7 @@
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>1161</t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>2631</t>
+          <t>264</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -4281,17 +4281,17 @@
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>261</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>8 9</t>
+          <t>3 9</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
@@ -4307,7 +4307,7 @@
       <c r="N31" s="3" t="n"/>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>12 90</t>
+          <t>21 90</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
@@ -4347,12 +4347,12 @@
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>204</t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>211</t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
@@ -4405,7 +4405,7 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>13 15</t>
+          <t>13 01</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
@@ -4427,7 +4427,7 @@
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>21</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t>158 8</t>
+          <t>2611 4</t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
@@ -4674,7 +4674,7 @@
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>26</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
@@ -4689,7 +4689,7 @@
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>183</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>176</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
@@ -4822,12 +4822,12 @@
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>102</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>800</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
@@ -4955,7 +4955,7 @@
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>191</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
@@ -5033,7 +5033,7 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>6432</t>
+          <t>16432</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>398</t>
+          <t>8398</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
@@ -5119,28 +5119,28 @@
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>342</t>
         </is>
       </c>
       <c r="V37" s="3" t="n"/>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>9231</t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t>029</t>
+          <t>0294</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t>487</t>
+          <t>1487</t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>011</t>
         </is>
       </c>
       <c r="AA37" s="3" t="inlineStr">
@@ -5158,7 +5158,7 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>3286</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
@@ -5214,7 +5214,7 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>116</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
@@ -5234,7 +5234,7 @@
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>2081</t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
@@ -5249,27 +5249,27 @@
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>196</t>
         </is>
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t>1851</t>
+          <t>183</t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>206</t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t>897</t>
+          <t>891</t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AA38" s="3" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>16</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
@@ -5354,7 +5354,7 @@
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>222</t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>267</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
@@ -5455,7 +5455,7 @@
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>28</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
@@ -5584,7 +5584,7 @@
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>26</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
@@ -5723,7 +5723,7 @@
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>36</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>4426</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
@@ -5842,7 +5842,7 @@
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>734</t>
         </is>
       </c>
       <c r="Z43" s="3" t="inlineStr">
@@ -5961,7 +5961,7 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>8390</t>
+          <t>18390</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
@@ -6007,12 +6007,12 @@
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>237</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>116</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
@@ -6062,17 +6062,17 @@
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t>012</t>
+          <t>212</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t>087</t>
+          <t>1087</t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>214</t>
         </is>
       </c>
       <c r="AA45" s="3" t="inlineStr">
@@ -6110,7 +6110,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>105</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>011</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
@@ -6165,17 +6165,17 @@
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>208</t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>011</t>
         </is>
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>114</t>
         </is>
       </c>
       <c r="U46" s="3" t="inlineStr">
@@ -6185,12 +6185,12 @@
       </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>04</t>
         </is>
       </c>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X46" s="3" t="inlineStr">
@@ -6200,12 +6200,12 @@
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>01</t>
         </is>
       </c>
       <c r="AA46" s="3" t="inlineStr">

--- a/results/05_transient_transcription_output/905/905_197311_SF.JPG_stage_digit_manipulation.xlsx
+++ b/results/05_transient_transcription_output/905/905_197311_SF.JPG_stage_digit_manipulation.xlsx
@@ -783,7 +783,7 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>3744</t>
+          <t>374</t>
         </is>
       </c>
       <c r="D7" s="3" t="n"/>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>898</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>284</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>21404</t>
+          <t>2140</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>1124</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t>031</t>
+          <t>1031</t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>20</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t>01 214 1</t>
+          <t>04 20</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t>181 14</t>
+          <t>00 04</t>
         </is>
       </c>
       <c r="AA10" s="3" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>09</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>19</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
@@ -1928,7 +1928,7 @@
       <c r="I13" s="3" t="n"/>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
@@ -1948,7 +1948,7 @@
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>19</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
@@ -2057,7 +2057,7 @@
       <c r="I14" s="3" t="n"/>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>1 21 2</t>
+          <t>21 2</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>95</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
@@ -2437,7 +2437,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>297</t>
+          <t>97</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t>7881</t>
+          <t>788</t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t>20 2 2</t>
+          <t>20 0 1</t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
@@ -2605,7 +2605,7 @@
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t>226 214</t>
+          <t>800 00</t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t>14 214</t>
+          <t>18 20</t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>20</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>890</t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
@@ -2969,12 +2969,12 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>178</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>840</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
@@ -3004,7 +3004,7 @@
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>19</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>200</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>1112</t>
+          <t>1018</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>91</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t>11034</t>
+          <t>1103</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>1168</t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
@@ -3372,7 +3372,7 @@
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t>2281</t>
+          <t>228</t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
@@ -3552,17 +3552,17 @@
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t>2114</t>
+          <t>20</t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t>2624</t>
+          <t>200</t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
@@ -3635,7 +3635,7 @@
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>170</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
@@ -3778,7 +3778,7 @@
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>011</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>840</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>184</t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>17884</t>
+          <t>1788</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>8141</t>
+          <t>814</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>859</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>2 89</t>
+          <t>8 89</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t>3922</t>
+          <t>392</t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>1018</t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
@@ -4228,7 +4228,7 @@
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t>1161</t>
+          <t>208</t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>263</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
@@ -4291,12 +4291,12 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>1721</t>
+          <t>172</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>00</t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
@@ -4352,7 +4352,7 @@
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
@@ -4405,7 +4405,7 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>13 01</t>
+          <t>13 00</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
@@ -4427,7 +4427,7 @@
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t>2611 4</t>
+          <t>000 2</t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
@@ -4689,7 +4689,7 @@
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
@@ -4955,7 +4955,7 @@
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>14</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
@@ -4995,12 +4995,12 @@
       </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>208</t>
         </is>
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>187</t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
@@ -5015,7 +5015,7 @@
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AA36" s="3" t="inlineStr">
@@ -5125,12 +5125,12 @@
       <c r="V37" s="3" t="n"/>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t>9231</t>
+          <t>923</t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t>0294</t>
+          <t>029</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t>011</t>
+          <t>00</t>
         </is>
       </c>
       <c r="AA37" s="3" t="inlineStr">
@@ -5214,7 +5214,7 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>28</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
@@ -5234,7 +5234,7 @@
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t>2081</t>
+          <t>208</t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>207</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
@@ -5584,7 +5584,7 @@
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
@@ -5713,12 +5713,12 @@
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>820</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>4426</t>
+          <t>9426</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
@@ -5842,7 +5842,7 @@
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
@@ -5920,7 +5920,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D44" s="3" t="n"/>
@@ -5961,7 +5961,7 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>18390</t>
+          <t>1890</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
@@ -6012,7 +6012,7 @@
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>896</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
@@ -6032,12 +6032,12 @@
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>1018</t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t>1042</t>
+          <t>1048</t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
@@ -6062,17 +6062,17 @@
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>288</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t>1087</t>
+          <t>10887</t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>011</t>
         </is>
       </c>
       <c r="AA45" s="3" t="inlineStr">
@@ -6110,7 +6110,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>108</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>011</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
@@ -6170,17 +6170,17 @@
       </c>
       <c r="S46" s="3" t="inlineStr">
         <is>
-          <t>011</t>
+          <t>00</t>
         </is>
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>10</t>
         </is>
       </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="V46" s="3" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
@@ -6205,7 +6205,7 @@
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="AA46" s="3" t="inlineStr">
